--- a/docs/詳細設計書/詳細設計書_在庫センター情報画面.xlsx
+++ b/docs/詳細設計書/詳細設計書_在庫センター情報画面.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="287">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>想定外エラー：都道府県リスト外の文字</t>
+  </si>
+  <si>
+    <t>クリック時：都道府県リスト外を表示</t>
   </si>
   <si>
     <t>　検索</t>
@@ -1053,10 +1056,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="45">
     <font>
@@ -1196,22 +1199,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1224,24 +1228,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1272,14 +1268,68 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1294,54 +1344,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1405,7 +1408,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1417,19 +1444,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1441,19 +1462,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1465,25 +1492,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1495,7 +1504,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1519,43 +1534,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1881,11 +1884,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1929,6 +1930,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1946,9 +1956,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1967,162 +1979,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="20" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="23" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="21" borderId="31" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="22" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5511,7 +5514,7 @@
       </c>
       <c r="I13" s="182"/>
       <c r="J13" s="227" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K13" s="228"/>
     </row>
@@ -5521,23 +5524,23 @@
         <v>7</v>
       </c>
       <c r="B14" s="179" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" s="179"/>
       <c r="D14" s="179"/>
       <c r="E14" s="179"/>
       <c r="F14" s="179" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14" s="179" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H14" s="177" t="s">
         <v>52</v>
       </c>
       <c r="I14" s="224"/>
       <c r="J14" s="225" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K14" s="226"/>
     </row>
@@ -5547,23 +5550,23 @@
         <v>8</v>
       </c>
       <c r="B15" s="180" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="181"/>
       <c r="D15" s="181"/>
       <c r="E15" s="182"/>
       <c r="F15" s="179" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G15" s="179" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H15" s="177" t="s">
         <v>52</v>
       </c>
       <c r="I15" s="224"/>
       <c r="J15" s="225" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K15" s="226"/>
     </row>
@@ -5573,16 +5576,16 @@
         <v>9</v>
       </c>
       <c r="B16" s="179" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" s="179"/>
       <c r="D16" s="179"/>
       <c r="E16" s="179"/>
       <c r="F16" s="179" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G16" s="179" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H16" s="177" t="s">
         <v>52</v>
@@ -5599,16 +5602,16 @@
         <v>10</v>
       </c>
       <c r="B17" s="179" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" s="179"/>
       <c r="D17" s="179"/>
       <c r="E17" s="179"/>
       <c r="F17" s="179" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G17" s="179" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H17" s="177" t="s">
         <v>52</v>
@@ -5625,23 +5628,23 @@
         <v>11</v>
       </c>
       <c r="B18" s="179" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="179"/>
       <c r="D18" s="179"/>
       <c r="E18" s="179"/>
       <c r="F18" s="179" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" s="179" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H18" s="177" t="s">
         <v>52</v>
       </c>
       <c r="I18" s="224"/>
       <c r="J18" s="225" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K18" s="226"/>
     </row>
@@ -5651,7 +5654,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="179" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" s="179"/>
       <c r="D19" s="179"/>
@@ -5660,7 +5663,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="179" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H19" s="177" t="s">
         <v>52</v>
@@ -5677,7 +5680,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="179" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20" s="179"/>
       <c r="D20" s="179"/>
@@ -5686,7 +5689,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="179" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H20" s="177" t="s">
         <v>52</v>
@@ -5703,7 +5706,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="179" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21" s="179"/>
       <c r="D21" s="179"/>
@@ -5712,7 +5715,7 @@
         <v>50</v>
       </c>
       <c r="G21" s="183" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" s="177" t="s">
         <v>52</v>
@@ -5729,7 +5732,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="179" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" s="179"/>
       <c r="D22" s="179"/>
@@ -5738,7 +5741,7 @@
         <v>50</v>
       </c>
       <c r="G22" s="183" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H22" s="177" t="s">
         <v>52</v>
@@ -5755,7 +5758,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="179" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" s="179"/>
       <c r="D23" s="179"/>
@@ -5764,7 +5767,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="183" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" s="177" t="s">
         <v>52</v>
@@ -5781,7 +5784,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="185" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C24" s="185"/>
       <c r="D24" s="185"/>
@@ -5790,7 +5793,7 @@
         <v>50</v>
       </c>
       <c r="G24" s="186" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24" s="187" t="s">
         <v>52</v>
@@ -5820,13 +5823,13 @@
       <c r="C26" s="192"/>
       <c r="D26" s="192"/>
       <c r="E26" s="193" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F26" s="192" t="s">
         <v>43</v>
       </c>
       <c r="G26" s="194" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" s="195"/>
       <c r="I26" s="195"/>
@@ -5870,7 +5873,7 @@
         <v>50</v>
       </c>
       <c r="G28" s="199" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" s="177"/>
       <c r="I28" s="224"/>
@@ -5883,7 +5886,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="203" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" s="204"/>
       <c r="D29" s="204"/>
@@ -5892,7 +5895,7 @@
         <v>50</v>
       </c>
       <c r="G29" s="203" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H29" s="177"/>
       <c r="I29" s="224"/>
@@ -5905,16 +5908,16 @@
         <v>3</v>
       </c>
       <c r="B30" s="203" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" s="204"/>
       <c r="D30" s="204"/>
       <c r="E30" s="204"/>
       <c r="F30" s="205" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G30" s="203" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H30" s="180"/>
       <c r="I30" s="182"/>
@@ -5927,7 +5930,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="206" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C31" s="207"/>
       <c r="D31" s="207"/>
@@ -5936,7 +5939,7 @@
         <v>50</v>
       </c>
       <c r="G31" s="203" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H31" s="180"/>
       <c r="I31" s="182"/>
@@ -5953,10 +5956,10 @@
       <c r="D32" s="207"/>
       <c r="E32" s="207"/>
       <c r="F32" s="205" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G32" s="208" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H32" s="180"/>
       <c r="I32" s="182"/>
@@ -5969,7 +5972,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="206" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C33" s="207"/>
       <c r="D33" s="207"/>
@@ -5978,7 +5981,7 @@
         <v>50</v>
       </c>
       <c r="G33" s="203" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H33" s="180"/>
       <c r="I33" s="182"/>
@@ -5995,10 +5998,10 @@
       <c r="D34" s="207"/>
       <c r="E34" s="207"/>
       <c r="F34" s="205" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G34" s="203" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H34" s="177"/>
       <c r="I34" s="224"/>
@@ -6011,7 +6014,7 @@
         <v>8</v>
       </c>
       <c r="B35" s="206" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="207"/>
@@ -6020,7 +6023,7 @@
         <v>50</v>
       </c>
       <c r="G35" s="203" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H35" s="177"/>
       <c r="I35" s="224"/>
@@ -6037,10 +6040,10 @@
       <c r="D36" s="207"/>
       <c r="E36" s="207"/>
       <c r="F36" s="205" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G36" s="203" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H36" s="177"/>
       <c r="I36" s="224"/>
@@ -6053,7 +6056,7 @@
         <v>10</v>
       </c>
       <c r="B37" s="206" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C37" s="207"/>
       <c r="D37" s="207"/>
@@ -6062,7 +6065,7 @@
         <v>50</v>
       </c>
       <c r="G37" s="203" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H37" s="177"/>
       <c r="I37" s="224"/>
@@ -6079,10 +6082,10 @@
       <c r="D38" s="207"/>
       <c r="E38" s="207"/>
       <c r="F38" s="205" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G38" s="203" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H38" s="177"/>
       <c r="I38" s="224"/>
@@ -6095,7 +6098,7 @@
         <v>12</v>
       </c>
       <c r="B39" s="206" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C39" s="207"/>
       <c r="D39" s="207"/>
@@ -6104,7 +6107,7 @@
         <v>50</v>
       </c>
       <c r="G39" s="203" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H39" s="180"/>
       <c r="I39" s="182"/>
@@ -6121,10 +6124,10 @@
       <c r="D40" s="207"/>
       <c r="E40" s="207"/>
       <c r="F40" s="205" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G40" s="203" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H40" s="180"/>
       <c r="I40" s="182"/>
@@ -6137,7 +6140,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="206" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C41" s="207"/>
       <c r="D41" s="207"/>
@@ -6146,7 +6149,7 @@
         <v>50</v>
       </c>
       <c r="G41" s="203" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H41" s="180"/>
       <c r="I41" s="182"/>
@@ -6163,10 +6166,10 @@
       <c r="D42" s="207"/>
       <c r="E42" s="207"/>
       <c r="F42" s="205" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G42" s="203" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H42" s="180"/>
       <c r="I42" s="182"/>
@@ -6179,7 +6182,7 @@
         <v>16</v>
       </c>
       <c r="B43" s="206" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C43" s="207"/>
       <c r="D43" s="207"/>
@@ -6188,7 +6191,7 @@
         <v>50</v>
       </c>
       <c r="G43" s="203" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H43" s="177"/>
       <c r="I43" s="224"/>
@@ -6205,10 +6208,10 @@
       <c r="D44" s="207"/>
       <c r="E44" s="207"/>
       <c r="F44" s="205" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G44" s="203" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H44" s="177"/>
       <c r="I44" s="224"/>
@@ -6221,7 +6224,7 @@
         <v>18</v>
       </c>
       <c r="B45" s="206" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C45" s="207"/>
       <c r="D45" s="207"/>
@@ -6230,7 +6233,7 @@
         <v>50</v>
       </c>
       <c r="G45" s="203" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H45" s="180"/>
       <c r="I45" s="182"/>
@@ -6247,10 +6250,10 @@
       <c r="D46" s="207"/>
       <c r="E46" s="207"/>
       <c r="F46" s="205" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G46" s="203" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H46" s="180"/>
       <c r="I46" s="182"/>
@@ -6263,7 +6266,7 @@
         <v>20</v>
       </c>
       <c r="B47" s="206" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C47" s="207"/>
       <c r="D47" s="207"/>
@@ -6272,7 +6275,7 @@
         <v>50</v>
       </c>
       <c r="G47" s="203" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H47" s="180"/>
       <c r="I47" s="182"/>
@@ -6289,10 +6292,10 @@
       <c r="D48" s="207"/>
       <c r="E48" s="207"/>
       <c r="F48" s="205" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G48" s="203" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H48" s="180"/>
       <c r="I48" s="182"/>
@@ -6305,16 +6308,16 @@
         <v>22</v>
       </c>
       <c r="B49" s="203" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C49" s="204"/>
       <c r="D49" s="204"/>
       <c r="E49" s="204"/>
       <c r="F49" s="205" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G49" s="207" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H49" s="177"/>
       <c r="I49" s="224"/>
@@ -6327,16 +6330,16 @@
         <v>23</v>
       </c>
       <c r="B50" s="210" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C50" s="211"/>
       <c r="D50" s="211"/>
       <c r="E50" s="211"/>
       <c r="F50" s="212" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G50" s="210" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H50" s="187"/>
       <c r="I50" s="229"/>
@@ -6363,13 +6366,13 @@
       <c r="C52" s="192"/>
       <c r="D52" s="192"/>
       <c r="E52" s="193" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F52" s="192" t="s">
         <v>43</v>
       </c>
       <c r="G52" s="194" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H52" s="195"/>
       <c r="I52" s="195"/>
@@ -6404,7 +6407,7 @@
         <v>1</v>
       </c>
       <c r="B54" s="199" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C54" s="200"/>
       <c r="D54" s="200"/>
@@ -6413,7 +6416,7 @@
         <v>50</v>
       </c>
       <c r="G54" s="199" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H54" s="177"/>
       <c r="I54" s="224"/>
@@ -6426,16 +6429,16 @@
         <v>2</v>
       </c>
       <c r="B55" s="203" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C55" s="204"/>
       <c r="D55" s="204"/>
       <c r="E55" s="204"/>
       <c r="F55" s="205" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G55" s="203" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H55" s="177"/>
       <c r="I55" s="224"/>
@@ -6448,7 +6451,7 @@
         <v>3</v>
       </c>
       <c r="B56" s="206" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C56" s="207"/>
       <c r="D56" s="207"/>
@@ -6457,7 +6460,7 @@
         <v>50</v>
       </c>
       <c r="G56" s="203" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H56" s="180"/>
       <c r="I56" s="182"/>
@@ -6474,10 +6477,10 @@
       <c r="D57" s="207"/>
       <c r="E57" s="207"/>
       <c r="F57" s="205" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G57" s="203" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H57" s="180"/>
       <c r="I57" s="182"/>
@@ -6490,7 +6493,7 @@
         <v>5</v>
       </c>
       <c r="B58" s="206" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" s="207"/>
       <c r="D58" s="207"/>
@@ -6499,7 +6502,7 @@
         <v>50</v>
       </c>
       <c r="G58" s="203" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H58" s="180"/>
       <c r="I58" s="182"/>
@@ -6516,10 +6519,10 @@
       <c r="D59" s="207"/>
       <c r="E59" s="207"/>
       <c r="F59" s="205" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G59" s="203" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H59" s="180"/>
       <c r="I59" s="182"/>
@@ -6532,7 +6535,7 @@
         <v>7</v>
       </c>
       <c r="B60" s="206" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C60" s="207"/>
       <c r="D60" s="207"/>
@@ -6541,7 +6544,7 @@
         <v>50</v>
       </c>
       <c r="G60" s="203" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H60" s="177"/>
       <c r="I60" s="224"/>
@@ -6558,10 +6561,10 @@
       <c r="D61" s="207"/>
       <c r="E61" s="207"/>
       <c r="F61" s="205" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G61" s="203" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H61" s="177"/>
       <c r="I61" s="224"/>
@@ -6574,7 +6577,7 @@
         <v>9</v>
       </c>
       <c r="B62" s="206" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C62" s="207"/>
       <c r="D62" s="207"/>
@@ -6583,7 +6586,7 @@
         <v>50</v>
       </c>
       <c r="G62" s="203" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H62" s="177"/>
       <c r="I62" s="224"/>
@@ -6600,10 +6603,10 @@
       <c r="D63" s="207"/>
       <c r="E63" s="207"/>
       <c r="F63" s="205" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G63" s="203" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H63" s="177"/>
       <c r="I63" s="224"/>
@@ -6616,7 +6619,7 @@
         <v>11</v>
       </c>
       <c r="B64" s="206" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C64" s="207"/>
       <c r="D64" s="207"/>
@@ -6625,7 +6628,7 @@
         <v>50</v>
       </c>
       <c r="G64" s="203" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H64" s="177"/>
       <c r="I64" s="224"/>
@@ -6642,10 +6645,10 @@
       <c r="D65" s="207"/>
       <c r="E65" s="207"/>
       <c r="F65" s="205" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G65" s="203" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H65" s="180"/>
       <c r="I65" s="182"/>
@@ -6658,7 +6661,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="206" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C66" s="207"/>
       <c r="D66" s="207"/>
@@ -6667,7 +6670,7 @@
         <v>50</v>
       </c>
       <c r="G66" s="203" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H66" s="180"/>
       <c r="I66" s="182"/>
@@ -6684,10 +6687,10 @@
       <c r="D67" s="207"/>
       <c r="E67" s="207"/>
       <c r="F67" s="205" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G67" s="203" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H67" s="180"/>
       <c r="I67" s="182"/>
@@ -6700,7 +6703,7 @@
         <v>15</v>
       </c>
       <c r="B68" s="206" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C68" s="207"/>
       <c r="D68" s="207"/>
@@ -6709,7 +6712,7 @@
         <v>50</v>
       </c>
       <c r="G68" s="203" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H68" s="180"/>
       <c r="I68" s="182"/>
@@ -6726,10 +6729,10 @@
       <c r="D69" s="207"/>
       <c r="E69" s="207"/>
       <c r="F69" s="205" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G69" s="203" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H69" s="177"/>
       <c r="I69" s="224"/>
@@ -6742,7 +6745,7 @@
         <v>17</v>
       </c>
       <c r="B70" s="206" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C70" s="207"/>
       <c r="D70" s="207"/>
@@ -6751,7 +6754,7 @@
         <v>50</v>
       </c>
       <c r="G70" s="203" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H70" s="177"/>
       <c r="I70" s="224"/>
@@ -6768,10 +6771,10 @@
       <c r="D71" s="207"/>
       <c r="E71" s="207"/>
       <c r="F71" s="205" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G71" s="203" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H71" s="180"/>
       <c r="I71" s="182"/>
@@ -6784,7 +6787,7 @@
         <v>19</v>
       </c>
       <c r="B72" s="206" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C72" s="207"/>
       <c r="D72" s="207"/>
@@ -6793,7 +6796,7 @@
         <v>50</v>
       </c>
       <c r="G72" s="203" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H72" s="180"/>
       <c r="I72" s="182"/>
@@ -6810,10 +6813,10 @@
       <c r="D73" s="207"/>
       <c r="E73" s="207"/>
       <c r="F73" s="205" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G73" s="203" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H73" s="180"/>
       <c r="I73" s="182"/>
@@ -6826,16 +6829,16 @@
         <v>21</v>
       </c>
       <c r="B74" s="203" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C74" s="204"/>
       <c r="D74" s="204"/>
       <c r="E74" s="204"/>
       <c r="F74" s="205" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G74" s="207" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H74" s="180"/>
       <c r="I74" s="182"/>
@@ -6848,16 +6851,16 @@
         <v>22</v>
       </c>
       <c r="B75" s="203" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C75" s="204"/>
       <c r="D75" s="204"/>
       <c r="E75" s="204"/>
       <c r="F75" s="205" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G75" s="208" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H75" s="177"/>
       <c r="I75" s="224"/>
@@ -6870,16 +6873,16 @@
         <v>23</v>
       </c>
       <c r="B76" s="210" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C76" s="211"/>
       <c r="D76" s="211"/>
       <c r="E76" s="211"/>
       <c r="F76" s="212" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G76" s="236" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H76" s="187"/>
       <c r="I76" s="229"/>
@@ -7096,7 +7099,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:38">
       <c r="A1" s="65" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -7334,7 +7337,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:38">
       <c r="A6" s="75" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B6" s="76"/>
       <c r="C6" s="76"/>
@@ -7376,7 +7379,7 @@
     </row>
     <row r="7" customHeight="1" spans="1:38">
       <c r="A7" s="77" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B7" s="77"/>
       <c r="C7" s="77"/>
@@ -7419,7 +7422,7 @@
     <row r="8" customHeight="1" spans="1:38">
       <c r="A8" s="78"/>
       <c r="B8" s="79" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C8" s="79"/>
       <c r="D8" s="79"/>
@@ -7462,7 +7465,7 @@
       <c r="A9" s="78"/>
       <c r="B9" s="79"/>
       <c r="C9" s="80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D9" s="81"/>
       <c r="E9" s="81"/>
@@ -7544,7 +7547,7 @@
       <c r="A11" s="78"/>
       <c r="B11" s="79"/>
       <c r="C11" s="78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D11" s="79"/>
       <c r="E11" s="79"/>
@@ -7609,7 +7612,7 @@
       <c r="A13" s="78"/>
       <c r="B13" s="79"/>
       <c r="C13" s="78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D13" s="79"/>
       <c r="E13" s="79"/>
@@ -7620,7 +7623,7 @@
       </c>
       <c r="I13" s="79"/>
       <c r="L13" s="64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N13" s="99"/>
       <c r="O13" s="99"/>
@@ -7628,15 +7631,15 @@
       <c r="Q13" s="99"/>
       <c r="R13" s="99"/>
       <c r="U13" s="64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W13" s="99"/>
       <c r="X13" s="99"/>
       <c r="Y13" s="125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AF13" s="126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG13" s="126"/>
       <c r="AJ13" s="90"/>
@@ -7661,44 +7664,44 @@
       <c r="A15" s="78"/>
       <c r="B15" s="79"/>
       <c r="C15" s="78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" s="79"/>
       <c r="E15" s="79"/>
       <c r="F15" s="90"/>
       <c r="G15" s="79"/>
       <c r="J15" s="100" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K15" s="101"/>
       <c r="L15" s="101"/>
       <c r="M15" s="102"/>
       <c r="N15" s="100" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O15" s="101"/>
       <c r="P15" s="101"/>
       <c r="Q15" s="102"/>
       <c r="R15" s="114" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S15" s="115"/>
       <c r="T15" s="115"/>
       <c r="U15" s="116"/>
       <c r="V15" s="114" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W15" s="115"/>
       <c r="X15" s="115"/>
       <c r="Y15" s="116"/>
       <c r="Z15" s="114" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA15" s="115"/>
       <c r="AB15" s="115"/>
       <c r="AC15" s="116"/>
       <c r="AD15" s="114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE15" s="115"/>
       <c r="AF15" s="115"/>
@@ -7718,25 +7721,25 @@
       <c r="F16" s="90"/>
       <c r="G16" s="79"/>
       <c r="J16" s="103" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K16" s="104"/>
       <c r="L16" s="104"/>
       <c r="M16" s="105"/>
       <c r="N16" s="106" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O16" s="107"/>
       <c r="P16" s="107"/>
       <c r="Q16" s="117"/>
       <c r="R16" s="118" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="S16" s="119"/>
       <c r="T16" s="119"/>
       <c r="U16" s="120"/>
       <c r="V16" s="106" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="W16" s="107"/>
       <c r="X16" s="107"/>
@@ -7763,32 +7766,32 @@
       <c r="A17" s="78"/>
       <c r="B17" s="79"/>
       <c r="C17" s="78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D17" s="79"/>
       <c r="E17" s="79"/>
       <c r="F17" s="90"/>
       <c r="G17" s="79"/>
       <c r="J17" s="103" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K17" s="104"/>
       <c r="L17" s="104"/>
       <c r="M17" s="105"/>
       <c r="N17" s="106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O17" s="107"/>
       <c r="P17" s="107"/>
       <c r="Q17" s="117"/>
       <c r="R17" s="118" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S17" s="119"/>
       <c r="T17" s="119"/>
       <c r="U17" s="120"/>
       <c r="V17" s="106" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="W17" s="107"/>
       <c r="X17" s="107"/>
@@ -7820,25 +7823,25 @@
       <c r="F18" s="90"/>
       <c r="G18" s="79"/>
       <c r="J18" s="103" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K18" s="104"/>
       <c r="L18" s="104"/>
       <c r="M18" s="105"/>
       <c r="N18" s="106" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O18" s="107"/>
       <c r="P18" s="107"/>
       <c r="Q18" s="117"/>
       <c r="R18" s="118" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S18" s="119"/>
       <c r="T18" s="119"/>
       <c r="U18" s="120"/>
       <c r="V18" s="106" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="W18" s="107"/>
       <c r="X18" s="107"/>
@@ -7870,25 +7873,25 @@
       <c r="F19" s="90"/>
       <c r="G19" s="79"/>
       <c r="J19" s="103" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K19" s="104"/>
       <c r="L19" s="104"/>
       <c r="M19" s="105"/>
       <c r="N19" s="106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O19" s="107"/>
       <c r="P19" s="107"/>
       <c r="Q19" s="117"/>
       <c r="R19" s="118" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S19" s="119"/>
       <c r="T19" s="119"/>
       <c r="U19" s="120"/>
       <c r="V19" s="106" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="W19" s="107"/>
       <c r="X19" s="107"/>
@@ -7920,25 +7923,25 @@
       <c r="F20" s="90"/>
       <c r="G20" s="79"/>
       <c r="J20" s="103" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K20" s="104"/>
       <c r="L20" s="104"/>
       <c r="M20" s="105"/>
       <c r="N20" s="106" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O20" s="107"/>
       <c r="P20" s="107"/>
       <c r="Q20" s="117"/>
       <c r="R20" s="118" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S20" s="119"/>
       <c r="T20" s="119"/>
       <c r="U20" s="120"/>
       <c r="V20" s="106" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="W20" s="107"/>
       <c r="X20" s="107"/>
@@ -7970,25 +7973,25 @@
       <c r="F21" s="90"/>
       <c r="G21" s="79"/>
       <c r="J21" s="103" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K21" s="104"/>
       <c r="L21" s="104"/>
       <c r="M21" s="105"/>
       <c r="N21" s="106" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O21" s="107"/>
       <c r="P21" s="107"/>
       <c r="Q21" s="117"/>
       <c r="R21" s="118" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="S21" s="119"/>
       <c r="T21" s="119"/>
       <c r="U21" s="120"/>
       <c r="V21" s="106" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W21" s="107"/>
       <c r="X21" s="107"/>
@@ -8020,37 +8023,37 @@
       <c r="F22" s="90"/>
       <c r="G22" s="79"/>
       <c r="J22" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K22" s="109"/>
       <c r="L22" s="109"/>
       <c r="M22" s="110"/>
       <c r="N22" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O22" s="109"/>
       <c r="P22" s="109"/>
       <c r="Q22" s="110"/>
       <c r="R22" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S22" s="122"/>
       <c r="T22" s="122"/>
       <c r="U22" s="123"/>
       <c r="V22" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W22" s="109"/>
       <c r="X22" s="109"/>
       <c r="Y22" s="110"/>
       <c r="Z22" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA22" s="109"/>
       <c r="AB22" s="109"/>
       <c r="AC22" s="110"/>
       <c r="AD22" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE22" s="109"/>
       <c r="AF22" s="109"/>
@@ -8070,37 +8073,37 @@
       <c r="F23" s="90"/>
       <c r="G23" s="79"/>
       <c r="J23" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K23" s="109"/>
       <c r="L23" s="109"/>
       <c r="M23" s="110"/>
       <c r="N23" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O23" s="109"/>
       <c r="P23" s="109"/>
       <c r="Q23" s="110"/>
       <c r="R23" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S23" s="122"/>
       <c r="T23" s="122"/>
       <c r="U23" s="123"/>
       <c r="V23" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W23" s="109"/>
       <c r="X23" s="109"/>
       <c r="Y23" s="110"/>
       <c r="Z23" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA23" s="109"/>
       <c r="AB23" s="109"/>
       <c r="AC23" s="110"/>
       <c r="AD23" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE23" s="109"/>
       <c r="AF23" s="109"/>
@@ -8120,37 +8123,37 @@
       <c r="F24" s="90"/>
       <c r="G24" s="79"/>
       <c r="J24" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K24" s="109"/>
       <c r="L24" s="109"/>
       <c r="M24" s="110"/>
       <c r="N24" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O24" s="109"/>
       <c r="P24" s="109"/>
       <c r="Q24" s="110"/>
       <c r="R24" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S24" s="122"/>
       <c r="T24" s="122"/>
       <c r="U24" s="123"/>
       <c r="V24" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W24" s="109"/>
       <c r="X24" s="109"/>
       <c r="Y24" s="110"/>
       <c r="Z24" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA24" s="109"/>
       <c r="AB24" s="109"/>
       <c r="AC24" s="110"/>
       <c r="AD24" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE24" s="109"/>
       <c r="AF24" s="109"/>
@@ -8170,37 +8173,37 @@
       <c r="F25" s="90"/>
       <c r="G25" s="79"/>
       <c r="J25" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K25" s="109"/>
       <c r="L25" s="109"/>
       <c r="M25" s="110"/>
       <c r="N25" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O25" s="109"/>
       <c r="P25" s="109"/>
       <c r="Q25" s="110"/>
       <c r="R25" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S25" s="122"/>
       <c r="T25" s="122"/>
       <c r="U25" s="123"/>
       <c r="V25" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W25" s="109"/>
       <c r="X25" s="109"/>
       <c r="Y25" s="110"/>
       <c r="Z25" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA25" s="109"/>
       <c r="AB25" s="109"/>
       <c r="AC25" s="110"/>
       <c r="AD25" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE25" s="109"/>
       <c r="AF25" s="109"/>
@@ -8220,37 +8223,37 @@
       <c r="F26" s="90"/>
       <c r="G26" s="79"/>
       <c r="J26" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K26" s="109"/>
       <c r="L26" s="109"/>
       <c r="M26" s="110"/>
       <c r="N26" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O26" s="109"/>
       <c r="P26" s="109"/>
       <c r="Q26" s="110"/>
       <c r="R26" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S26" s="122"/>
       <c r="T26" s="122"/>
       <c r="U26" s="123"/>
       <c r="V26" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W26" s="109"/>
       <c r="X26" s="109"/>
       <c r="Y26" s="110"/>
       <c r="Z26" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA26" s="109"/>
       <c r="AB26" s="109"/>
       <c r="AC26" s="110"/>
       <c r="AD26" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE26" s="109"/>
       <c r="AF26" s="109"/>
@@ -8270,37 +8273,37 @@
       <c r="F27" s="90"/>
       <c r="G27" s="79"/>
       <c r="J27" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K27" s="109"/>
       <c r="L27" s="109"/>
       <c r="M27" s="110"/>
       <c r="N27" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O27" s="109"/>
       <c r="P27" s="109"/>
       <c r="Q27" s="110"/>
       <c r="R27" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S27" s="122"/>
       <c r="T27" s="122"/>
       <c r="U27" s="123"/>
       <c r="V27" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W27" s="109"/>
       <c r="X27" s="109"/>
       <c r="Y27" s="110"/>
       <c r="Z27" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA27" s="109"/>
       <c r="AB27" s="109"/>
       <c r="AC27" s="110"/>
       <c r="AD27" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE27" s="109"/>
       <c r="AF27" s="109"/>
@@ -8320,37 +8323,37 @@
       <c r="F28" s="90"/>
       <c r="G28" s="79"/>
       <c r="J28" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K28" s="109"/>
       <c r="L28" s="109"/>
       <c r="M28" s="110"/>
       <c r="N28" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O28" s="109"/>
       <c r="P28" s="109"/>
       <c r="Q28" s="110"/>
       <c r="R28" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S28" s="122"/>
       <c r="T28" s="122"/>
       <c r="U28" s="123"/>
       <c r="V28" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W28" s="109"/>
       <c r="X28" s="109"/>
       <c r="Y28" s="110"/>
       <c r="Z28" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA28" s="109"/>
       <c r="AB28" s="109"/>
       <c r="AC28" s="110"/>
       <c r="AD28" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE28" s="109"/>
       <c r="AF28" s="109"/>
@@ -8395,7 +8398,7 @@
       <c r="AE30" s="79"/>
       <c r="AF30" s="79"/>
       <c r="AG30" s="130" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AH30" s="130"/>
       <c r="AI30" s="130"/>
@@ -8486,7 +8489,7 @@
     <row r="33" customHeight="1" spans="1:38">
       <c r="A33" s="78"/>
       <c r="B33" s="79" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="79"/>
       <c r="D33" s="79"/>
@@ -8529,7 +8532,7 @@
       <c r="A34" s="78"/>
       <c r="B34" s="79"/>
       <c r="C34" s="80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D34" s="81"/>
       <c r="E34" s="81"/>
@@ -8611,7 +8614,7 @@
       <c r="A36" s="78"/>
       <c r="B36" s="79"/>
       <c r="C36" s="78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D36" s="79"/>
       <c r="E36" s="79"/>
@@ -8676,7 +8679,7 @@
       <c r="A38" s="78"/>
       <c r="B38" s="79"/>
       <c r="C38" s="78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D38" s="79"/>
       <c r="E38" s="79"/>
@@ -8687,7 +8690,7 @@
       </c>
       <c r="I38" s="79"/>
       <c r="L38" s="64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N38" s="99"/>
       <c r="O38" s="99"/>
@@ -8695,15 +8698,15 @@
       <c r="Q38" s="99"/>
       <c r="R38" s="99"/>
       <c r="U38" s="64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W38" s="99"/>
       <c r="X38" s="99"/>
       <c r="Y38" s="125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AF38" s="126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG38" s="126"/>
       <c r="AJ38" s="90"/>
@@ -8728,44 +8731,44 @@
       <c r="A40" s="78"/>
       <c r="B40" s="79"/>
       <c r="C40" s="78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D40" s="79"/>
       <c r="E40" s="79"/>
       <c r="F40" s="90"/>
       <c r="G40" s="79"/>
       <c r="J40" s="100" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K40" s="101"/>
       <c r="L40" s="101"/>
       <c r="M40" s="102"/>
       <c r="N40" s="100" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O40" s="101"/>
       <c r="P40" s="101"/>
       <c r="Q40" s="102"/>
       <c r="R40" s="114" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S40" s="115"/>
       <c r="T40" s="115"/>
       <c r="U40" s="116"/>
       <c r="V40" s="114" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W40" s="115"/>
       <c r="X40" s="115"/>
       <c r="Y40" s="116"/>
       <c r="Z40" s="114" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA40" s="115"/>
       <c r="AB40" s="115"/>
       <c r="AC40" s="116"/>
       <c r="AD40" s="114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE40" s="115"/>
       <c r="AF40" s="115"/>
@@ -8785,25 +8788,25 @@
       <c r="F41" s="90"/>
       <c r="G41" s="79"/>
       <c r="J41" s="103" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K41" s="104"/>
       <c r="L41" s="104"/>
       <c r="M41" s="105"/>
       <c r="N41" s="106" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O41" s="107"/>
       <c r="P41" s="107"/>
       <c r="Q41" s="117"/>
       <c r="R41" s="118" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="S41" s="119"/>
       <c r="T41" s="119"/>
       <c r="U41" s="120"/>
       <c r="V41" s="106" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="W41" s="107"/>
       <c r="X41" s="107"/>
@@ -8830,32 +8833,32 @@
       <c r="A42" s="78"/>
       <c r="B42" s="79"/>
       <c r="C42" s="78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D42" s="79"/>
       <c r="E42" s="79"/>
       <c r="F42" s="90"/>
       <c r="G42" s="79"/>
       <c r="J42" s="103" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K42" s="104"/>
       <c r="L42" s="104"/>
       <c r="M42" s="105"/>
       <c r="N42" s="106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O42" s="107"/>
       <c r="P42" s="107"/>
       <c r="Q42" s="117"/>
       <c r="R42" s="118" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S42" s="119"/>
       <c r="T42" s="119"/>
       <c r="U42" s="120"/>
       <c r="V42" s="106" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="W42" s="107"/>
       <c r="X42" s="107"/>
@@ -8887,25 +8890,25 @@
       <c r="F43" s="90"/>
       <c r="G43" s="79"/>
       <c r="J43" s="103" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K43" s="104"/>
       <c r="L43" s="104"/>
       <c r="M43" s="105"/>
       <c r="N43" s="106" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O43" s="107"/>
       <c r="P43" s="107"/>
       <c r="Q43" s="117"/>
       <c r="R43" s="118" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S43" s="119"/>
       <c r="T43" s="119"/>
       <c r="U43" s="120"/>
       <c r="V43" s="106" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="W43" s="107"/>
       <c r="X43" s="107"/>
@@ -8937,25 +8940,25 @@
       <c r="F44" s="90"/>
       <c r="G44" s="79"/>
       <c r="J44" s="103" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K44" s="104"/>
       <c r="L44" s="104"/>
       <c r="M44" s="105"/>
       <c r="N44" s="106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O44" s="107"/>
       <c r="P44" s="107"/>
       <c r="Q44" s="117"/>
       <c r="R44" s="118" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S44" s="119"/>
       <c r="T44" s="119"/>
       <c r="U44" s="120"/>
       <c r="V44" s="106" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="W44" s="107"/>
       <c r="X44" s="107"/>
@@ -8987,25 +8990,25 @@
       <c r="F45" s="90"/>
       <c r="G45" s="79"/>
       <c r="J45" s="103" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K45" s="104"/>
       <c r="L45" s="104"/>
       <c r="M45" s="105"/>
       <c r="N45" s="106" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O45" s="107"/>
       <c r="P45" s="107"/>
       <c r="Q45" s="117"/>
       <c r="R45" s="118" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S45" s="119"/>
       <c r="T45" s="119"/>
       <c r="U45" s="120"/>
       <c r="V45" s="106" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="W45" s="107"/>
       <c r="X45" s="107"/>
@@ -9037,25 +9040,25 @@
       <c r="F46" s="90"/>
       <c r="G46" s="79"/>
       <c r="J46" s="103" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K46" s="104"/>
       <c r="L46" s="104"/>
       <c r="M46" s="105"/>
       <c r="N46" s="106" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O46" s="107"/>
       <c r="P46" s="107"/>
       <c r="Q46" s="117"/>
       <c r="R46" s="118" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="S46" s="119"/>
       <c r="T46" s="119"/>
       <c r="U46" s="120"/>
       <c r="V46" s="106" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W46" s="107"/>
       <c r="X46" s="107"/>
@@ -9087,37 +9090,37 @@
       <c r="F47" s="90"/>
       <c r="G47" s="79"/>
       <c r="J47" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K47" s="109"/>
       <c r="L47" s="109"/>
       <c r="M47" s="110"/>
       <c r="N47" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O47" s="109"/>
       <c r="P47" s="109"/>
       <c r="Q47" s="110"/>
       <c r="R47" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S47" s="122"/>
       <c r="T47" s="122"/>
       <c r="U47" s="123"/>
       <c r="V47" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W47" s="109"/>
       <c r="X47" s="109"/>
       <c r="Y47" s="110"/>
       <c r="Z47" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA47" s="109"/>
       <c r="AB47" s="109"/>
       <c r="AC47" s="110"/>
       <c r="AD47" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE47" s="109"/>
       <c r="AF47" s="109"/>
@@ -9137,37 +9140,37 @@
       <c r="F48" s="90"/>
       <c r="G48" s="79"/>
       <c r="J48" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K48" s="109"/>
       <c r="L48" s="109"/>
       <c r="M48" s="110"/>
       <c r="N48" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O48" s="109"/>
       <c r="P48" s="109"/>
       <c r="Q48" s="110"/>
       <c r="R48" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S48" s="122"/>
       <c r="T48" s="122"/>
       <c r="U48" s="123"/>
       <c r="V48" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W48" s="109"/>
       <c r="X48" s="109"/>
       <c r="Y48" s="110"/>
       <c r="Z48" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA48" s="109"/>
       <c r="AB48" s="109"/>
       <c r="AC48" s="110"/>
       <c r="AD48" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE48" s="109"/>
       <c r="AF48" s="109"/>
@@ -9187,37 +9190,37 @@
       <c r="F49" s="90"/>
       <c r="G49" s="79"/>
       <c r="J49" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K49" s="109"/>
       <c r="L49" s="109"/>
       <c r="M49" s="110"/>
       <c r="N49" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O49" s="109"/>
       <c r="P49" s="109"/>
       <c r="Q49" s="110"/>
       <c r="R49" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S49" s="122"/>
       <c r="T49" s="122"/>
       <c r="U49" s="123"/>
       <c r="V49" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W49" s="109"/>
       <c r="X49" s="109"/>
       <c r="Y49" s="110"/>
       <c r="Z49" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA49" s="109"/>
       <c r="AB49" s="109"/>
       <c r="AC49" s="110"/>
       <c r="AD49" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE49" s="109"/>
       <c r="AF49" s="109"/>
@@ -9237,37 +9240,37 @@
       <c r="F50" s="90"/>
       <c r="G50" s="79"/>
       <c r="J50" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K50" s="109"/>
       <c r="L50" s="109"/>
       <c r="M50" s="110"/>
       <c r="N50" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O50" s="109"/>
       <c r="P50" s="109"/>
       <c r="Q50" s="110"/>
       <c r="R50" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S50" s="122"/>
       <c r="T50" s="122"/>
       <c r="U50" s="123"/>
       <c r="V50" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W50" s="109"/>
       <c r="X50" s="109"/>
       <c r="Y50" s="110"/>
       <c r="Z50" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA50" s="109"/>
       <c r="AB50" s="109"/>
       <c r="AC50" s="110"/>
       <c r="AD50" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE50" s="109"/>
       <c r="AF50" s="109"/>
@@ -9287,37 +9290,37 @@
       <c r="F51" s="90"/>
       <c r="G51" s="79"/>
       <c r="J51" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K51" s="109"/>
       <c r="L51" s="109"/>
       <c r="M51" s="110"/>
       <c r="N51" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O51" s="109"/>
       <c r="P51" s="109"/>
       <c r="Q51" s="110"/>
       <c r="R51" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S51" s="122"/>
       <c r="T51" s="122"/>
       <c r="U51" s="123"/>
       <c r="V51" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W51" s="109"/>
       <c r="X51" s="109"/>
       <c r="Y51" s="110"/>
       <c r="Z51" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA51" s="109"/>
       <c r="AB51" s="109"/>
       <c r="AC51" s="110"/>
       <c r="AD51" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE51" s="109"/>
       <c r="AF51" s="109"/>
@@ -9337,37 +9340,37 @@
       <c r="F52" s="90"/>
       <c r="G52" s="79"/>
       <c r="J52" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K52" s="109"/>
       <c r="L52" s="109"/>
       <c r="M52" s="110"/>
       <c r="N52" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O52" s="109"/>
       <c r="P52" s="109"/>
       <c r="Q52" s="110"/>
       <c r="R52" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S52" s="122"/>
       <c r="T52" s="122"/>
       <c r="U52" s="123"/>
       <c r="V52" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W52" s="109"/>
       <c r="X52" s="109"/>
       <c r="Y52" s="110"/>
       <c r="Z52" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA52" s="109"/>
       <c r="AB52" s="109"/>
       <c r="AC52" s="110"/>
       <c r="AD52" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE52" s="109"/>
       <c r="AF52" s="109"/>
@@ -9387,37 +9390,37 @@
       <c r="F53" s="90"/>
       <c r="G53" s="79"/>
       <c r="J53" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K53" s="109"/>
       <c r="L53" s="109"/>
       <c r="M53" s="110"/>
       <c r="N53" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O53" s="109"/>
       <c r="P53" s="109"/>
       <c r="Q53" s="110"/>
       <c r="R53" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S53" s="122"/>
       <c r="T53" s="122"/>
       <c r="U53" s="123"/>
       <c r="V53" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W53" s="109"/>
       <c r="X53" s="109"/>
       <c r="Y53" s="110"/>
       <c r="Z53" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA53" s="109"/>
       <c r="AB53" s="109"/>
       <c r="AC53" s="110"/>
       <c r="AD53" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE53" s="109"/>
       <c r="AF53" s="109"/>
@@ -9462,7 +9465,7 @@
       <c r="AE55" s="79"/>
       <c r="AF55" s="79"/>
       <c r="AG55" s="130" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AH55" s="130"/>
       <c r="AI55" s="130"/>
@@ -9552,7 +9555,7 @@
     </row>
     <row r="58" customHeight="1" spans="1:38">
       <c r="A58" s="77" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B58" s="77"/>
       <c r="C58" s="77"/>
@@ -9595,7 +9598,7 @@
     <row r="59" customHeight="1" spans="1:38">
       <c r="A59" s="78"/>
       <c r="B59" s="79" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C59" s="79"/>
       <c r="D59" s="79"/>
@@ -9638,7 +9641,7 @@
       <c r="A60" s="78"/>
       <c r="B60" s="79"/>
       <c r="C60" s="80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D60" s="81"/>
       <c r="E60" s="81"/>
@@ -9720,7 +9723,7 @@
       <c r="A62" s="78"/>
       <c r="B62" s="79"/>
       <c r="C62" s="78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D62" s="79"/>
       <c r="E62" s="79"/>
@@ -9785,7 +9788,7 @@
       <c r="A64" s="78"/>
       <c r="B64" s="79"/>
       <c r="C64" s="78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D64" s="79"/>
       <c r="E64" s="79"/>
@@ -9796,7 +9799,7 @@
       </c>
       <c r="I64" s="79"/>
       <c r="L64" s="64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N64" s="99"/>
       <c r="O64" s="99"/>
@@ -9804,15 +9807,15 @@
       <c r="Q64" s="99"/>
       <c r="R64" s="99"/>
       <c r="U64" s="64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W64" s="99"/>
       <c r="X64" s="99"/>
       <c r="Y64" s="125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AF64" s="126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG64" s="126"/>
       <c r="AJ64" s="90"/>
@@ -9828,7 +9831,7 @@
       <c r="F65" s="90"/>
       <c r="G65" s="79"/>
       <c r="L65" s="131" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AH65" s="79"/>
       <c r="AI65" s="79"/>
@@ -9840,44 +9843,44 @@
       <c r="A66" s="78"/>
       <c r="B66" s="79"/>
       <c r="C66" s="78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D66" s="79"/>
       <c r="E66" s="79"/>
       <c r="F66" s="90"/>
       <c r="G66" s="79"/>
       <c r="J66" s="132" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K66" s="133"/>
       <c r="L66" s="133"/>
       <c r="M66" s="134"/>
       <c r="N66" s="132" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O66" s="133"/>
       <c r="P66" s="133"/>
       <c r="Q66" s="134"/>
       <c r="R66" s="141" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S66" s="142"/>
       <c r="T66" s="142"/>
       <c r="U66" s="143"/>
       <c r="V66" s="141" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W66" s="142"/>
       <c r="X66" s="142"/>
       <c r="Y66" s="143"/>
       <c r="Z66" s="141" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA66" s="142"/>
       <c r="AB66" s="142"/>
       <c r="AC66" s="143"/>
       <c r="AD66" s="141" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE66" s="142"/>
       <c r="AF66" s="142"/>
@@ -9897,25 +9900,25 @@
       <c r="F67" s="90"/>
       <c r="G67" s="79"/>
       <c r="J67" s="103" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K67" s="104"/>
       <c r="L67" s="104"/>
       <c r="M67" s="105"/>
       <c r="N67" s="106" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O67" s="107"/>
       <c r="P67" s="107"/>
       <c r="Q67" s="117"/>
       <c r="R67" s="118" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="S67" s="119"/>
       <c r="T67" s="119"/>
       <c r="U67" s="120"/>
       <c r="V67" s="106" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="W67" s="107"/>
       <c r="X67" s="107"/>
@@ -9942,32 +9945,32 @@
       <c r="A68" s="78"/>
       <c r="B68" s="79"/>
       <c r="C68" s="78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D68" s="79"/>
       <c r="E68" s="79"/>
       <c r="F68" s="90"/>
       <c r="G68" s="79"/>
       <c r="J68" s="103" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K68" s="104"/>
       <c r="L68" s="104"/>
       <c r="M68" s="105"/>
       <c r="N68" s="106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O68" s="107"/>
       <c r="P68" s="107"/>
       <c r="Q68" s="117"/>
       <c r="R68" s="118" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S68" s="119"/>
       <c r="T68" s="119"/>
       <c r="U68" s="120"/>
       <c r="V68" s="106" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="W68" s="107"/>
       <c r="X68" s="107"/>
@@ -9999,25 +10002,25 @@
       <c r="F69" s="90"/>
       <c r="G69" s="79"/>
       <c r="J69" s="103" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K69" s="104"/>
       <c r="L69" s="104"/>
       <c r="M69" s="105"/>
       <c r="N69" s="106" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O69" s="107"/>
       <c r="P69" s="107"/>
       <c r="Q69" s="117"/>
       <c r="R69" s="118" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S69" s="119"/>
       <c r="T69" s="119"/>
       <c r="U69" s="120"/>
       <c r="V69" s="106" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="W69" s="107"/>
       <c r="X69" s="107"/>
@@ -10049,25 +10052,25 @@
       <c r="F70" s="90"/>
       <c r="G70" s="79"/>
       <c r="J70" s="103" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K70" s="104"/>
       <c r="L70" s="104"/>
       <c r="M70" s="105"/>
       <c r="N70" s="106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O70" s="107"/>
       <c r="P70" s="107"/>
       <c r="Q70" s="117"/>
       <c r="R70" s="118" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S70" s="119"/>
       <c r="T70" s="119"/>
       <c r="U70" s="120"/>
       <c r="V70" s="106" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="W70" s="107"/>
       <c r="X70" s="107"/>
@@ -10099,25 +10102,25 @@
       <c r="F71" s="90"/>
       <c r="G71" s="79"/>
       <c r="J71" s="103" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K71" s="104"/>
       <c r="L71" s="104"/>
       <c r="M71" s="105"/>
       <c r="N71" s="106" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O71" s="107"/>
       <c r="P71" s="107"/>
       <c r="Q71" s="117"/>
       <c r="R71" s="118" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S71" s="119"/>
       <c r="T71" s="119"/>
       <c r="U71" s="120"/>
       <c r="V71" s="106" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="W71" s="107"/>
       <c r="X71" s="107"/>
@@ -10149,25 +10152,25 @@
       <c r="F72" s="90"/>
       <c r="G72" s="79"/>
       <c r="J72" s="103" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K72" s="104"/>
       <c r="L72" s="104"/>
       <c r="M72" s="105"/>
       <c r="N72" s="106" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O72" s="107"/>
       <c r="P72" s="107"/>
       <c r="Q72" s="117"/>
       <c r="R72" s="118" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="S72" s="119"/>
       <c r="T72" s="119"/>
       <c r="U72" s="120"/>
       <c r="V72" s="106" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W72" s="107"/>
       <c r="X72" s="107"/>
@@ -10199,37 +10202,37 @@
       <c r="F73" s="90"/>
       <c r="G73" s="79"/>
       <c r="J73" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K73" s="109"/>
       <c r="L73" s="109"/>
       <c r="M73" s="110"/>
       <c r="N73" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O73" s="109"/>
       <c r="P73" s="109"/>
       <c r="Q73" s="110"/>
       <c r="R73" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S73" s="122"/>
       <c r="T73" s="122"/>
       <c r="U73" s="123"/>
       <c r="V73" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W73" s="109"/>
       <c r="X73" s="109"/>
       <c r="Y73" s="110"/>
       <c r="Z73" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA73" s="109"/>
       <c r="AB73" s="109"/>
       <c r="AC73" s="110"/>
       <c r="AD73" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE73" s="109"/>
       <c r="AF73" s="109"/>
@@ -10249,37 +10252,37 @@
       <c r="F74" s="90"/>
       <c r="G74" s="79"/>
       <c r="J74" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K74" s="109"/>
       <c r="L74" s="109"/>
       <c r="M74" s="110"/>
       <c r="N74" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O74" s="109"/>
       <c r="P74" s="109"/>
       <c r="Q74" s="110"/>
       <c r="R74" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S74" s="122"/>
       <c r="T74" s="122"/>
       <c r="U74" s="123"/>
       <c r="V74" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W74" s="109"/>
       <c r="X74" s="109"/>
       <c r="Y74" s="110"/>
       <c r="Z74" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA74" s="109"/>
       <c r="AB74" s="109"/>
       <c r="AC74" s="110"/>
       <c r="AD74" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE74" s="109"/>
       <c r="AF74" s="109"/>
@@ -10299,37 +10302,37 @@
       <c r="F75" s="90"/>
       <c r="G75" s="79"/>
       <c r="J75" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K75" s="109"/>
       <c r="L75" s="109"/>
       <c r="M75" s="110"/>
       <c r="N75" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O75" s="109"/>
       <c r="P75" s="109"/>
       <c r="Q75" s="110"/>
       <c r="R75" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S75" s="122"/>
       <c r="T75" s="122"/>
       <c r="U75" s="123"/>
       <c r="V75" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W75" s="109"/>
       <c r="X75" s="109"/>
       <c r="Y75" s="110"/>
       <c r="Z75" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA75" s="109"/>
       <c r="AB75" s="109"/>
       <c r="AC75" s="110"/>
       <c r="AD75" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE75" s="109"/>
       <c r="AF75" s="109"/>
@@ -10349,37 +10352,37 @@
       <c r="F76" s="90"/>
       <c r="G76" s="79"/>
       <c r="J76" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K76" s="109"/>
       <c r="L76" s="109"/>
       <c r="M76" s="110"/>
       <c r="N76" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O76" s="109"/>
       <c r="P76" s="109"/>
       <c r="Q76" s="110"/>
       <c r="R76" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S76" s="122"/>
       <c r="T76" s="122"/>
       <c r="U76" s="123"/>
       <c r="V76" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W76" s="109"/>
       <c r="X76" s="109"/>
       <c r="Y76" s="110"/>
       <c r="Z76" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA76" s="109"/>
       <c r="AB76" s="109"/>
       <c r="AC76" s="110"/>
       <c r="AD76" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE76" s="109"/>
       <c r="AF76" s="109"/>
@@ -10399,37 +10402,37 @@
       <c r="F77" s="90"/>
       <c r="G77" s="79"/>
       <c r="J77" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K77" s="109"/>
       <c r="L77" s="109"/>
       <c r="M77" s="110"/>
       <c r="N77" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O77" s="109"/>
       <c r="P77" s="109"/>
       <c r="Q77" s="110"/>
       <c r="R77" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S77" s="122"/>
       <c r="T77" s="122"/>
       <c r="U77" s="123"/>
       <c r="V77" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W77" s="109"/>
       <c r="X77" s="109"/>
       <c r="Y77" s="110"/>
       <c r="Z77" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA77" s="109"/>
       <c r="AB77" s="109"/>
       <c r="AC77" s="110"/>
       <c r="AD77" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE77" s="109"/>
       <c r="AF77" s="109"/>
@@ -10449,37 +10452,37 @@
       <c r="F78" s="90"/>
       <c r="G78" s="79"/>
       <c r="J78" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K78" s="109"/>
       <c r="L78" s="109"/>
       <c r="M78" s="110"/>
       <c r="N78" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O78" s="109"/>
       <c r="P78" s="109"/>
       <c r="Q78" s="110"/>
       <c r="R78" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S78" s="122"/>
       <c r="T78" s="122"/>
       <c r="U78" s="123"/>
       <c r="V78" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W78" s="109"/>
       <c r="X78" s="109"/>
       <c r="Y78" s="110"/>
       <c r="Z78" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA78" s="109"/>
       <c r="AB78" s="109"/>
       <c r="AC78" s="110"/>
       <c r="AD78" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE78" s="109"/>
       <c r="AF78" s="109"/>
@@ -10499,37 +10502,37 @@
       <c r="F79" s="90"/>
       <c r="G79" s="79"/>
       <c r="J79" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K79" s="109"/>
       <c r="L79" s="109"/>
       <c r="M79" s="110"/>
       <c r="N79" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O79" s="109"/>
       <c r="P79" s="109"/>
       <c r="Q79" s="110"/>
       <c r="R79" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S79" s="122"/>
       <c r="T79" s="122"/>
       <c r="U79" s="123"/>
       <c r="V79" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W79" s="109"/>
       <c r="X79" s="109"/>
       <c r="Y79" s="110"/>
       <c r="Z79" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA79" s="109"/>
       <c r="AB79" s="109"/>
       <c r="AC79" s="110"/>
       <c r="AD79" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE79" s="109"/>
       <c r="AF79" s="109"/>
@@ -10574,7 +10577,7 @@
       <c r="AE81" s="79"/>
       <c r="AF81" s="79"/>
       <c r="AG81" s="130" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AH81" s="130"/>
       <c r="AI81" s="130"/>
@@ -10665,7 +10668,7 @@
     <row r="84" customHeight="1" spans="1:38">
       <c r="A84" s="78"/>
       <c r="B84" s="79" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C84" s="79"/>
       <c r="D84" s="79"/>
@@ -10708,7 +10711,7 @@
       <c r="A85" s="78"/>
       <c r="B85" s="79"/>
       <c r="C85" s="80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D85" s="81"/>
       <c r="E85" s="81"/>
@@ -10790,7 +10793,7 @@
       <c r="A87" s="78"/>
       <c r="B87" s="79"/>
       <c r="C87" s="78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D87" s="79"/>
       <c r="E87" s="79"/>
@@ -10855,7 +10858,7 @@
       <c r="A89" s="78"/>
       <c r="B89" s="79"/>
       <c r="C89" s="78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D89" s="79"/>
       <c r="E89" s="79"/>
@@ -10866,7 +10869,7 @@
       </c>
       <c r="I89" s="79"/>
       <c r="L89" s="64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N89" s="99"/>
       <c r="O89" s="99"/>
@@ -10874,15 +10877,15 @@
       <c r="Q89" s="99"/>
       <c r="R89" s="99"/>
       <c r="U89" s="64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W89" s="99"/>
       <c r="X89" s="99"/>
       <c r="Y89" s="125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AF89" s="126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG89" s="126"/>
       <c r="AJ89" s="90"/>
@@ -10907,44 +10910,44 @@
       <c r="A91" s="78"/>
       <c r="B91" s="79"/>
       <c r="C91" s="78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D91" s="79"/>
       <c r="E91" s="79"/>
       <c r="F91" s="90"/>
       <c r="G91" s="79"/>
       <c r="J91" s="100" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K91" s="101"/>
       <c r="L91" s="101"/>
       <c r="M91" s="102"/>
       <c r="N91" s="100" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O91" s="101"/>
       <c r="P91" s="101"/>
       <c r="Q91" s="102"/>
       <c r="R91" s="114" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S91" s="115"/>
       <c r="T91" s="115"/>
       <c r="U91" s="116"/>
       <c r="V91" s="114" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W91" s="115"/>
       <c r="X91" s="115"/>
       <c r="Y91" s="116"/>
       <c r="Z91" s="114" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA91" s="115"/>
       <c r="AB91" s="115"/>
       <c r="AC91" s="116"/>
       <c r="AD91" s="114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE91" s="115"/>
       <c r="AF91" s="115"/>
@@ -10964,25 +10967,25 @@
       <c r="F92" s="90"/>
       <c r="G92" s="79"/>
       <c r="J92" s="135" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K92" s="136"/>
       <c r="L92" s="136"/>
       <c r="M92" s="137"/>
       <c r="N92" s="138" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O92" s="139"/>
       <c r="P92" s="139"/>
       <c r="Q92" s="144"/>
       <c r="R92" s="145" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="S92" s="146"/>
       <c r="T92" s="146"/>
       <c r="U92" s="147"/>
       <c r="V92" s="138" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="W92" s="139"/>
       <c r="X92" s="139"/>
@@ -11009,44 +11012,44 @@
       <c r="A93" s="78"/>
       <c r="B93" s="79"/>
       <c r="C93" s="78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D93" s="79"/>
       <c r="E93" s="79"/>
       <c r="F93" s="90"/>
       <c r="G93" s="79"/>
       <c r="J93" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K93" s="109"/>
       <c r="L93" s="109"/>
       <c r="M93" s="110"/>
       <c r="N93" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O93" s="109"/>
       <c r="P93" s="109"/>
       <c r="Q93" s="110"/>
       <c r="R93" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S93" s="122"/>
       <c r="T93" s="122"/>
       <c r="U93" s="123"/>
       <c r="V93" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W93" s="109"/>
       <c r="X93" s="109"/>
       <c r="Y93" s="110"/>
       <c r="Z93" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA93" s="109"/>
       <c r="AB93" s="109"/>
       <c r="AC93" s="110"/>
       <c r="AD93" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE93" s="109"/>
       <c r="AF93" s="109"/>
@@ -11066,37 +11069,37 @@
       <c r="F94" s="90"/>
       <c r="G94" s="79"/>
       <c r="J94" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K94" s="109"/>
       <c r="L94" s="109"/>
       <c r="M94" s="110"/>
       <c r="N94" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O94" s="109"/>
       <c r="P94" s="109"/>
       <c r="Q94" s="110"/>
       <c r="R94" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S94" s="122"/>
       <c r="T94" s="122"/>
       <c r="U94" s="123"/>
       <c r="V94" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W94" s="109"/>
       <c r="X94" s="109"/>
       <c r="Y94" s="110"/>
       <c r="Z94" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA94" s="109"/>
       <c r="AB94" s="109"/>
       <c r="AC94" s="110"/>
       <c r="AD94" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE94" s="109"/>
       <c r="AF94" s="109"/>
@@ -11261,7 +11264,7 @@
       <c r="AE105" s="79"/>
       <c r="AF105" s="79"/>
       <c r="AG105" s="130" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AH105" s="130"/>
       <c r="AI105" s="130"/>
@@ -11352,7 +11355,7 @@
     <row r="108" customHeight="1" spans="1:38">
       <c r="A108" s="78"/>
       <c r="B108" s="79" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C108" s="79"/>
       <c r="D108" s="79"/>
@@ -11395,7 +11398,7 @@
       <c r="A109" s="78"/>
       <c r="B109" s="79"/>
       <c r="C109" s="80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D109" s="81"/>
       <c r="E109" s="81"/>
@@ -11477,7 +11480,7 @@
       <c r="A111" s="78"/>
       <c r="B111" s="79"/>
       <c r="C111" s="78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D111" s="79"/>
       <c r="E111" s="79"/>
@@ -11542,7 +11545,7 @@
       <c r="A113" s="78"/>
       <c r="B113" s="79"/>
       <c r="C113" s="78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D113" s="79"/>
       <c r="E113" s="79"/>
@@ -11553,25 +11556,25 @@
       </c>
       <c r="I113" s="79"/>
       <c r="L113" s="64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N113" s="99" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O113" s="99"/>
       <c r="P113" s="99"/>
       <c r="Q113" s="99"/>
       <c r="R113" s="99"/>
       <c r="U113" s="64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W113" s="99"/>
       <c r="X113" s="99"/>
       <c r="Y113" s="125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AF113" s="126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG113" s="126"/>
       <c r="AJ113" s="90"/>
@@ -11587,7 +11590,7 @@
       <c r="F114" s="90"/>
       <c r="G114" s="79"/>
       <c r="L114" s="131" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AH114" s="79"/>
       <c r="AI114" s="79"/>
@@ -11599,44 +11602,44 @@
       <c r="A115" s="78"/>
       <c r="B115" s="79"/>
       <c r="C115" s="78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D115" s="79"/>
       <c r="E115" s="79"/>
       <c r="F115" s="90"/>
       <c r="G115" s="79"/>
       <c r="J115" s="132" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K115" s="133"/>
       <c r="L115" s="133"/>
       <c r="M115" s="134"/>
       <c r="N115" s="132" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O115" s="133"/>
       <c r="P115" s="133"/>
       <c r="Q115" s="134"/>
       <c r="R115" s="141" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S115" s="142"/>
       <c r="T115" s="142"/>
       <c r="U115" s="143"/>
       <c r="V115" s="141" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W115" s="142"/>
       <c r="X115" s="142"/>
       <c r="Y115" s="143"/>
       <c r="Z115" s="141" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA115" s="142"/>
       <c r="AB115" s="142"/>
       <c r="AC115" s="143"/>
       <c r="AD115" s="141" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE115" s="142"/>
       <c r="AF115" s="142"/>
@@ -11656,25 +11659,25 @@
       <c r="F116" s="90"/>
       <c r="G116" s="79"/>
       <c r="J116" s="135" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K116" s="136"/>
       <c r="L116" s="136"/>
       <c r="M116" s="137"/>
       <c r="N116" s="138" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O116" s="139"/>
       <c r="P116" s="139"/>
       <c r="Q116" s="144"/>
       <c r="R116" s="145" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="S116" s="146"/>
       <c r="T116" s="146"/>
       <c r="U116" s="147"/>
       <c r="V116" s="138" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="W116" s="139"/>
       <c r="X116" s="139"/>
@@ -11701,44 +11704,44 @@
       <c r="A117" s="78"/>
       <c r="B117" s="79"/>
       <c r="C117" s="78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D117" s="79"/>
       <c r="E117" s="79"/>
       <c r="F117" s="90"/>
       <c r="G117" s="79"/>
       <c r="J117" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K117" s="109"/>
       <c r="L117" s="109"/>
       <c r="M117" s="110"/>
       <c r="N117" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O117" s="109"/>
       <c r="P117" s="109"/>
       <c r="Q117" s="110"/>
       <c r="R117" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S117" s="122"/>
       <c r="T117" s="122"/>
       <c r="U117" s="123"/>
       <c r="V117" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W117" s="109"/>
       <c r="X117" s="109"/>
       <c r="Y117" s="110"/>
       <c r="Z117" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA117" s="109"/>
       <c r="AB117" s="109"/>
       <c r="AC117" s="110"/>
       <c r="AD117" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE117" s="109"/>
       <c r="AF117" s="109"/>
@@ -11758,37 +11761,37 @@
       <c r="F118" s="90"/>
       <c r="G118" s="79"/>
       <c r="J118" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K118" s="109"/>
       <c r="L118" s="109"/>
       <c r="M118" s="110"/>
       <c r="N118" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O118" s="109"/>
       <c r="P118" s="109"/>
       <c r="Q118" s="110"/>
       <c r="R118" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S118" s="122"/>
       <c r="T118" s="122"/>
       <c r="U118" s="123"/>
       <c r="V118" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W118" s="109"/>
       <c r="X118" s="109"/>
       <c r="Y118" s="110"/>
       <c r="Z118" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA118" s="109"/>
       <c r="AB118" s="109"/>
       <c r="AC118" s="110"/>
       <c r="AD118" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE118" s="109"/>
       <c r="AF118" s="109"/>
@@ -12133,7 +12136,7 @@
       <c r="AE129" s="79"/>
       <c r="AF129" s="79"/>
       <c r="AG129" s="130" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AH129" s="130"/>
       <c r="AI129" s="130"/>
@@ -12224,7 +12227,7 @@
     <row r="132" customHeight="1" spans="1:38">
       <c r="A132" s="78"/>
       <c r="B132" s="79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C132" s="79"/>
       <c r="D132" s="79"/>
@@ -12267,7 +12270,7 @@
       <c r="A133" s="78"/>
       <c r="B133" s="79"/>
       <c r="C133" s="80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D133" s="81"/>
       <c r="E133" s="81"/>
@@ -12349,7 +12352,7 @@
       <c r="A135" s="78"/>
       <c r="B135" s="79"/>
       <c r="C135" s="78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D135" s="79"/>
       <c r="E135" s="79"/>
@@ -12414,7 +12417,7 @@
       <c r="A137" s="78"/>
       <c r="B137" s="79"/>
       <c r="C137" s="78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D137" s="79"/>
       <c r="E137" s="79"/>
@@ -12425,7 +12428,7 @@
       </c>
       <c r="I137" s="79"/>
       <c r="L137" s="64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N137" s="99"/>
       <c r="O137" s="99"/>
@@ -12433,17 +12436,17 @@
       <c r="Q137" s="99"/>
       <c r="R137" s="99"/>
       <c r="U137" s="64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W137" s="99" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="X137" s="99"/>
       <c r="Y137" s="125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AF137" s="126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG137" s="126"/>
       <c r="AJ137" s="90"/>
@@ -12469,44 +12472,44 @@
       <c r="A139" s="78"/>
       <c r="B139" s="79"/>
       <c r="C139" s="78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D139" s="79"/>
       <c r="E139" s="79"/>
       <c r="F139" s="90"/>
       <c r="G139" s="79"/>
       <c r="J139" s="100" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K139" s="101"/>
       <c r="L139" s="101"/>
       <c r="M139" s="102"/>
       <c r="N139" s="100" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O139" s="101"/>
       <c r="P139" s="101"/>
       <c r="Q139" s="102"/>
       <c r="R139" s="114" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S139" s="115"/>
       <c r="T139" s="115"/>
       <c r="U139" s="116"/>
       <c r="V139" s="114" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W139" s="115"/>
       <c r="X139" s="115"/>
       <c r="Y139" s="116"/>
       <c r="Z139" s="114" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA139" s="115"/>
       <c r="AB139" s="115"/>
       <c r="AC139" s="116"/>
       <c r="AD139" s="114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE139" s="115"/>
       <c r="AF139" s="115"/>
@@ -12526,25 +12529,25 @@
       <c r="F140" s="90"/>
       <c r="G140" s="79"/>
       <c r="J140" s="103" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K140" s="104"/>
       <c r="L140" s="104"/>
       <c r="M140" s="105"/>
       <c r="N140" s="106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O140" s="107"/>
       <c r="P140" s="107"/>
       <c r="Q140" s="117"/>
       <c r="R140" s="118" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S140" s="119"/>
       <c r="T140" s="119"/>
       <c r="U140" s="120"/>
       <c r="V140" s="106" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="W140" s="107"/>
       <c r="X140" s="107"/>
@@ -12571,44 +12574,44 @@
       <c r="A141" s="78"/>
       <c r="B141" s="79"/>
       <c r="C141" s="78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D141" s="79"/>
       <c r="E141" s="79"/>
       <c r="F141" s="90"/>
       <c r="G141" s="79"/>
       <c r="J141" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K141" s="109"/>
       <c r="L141" s="109"/>
       <c r="M141" s="110"/>
       <c r="N141" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O141" s="109"/>
       <c r="P141" s="109"/>
       <c r="Q141" s="110"/>
       <c r="R141" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S141" s="122"/>
       <c r="T141" s="122"/>
       <c r="U141" s="123"/>
       <c r="V141" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W141" s="109"/>
       <c r="X141" s="109"/>
       <c r="Y141" s="110"/>
       <c r="Z141" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA141" s="109"/>
       <c r="AB141" s="109"/>
       <c r="AC141" s="110"/>
       <c r="AD141" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE141" s="109"/>
       <c r="AF141" s="109"/>
@@ -12628,37 +12631,37 @@
       <c r="F142" s="90"/>
       <c r="G142" s="79"/>
       <c r="J142" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K142" s="109"/>
       <c r="L142" s="109"/>
       <c r="M142" s="110"/>
       <c r="N142" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O142" s="109"/>
       <c r="P142" s="109"/>
       <c r="Q142" s="110"/>
       <c r="R142" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S142" s="122"/>
       <c r="T142" s="122"/>
       <c r="U142" s="123"/>
       <c r="V142" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W142" s="109"/>
       <c r="X142" s="109"/>
       <c r="Y142" s="110"/>
       <c r="Z142" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA142" s="109"/>
       <c r="AB142" s="109"/>
       <c r="AC142" s="110"/>
       <c r="AD142" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE142" s="109"/>
       <c r="AF142" s="109"/>
@@ -12678,37 +12681,37 @@
       <c r="F143" s="90"/>
       <c r="G143" s="79"/>
       <c r="J143" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K143" s="109"/>
       <c r="L143" s="109"/>
       <c r="M143" s="110"/>
       <c r="N143" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O143" s="109"/>
       <c r="P143" s="109"/>
       <c r="Q143" s="110"/>
       <c r="R143" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S143" s="122"/>
       <c r="T143" s="122"/>
       <c r="U143" s="123"/>
       <c r="V143" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W143" s="109"/>
       <c r="X143" s="109"/>
       <c r="Y143" s="110"/>
       <c r="Z143" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA143" s="109"/>
       <c r="AB143" s="109"/>
       <c r="AC143" s="110"/>
       <c r="AD143" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE143" s="109"/>
       <c r="AF143" s="109"/>
@@ -12859,7 +12862,7 @@
       <c r="AE153" s="79"/>
       <c r="AF153" s="79"/>
       <c r="AG153" s="130" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AH153" s="130"/>
       <c r="AI153" s="130"/>
@@ -12950,7 +12953,7 @@
     <row r="156" customHeight="1" spans="1:38">
       <c r="A156" s="78"/>
       <c r="B156" s="79" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C156" s="79"/>
       <c r="D156" s="79"/>
@@ -12993,7 +12996,7 @@
       <c r="A157" s="78"/>
       <c r="B157" s="79"/>
       <c r="C157" s="80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D157" s="81"/>
       <c r="E157" s="81"/>
@@ -13075,7 +13078,7 @@
       <c r="A159" s="78"/>
       <c r="B159" s="79"/>
       <c r="C159" s="78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D159" s="79"/>
       <c r="E159" s="79"/>
@@ -13140,7 +13143,7 @@
       <c r="A161" s="78"/>
       <c r="B161" s="79"/>
       <c r="C161" s="78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D161" s="79"/>
       <c r="E161" s="79"/>
@@ -13151,7 +13154,7 @@
       </c>
       <c r="I161" s="79"/>
       <c r="L161" s="64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N161" s="99"/>
       <c r="O161" s="99"/>
@@ -13159,17 +13162,17 @@
       <c r="Q161" s="99"/>
       <c r="R161" s="99"/>
       <c r="U161" s="64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W161" s="99" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="X161" s="99"/>
       <c r="Y161" s="125" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AF161" s="126" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG161" s="126"/>
       <c r="AJ161" s="90"/>
@@ -13185,7 +13188,7 @@
       <c r="F162" s="90"/>
       <c r="G162" s="79"/>
       <c r="L162" s="131" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AH162" s="79"/>
       <c r="AI162" s="79"/>
@@ -13197,44 +13200,44 @@
       <c r="A163" s="78"/>
       <c r="B163" s="79"/>
       <c r="C163" s="78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D163" s="79"/>
       <c r="E163" s="79"/>
       <c r="F163" s="90"/>
       <c r="G163" s="79"/>
       <c r="J163" s="100" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K163" s="101"/>
       <c r="L163" s="101"/>
       <c r="M163" s="102"/>
       <c r="N163" s="100" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O163" s="101"/>
       <c r="P163" s="101"/>
       <c r="Q163" s="102"/>
       <c r="R163" s="114" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S163" s="115"/>
       <c r="T163" s="115"/>
       <c r="U163" s="116"/>
       <c r="V163" s="114" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="W163" s="115"/>
       <c r="X163" s="115"/>
       <c r="Y163" s="116"/>
       <c r="Z163" s="114" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA163" s="115"/>
       <c r="AB163" s="115"/>
       <c r="AC163" s="116"/>
       <c r="AD163" s="114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AE163" s="115"/>
       <c r="AF163" s="115"/>
@@ -13254,25 +13257,25 @@
       <c r="F164" s="90"/>
       <c r="G164" s="79"/>
       <c r="J164" s="103" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K164" s="104"/>
       <c r="L164" s="104"/>
       <c r="M164" s="105"/>
       <c r="N164" s="106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O164" s="107"/>
       <c r="P164" s="107"/>
       <c r="Q164" s="117"/>
       <c r="R164" s="118" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S164" s="119"/>
       <c r="T164" s="119"/>
       <c r="U164" s="120"/>
       <c r="V164" s="106" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="W164" s="107"/>
       <c r="X164" s="107"/>
@@ -13299,44 +13302,44 @@
       <c r="A165" s="78"/>
       <c r="B165" s="79"/>
       <c r="C165" s="78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D165" s="79"/>
       <c r="E165" s="79"/>
       <c r="F165" s="90"/>
       <c r="G165" s="79"/>
       <c r="J165" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K165" s="109"/>
       <c r="L165" s="109"/>
       <c r="M165" s="110"/>
       <c r="N165" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O165" s="109"/>
       <c r="P165" s="109"/>
       <c r="Q165" s="110"/>
       <c r="R165" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S165" s="122"/>
       <c r="T165" s="122"/>
       <c r="U165" s="123"/>
       <c r="V165" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W165" s="109"/>
       <c r="X165" s="109"/>
       <c r="Y165" s="110"/>
       <c r="Z165" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA165" s="109"/>
       <c r="AB165" s="109"/>
       <c r="AC165" s="110"/>
       <c r="AD165" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE165" s="109"/>
       <c r="AF165" s="109"/>
@@ -13356,37 +13359,37 @@
       <c r="F166" s="90"/>
       <c r="G166" s="79"/>
       <c r="J166" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K166" s="109"/>
       <c r="L166" s="109"/>
       <c r="M166" s="110"/>
       <c r="N166" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O166" s="109"/>
       <c r="P166" s="109"/>
       <c r="Q166" s="110"/>
       <c r="R166" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S166" s="122"/>
       <c r="T166" s="122"/>
       <c r="U166" s="123"/>
       <c r="V166" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W166" s="109"/>
       <c r="X166" s="109"/>
       <c r="Y166" s="110"/>
       <c r="Z166" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA166" s="109"/>
       <c r="AB166" s="109"/>
       <c r="AC166" s="110"/>
       <c r="AD166" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE166" s="109"/>
       <c r="AF166" s="109"/>
@@ -13406,37 +13409,37 @@
       <c r="F167" s="90"/>
       <c r="G167" s="79"/>
       <c r="J167" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K167" s="109"/>
       <c r="L167" s="109"/>
       <c r="M167" s="110"/>
       <c r="N167" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O167" s="109"/>
       <c r="P167" s="109"/>
       <c r="Q167" s="110"/>
       <c r="R167" s="121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S167" s="122"/>
       <c r="T167" s="122"/>
       <c r="U167" s="123"/>
       <c r="V167" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="W167" s="109"/>
       <c r="X167" s="109"/>
       <c r="Y167" s="110"/>
       <c r="Z167" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA167" s="109"/>
       <c r="AB167" s="109"/>
       <c r="AC167" s="110"/>
       <c r="AD167" s="108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AE167" s="109"/>
       <c r="AF167" s="109"/>
@@ -13587,7 +13590,7 @@
       <c r="AE177" s="79"/>
       <c r="AF177" s="79"/>
       <c r="AG177" s="130" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AH177" s="130"/>
       <c r="AI177" s="130"/>
@@ -13677,7 +13680,7 @@
     </row>
     <row r="180" customHeight="1" spans="1:38">
       <c r="A180" s="77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B180" s="77"/>
       <c r="C180" s="77"/>
@@ -13720,7 +13723,7 @@
     <row r="181" customHeight="1" spans="1:38">
       <c r="A181" s="78"/>
       <c r="B181" s="79" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C181" s="79"/>
       <c r="D181" s="79"/>
@@ -13762,7 +13765,7 @@
     <row r="182" customHeight="1" spans="1:38">
       <c r="A182" s="78"/>
       <c r="B182" s="79" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C182" s="79"/>
       <c r="D182" s="79"/>
@@ -13804,7 +13807,7 @@
     <row r="183" customHeight="1" spans="1:38">
       <c r="A183" s="78"/>
       <c r="B183" s="79" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C183" s="79"/>
       <c r="D183" s="79"/>
@@ -13847,7 +13850,7 @@
       <c r="A184" s="78"/>
       <c r="B184" s="79"/>
       <c r="C184" s="80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D184" s="81"/>
       <c r="E184" s="81"/>
@@ -13929,13 +13932,13 @@
       <c r="A186" s="79"/>
       <c r="B186" s="79"/>
       <c r="C186" s="78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D186" s="79"/>
       <c r="E186" s="79"/>
       <c r="F186" s="90"/>
       <c r="G186" s="79" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H186" s="79"/>
       <c r="I186" s="79"/>
@@ -14001,7 +14004,7 @@
       <c r="A188" s="79"/>
       <c r="B188" s="79"/>
       <c r="C188" s="78" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D188" s="79"/>
       <c r="E188" s="79"/>
@@ -14009,7 +14012,7 @@
       <c r="G188" s="79"/>
       <c r="H188" s="91"/>
       <c r="I188" s="79" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M188" s="125"/>
       <c r="N188" s="125"/>
@@ -14039,13 +14042,13 @@
       <c r="F189" s="90"/>
       <c r="G189" s="79"/>
       <c r="I189" s="149" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J189" s="150"/>
       <c r="K189" s="150"/>
       <c r="L189" s="151"/>
       <c r="M189" s="152" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N189" s="152"/>
       <c r="O189" s="152"/>
@@ -14076,20 +14079,20 @@
       <c r="A190" s="79"/>
       <c r="B190" s="79"/>
       <c r="C190" s="78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D190" s="79"/>
       <c r="E190" s="79"/>
       <c r="F190" s="90"/>
       <c r="G190" s="79"/>
       <c r="I190" s="149" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J190" s="150"/>
       <c r="K190" s="150"/>
       <c r="L190" s="151"/>
       <c r="M190" s="152" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N190" s="152"/>
       <c r="O190" s="152"/>
@@ -14126,13 +14129,13 @@
       <c r="F191" s="90"/>
       <c r="G191" s="79"/>
       <c r="I191" s="149" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J191" s="150"/>
       <c r="K191" s="150"/>
       <c r="L191" s="151"/>
       <c r="M191" s="152" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N191" s="152"/>
       <c r="O191" s="152"/>
@@ -14164,20 +14167,20 @@
       <c r="A192" s="79"/>
       <c r="B192" s="79"/>
       <c r="C192" s="78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D192" s="79"/>
       <c r="E192" s="79"/>
       <c r="F192" s="90"/>
       <c r="G192" s="79"/>
       <c r="I192" s="149" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J192" s="150"/>
       <c r="K192" s="150"/>
       <c r="L192" s="151"/>
       <c r="M192" s="152" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N192" s="152"/>
       <c r="O192" s="152"/>
@@ -14214,13 +14217,13 @@
       <c r="F193" s="90"/>
       <c r="G193" s="79"/>
       <c r="I193" s="149" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J193" s="150"/>
       <c r="K193" s="150"/>
       <c r="L193" s="151"/>
       <c r="M193" s="152" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N193" s="152"/>
       <c r="O193" s="152"/>
@@ -14257,13 +14260,13 @@
       <c r="F194" s="90"/>
       <c r="G194" s="79"/>
       <c r="I194" s="149" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J194" s="150"/>
       <c r="K194" s="150"/>
       <c r="L194" s="151"/>
       <c r="M194" s="106" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N194" s="107"/>
       <c r="O194" s="107"/>
@@ -14300,7 +14303,7 @@
       <c r="F195" s="90"/>
       <c r="G195" s="79"/>
       <c r="I195" s="149" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J195" s="150"/>
       <c r="K195" s="150"/>
@@ -14343,7 +14346,7 @@
       <c r="F196" s="90"/>
       <c r="G196" s="79"/>
       <c r="I196" s="149" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J196" s="150"/>
       <c r="K196" s="150"/>
@@ -14386,7 +14389,7 @@
       <c r="F197" s="90"/>
       <c r="G197" s="79"/>
       <c r="I197" s="157" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J197" s="157"/>
       <c r="K197" s="157"/>
@@ -14457,7 +14460,7 @@
       <c r="F200" s="90"/>
       <c r="G200" s="79"/>
       <c r="I200" s="158" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J200" s="158"/>
       <c r="K200" s="159"/>
@@ -14481,7 +14484,7 @@
       <c r="AC200" s="159"/>
       <c r="AD200" s="159"/>
       <c r="AE200" s="164" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF200" s="165"/>
       <c r="AI200" s="79"/>
@@ -14626,7 +14629,7 @@
     </row>
     <row r="205" customHeight="1" spans="1:38">
       <c r="A205" s="77" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B205" s="77"/>
       <c r="C205" s="77"/>
@@ -14669,7 +14672,7 @@
     <row r="206" customHeight="1" spans="1:38">
       <c r="A206" s="78"/>
       <c r="B206" s="79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C206" s="79"/>
       <c r="D206" s="79"/>
@@ -14711,7 +14714,7 @@
     <row r="207" customHeight="1" spans="1:38">
       <c r="A207" s="78"/>
       <c r="B207" s="79" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C207" s="79"/>
       <c r="D207" s="79"/>
@@ -14754,7 +14757,7 @@
       <c r="A208" s="78"/>
       <c r="B208" s="79"/>
       <c r="C208" s="79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D208" s="79"/>
       <c r="E208" s="79"/>
@@ -14796,7 +14799,7 @@
       <c r="A209" s="78"/>
       <c r="B209" s="79"/>
       <c r="C209" s="79" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D209" s="79"/>
       <c r="E209" s="79"/>
@@ -14838,7 +14841,7 @@
       <c r="A210" s="78"/>
       <c r="B210" s="79"/>
       <c r="C210" s="79" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D210" s="79"/>
       <c r="E210" s="79"/>
@@ -14880,7 +14883,7 @@
       <c r="A211" s="78"/>
       <c r="B211" s="79"/>
       <c r="C211" s="79" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D211" s="79"/>
       <c r="E211" s="79"/>
@@ -14922,7 +14925,7 @@
       <c r="A212" s="78"/>
       <c r="B212" s="79"/>
       <c r="C212" s="80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D212" s="81"/>
       <c r="E212" s="81"/>
@@ -15004,13 +15007,13 @@
       <c r="A214" s="79"/>
       <c r="B214" s="79"/>
       <c r="C214" s="78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D214" s="79"/>
       <c r="E214" s="79"/>
       <c r="F214" s="90"/>
       <c r="G214" s="79" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H214" s="79"/>
       <c r="I214" s="79"/>
@@ -15076,7 +15079,7 @@
       <c r="A216" s="79"/>
       <c r="B216" s="79"/>
       <c r="C216" s="78" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D216" s="79"/>
       <c r="E216" s="79"/>
@@ -15084,7 +15087,7 @@
       <c r="G216" s="79"/>
       <c r="H216" s="91"/>
       <c r="I216" s="79" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M216" s="160"/>
       <c r="N216" s="160"/>
@@ -15117,13 +15120,13 @@
       <c r="F217" s="90"/>
       <c r="G217" s="79"/>
       <c r="I217" s="149" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J217" s="150"/>
       <c r="K217" s="150"/>
       <c r="L217" s="151"/>
       <c r="M217" s="161" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N217" s="161"/>
       <c r="O217" s="161"/>
@@ -15154,20 +15157,20 @@
       <c r="A218" s="79"/>
       <c r="B218" s="79"/>
       <c r="C218" s="78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D218" s="79"/>
       <c r="E218" s="79"/>
       <c r="F218" s="90"/>
       <c r="G218" s="79"/>
       <c r="I218" s="149" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J218" s="150"/>
       <c r="K218" s="150"/>
       <c r="L218" s="151"/>
       <c r="M218" s="161" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N218" s="161"/>
       <c r="O218" s="161"/>
@@ -15204,13 +15207,13 @@
       <c r="F219" s="90"/>
       <c r="G219" s="79"/>
       <c r="I219" s="149" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J219" s="150"/>
       <c r="K219" s="150"/>
       <c r="L219" s="151"/>
       <c r="M219" s="161" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N219" s="161"/>
       <c r="O219" s="161"/>
@@ -15242,20 +15245,20 @@
       <c r="A220" s="79"/>
       <c r="B220" s="79"/>
       <c r="C220" s="78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D220" s="79"/>
       <c r="E220" s="79"/>
       <c r="F220" s="90"/>
       <c r="G220" s="79"/>
       <c r="I220" s="149" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J220" s="150"/>
       <c r="K220" s="150"/>
       <c r="L220" s="151"/>
       <c r="M220" s="161" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N220" s="161"/>
       <c r="O220" s="161"/>
@@ -15292,13 +15295,13 @@
       <c r="F221" s="90"/>
       <c r="G221" s="79"/>
       <c r="I221" s="149" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J221" s="150"/>
       <c r="K221" s="150"/>
       <c r="L221" s="151"/>
       <c r="M221" s="161" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N221" s="161"/>
       <c r="O221" s="161"/>
@@ -15335,13 +15338,13 @@
       <c r="F222" s="90"/>
       <c r="G222" s="79"/>
       <c r="I222" s="149" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J222" s="150"/>
       <c r="K222" s="150"/>
       <c r="L222" s="151"/>
       <c r="M222" s="106" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N222" s="107"/>
       <c r="O222" s="107"/>
@@ -15378,7 +15381,7 @@
       <c r="F223" s="90"/>
       <c r="G223" s="79"/>
       <c r="I223" s="149" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J223" s="150"/>
       <c r="K223" s="150"/>
@@ -15421,7 +15424,7 @@
       <c r="F224" s="90"/>
       <c r="G224" s="79"/>
       <c r="I224" s="149" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J224" s="150"/>
       <c r="K224" s="150"/>
@@ -15464,7 +15467,7 @@
       <c r="F225" s="90"/>
       <c r="G225" s="79"/>
       <c r="I225" s="157" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J225" s="157"/>
       <c r="K225" s="157"/>
@@ -15535,7 +15538,7 @@
       <c r="F228" s="90"/>
       <c r="G228" s="79"/>
       <c r="I228" s="158" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J228" s="158"/>
       <c r="K228" s="159"/>
@@ -15556,12 +15559,12 @@
       <c r="Z228" s="159"/>
       <c r="AA228" s="159"/>
       <c r="AB228" s="166" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC228" s="167"/>
       <c r="AD228" s="159"/>
       <c r="AE228" s="164" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF228" s="165"/>
       <c r="AI228" s="79"/>
@@ -15732,7 +15735,7 @@
     </row>
     <row r="235" customHeight="1" spans="1:38">
       <c r="A235" s="77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B235" s="77"/>
       <c r="C235" s="77"/>
@@ -15776,7 +15779,7 @@
       <c r="A236" s="78"/>
       <c r="B236" s="79"/>
       <c r="C236" s="79" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D236" s="79"/>
       <c r="E236" s="79"/>
@@ -15818,7 +15821,7 @@
       <c r="A237" s="78"/>
       <c r="B237" s="79"/>
       <c r="C237" s="79" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D237" s="79"/>
       <c r="E237" s="79"/>
@@ -15860,7 +15863,7 @@
       <c r="A238" s="78"/>
       <c r="B238" s="79"/>
       <c r="C238" s="80" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D238" s="81"/>
       <c r="E238" s="81"/>
@@ -15942,13 +15945,13 @@
       <c r="A240" s="79"/>
       <c r="B240" s="79"/>
       <c r="C240" s="78" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D240" s="79"/>
       <c r="E240" s="79"/>
       <c r="F240" s="90"/>
       <c r="G240" s="79" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H240" s="79"/>
       <c r="I240" s="79"/>
@@ -16014,7 +16017,7 @@
       <c r="A242" s="79"/>
       <c r="B242" s="79"/>
       <c r="C242" s="78" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D242" s="79"/>
       <c r="E242" s="79"/>
@@ -16022,7 +16025,7 @@
       <c r="G242" s="79"/>
       <c r="H242" s="91"/>
       <c r="I242" s="79" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M242" s="125"/>
       <c r="N242" s="125"/>
@@ -16052,13 +16055,13 @@
       <c r="F243" s="90"/>
       <c r="G243" s="79"/>
       <c r="I243" s="149" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J243" s="150"/>
       <c r="K243" s="150"/>
       <c r="L243" s="151"/>
       <c r="M243" s="152" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N243" s="152"/>
       <c r="O243" s="152"/>
@@ -16089,20 +16092,20 @@
       <c r="A244" s="79"/>
       <c r="B244" s="79"/>
       <c r="C244" s="78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D244" s="79"/>
       <c r="E244" s="79"/>
       <c r="F244" s="90"/>
       <c r="G244" s="79"/>
       <c r="I244" s="149" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J244" s="150"/>
       <c r="K244" s="150"/>
       <c r="L244" s="151"/>
       <c r="M244" s="152" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N244" s="152"/>
       <c r="O244" s="152"/>
@@ -16139,13 +16142,13 @@
       <c r="F245" s="90"/>
       <c r="G245" s="79"/>
       <c r="I245" s="149" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J245" s="150"/>
       <c r="K245" s="150"/>
       <c r="L245" s="151"/>
       <c r="M245" s="152" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N245" s="152"/>
       <c r="O245" s="152"/>
@@ -16177,20 +16180,20 @@
       <c r="A246" s="79"/>
       <c r="B246" s="79"/>
       <c r="C246" s="78" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D246" s="79"/>
       <c r="E246" s="79"/>
       <c r="F246" s="90"/>
       <c r="G246" s="79"/>
       <c r="I246" s="149" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J246" s="150"/>
       <c r="K246" s="150"/>
       <c r="L246" s="151"/>
       <c r="M246" s="152" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N246" s="152"/>
       <c r="O246" s="152"/>
@@ -16227,13 +16230,13 @@
       <c r="F247" s="90"/>
       <c r="G247" s="79"/>
       <c r="I247" s="149" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J247" s="150"/>
       <c r="K247" s="150"/>
       <c r="L247" s="151"/>
       <c r="M247" s="152" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N247" s="152"/>
       <c r="O247" s="152"/>
@@ -16270,13 +16273,13 @@
       <c r="F248" s="90"/>
       <c r="G248" s="79"/>
       <c r="I248" s="149" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J248" s="150"/>
       <c r="K248" s="150"/>
       <c r="L248" s="151"/>
       <c r="M248" s="106" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N248" s="107"/>
       <c r="O248" s="107"/>
@@ -16313,7 +16316,7 @@
       <c r="F249" s="90"/>
       <c r="G249" s="79"/>
       <c r="I249" s="149" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J249" s="150"/>
       <c r="K249" s="150"/>
@@ -16356,7 +16359,7 @@
       <c r="F250" s="90"/>
       <c r="G250" s="79"/>
       <c r="I250" s="149" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J250" s="150"/>
       <c r="K250" s="150"/>
@@ -16399,7 +16402,7 @@
       <c r="F251" s="90"/>
       <c r="G251" s="79"/>
       <c r="I251" s="157" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J251" s="157"/>
       <c r="K251" s="157"/>
@@ -16455,7 +16458,7 @@
       <c r="F253" s="90"/>
       <c r="G253" s="79"/>
       <c r="I253" s="158" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J253" s="158"/>
       <c r="K253" s="159"/>
@@ -16479,7 +16482,7 @@
       <c r="AC253" s="159"/>
       <c r="AD253" s="159"/>
       <c r="AE253" s="164" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF253" s="165"/>
       <c r="AI253" s="79"/>
@@ -17106,7 +17109,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:38">
       <c r="A1" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -17348,7 +17351,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:38">
       <c r="A6" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -17357,7 +17360,7 @@
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I6" s="34"/>
       <c r="J6" s="34"/>
@@ -17383,7 +17386,7 @@
       <c r="AD6" s="34"/>
       <c r="AE6" s="48"/>
       <c r="AF6" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG6" s="13"/>
       <c r="AH6" s="13"/>
@@ -17434,7 +17437,7 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A8" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -17444,7 +17447,7 @@
       <c r="G8" s="19"/>
       <c r="H8" s="20"/>
       <c r="I8" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AE8" s="51"/>
       <c r="AF8" s="23"/>
@@ -17457,7 +17460,7 @@
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A9" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -17467,7 +17470,7 @@
       <c r="G9" s="19"/>
       <c r="H9" s="20"/>
       <c r="J9" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AE9" s="51"/>
       <c r="AF9" s="23"/>
@@ -17480,7 +17483,7 @@
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A10" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -17490,7 +17493,7 @@
       <c r="G10" s="19"/>
       <c r="H10" s="20"/>
       <c r="K10" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AE10" s="51"/>
       <c r="AF10" s="23"/>
@@ -17511,7 +17514,7 @@
       <c r="G11" s="19"/>
       <c r="H11" s="20"/>
       <c r="K11" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AE11" s="51"/>
       <c r="AF11" s="23"/>
@@ -17550,11 +17553,11 @@
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
       <c r="J13" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AE13" s="51"/>
       <c r="AF13" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG13" s="19"/>
       <c r="AH13" s="19"/>
@@ -17573,7 +17576,7 @@
       <c r="G14" s="19"/>
       <c r="H14" s="20"/>
       <c r="K14" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AE14" s="51"/>
       <c r="AF14" s="23"/>
@@ -17594,7 +17597,7 @@
       <c r="G15" s="19"/>
       <c r="H15" s="20"/>
       <c r="K15" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AE15" s="51"/>
       <c r="AF15" s="23"/>
@@ -17625,7 +17628,7 @@
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A17" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -17635,7 +17638,7 @@
       <c r="G17" s="21"/>
       <c r="H17" s="20"/>
       <c r="J17" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AE17" s="51"/>
       <c r="AF17" s="23"/>
@@ -17674,7 +17677,7 @@
       <c r="G19" s="19"/>
       <c r="H19" s="20"/>
       <c r="J19" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AE19" s="51"/>
       <c r="AF19" s="23"/>
@@ -17695,7 +17698,7 @@
       <c r="G20" s="19"/>
       <c r="H20" s="20"/>
       <c r="K20" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AE20" s="51"/>
       <c r="AF20" s="23"/>
@@ -17716,7 +17719,7 @@
       <c r="G21" s="19"/>
       <c r="H21" s="20"/>
       <c r="K21" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AE21" s="51"/>
       <c r="AF21" s="23"/>
@@ -17755,11 +17758,11 @@
       <c r="G23" s="23"/>
       <c r="H23" s="20"/>
       <c r="J23" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AE23" s="51"/>
       <c r="AF23" s="19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG23" s="23"/>
       <c r="AH23" s="23"/>
@@ -17788,7 +17791,7 @@
     </row>
     <row r="25" customHeight="1" spans="1:38">
       <c r="A25" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
@@ -17798,7 +17801,7 @@
       <c r="G25" s="19"/>
       <c r="H25" s="24"/>
       <c r="I25" s="25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J25" s="36"/>
       <c r="K25" s="25"/>
@@ -17832,7 +17835,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A26" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -17842,7 +17845,7 @@
       <c r="G26" s="19"/>
       <c r="H26" s="20"/>
       <c r="J26" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AE26" s="51"/>
       <c r="AF26" s="23"/>
@@ -17856,7 +17859,7 @@
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A27" s="18"/>
       <c r="B27" s="19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -17865,7 +17868,7 @@
       <c r="G27" s="19"/>
       <c r="H27" s="20"/>
       <c r="K27" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AE27" s="51"/>
       <c r="AF27" s="23"/>
@@ -17879,7 +17882,7 @@
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A28" s="18"/>
       <c r="B28" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -17888,7 +17891,7 @@
       <c r="G28" s="19"/>
       <c r="H28" s="20"/>
       <c r="K28" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AE28" s="51"/>
       <c r="AF28" s="23"/>
@@ -17902,7 +17905,7 @@
     <row r="29" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A29" s="22"/>
       <c r="B29" s="19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
@@ -17931,7 +17934,7 @@
       <c r="H30" s="24"/>
       <c r="I30" s="36"/>
       <c r="J30" s="25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
@@ -17973,7 +17976,7 @@
       <c r="I31" s="25"/>
       <c r="J31" s="25"/>
       <c r="K31" s="25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L31" s="25"/>
       <c r="M31" s="25"/>
@@ -18015,7 +18018,7 @@
       <c r="I32" s="25"/>
       <c r="J32" s="25"/>
       <c r="K32" s="25" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L32" s="25"/>
       <c r="M32" s="25"/>
@@ -18097,7 +18100,7 @@
       <c r="I34" s="25"/>
       <c r="J34" s="25"/>
       <c r="K34" s="25" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
@@ -18139,14 +18142,14 @@
       <c r="I35" s="25"/>
       <c r="J35" s="25"/>
       <c r="K35" s="29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L35" s="29"/>
       <c r="M35" s="29"/>
       <c r="N35" s="29"/>
       <c r="O35" s="29"/>
       <c r="P35" s="37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q35" s="45"/>
       <c r="R35" s="45"/>
@@ -18159,7 +18162,7 @@
       <c r="Y35" s="45"/>
       <c r="Z35" s="53"/>
       <c r="AA35" s="29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AB35" s="29"/>
       <c r="AC35" s="29"/>
@@ -18192,7 +18195,7 @@
       <c r="N36" s="39"/>
       <c r="O36" s="39"/>
       <c r="P36" s="40" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q36" s="46"/>
       <c r="R36" s="46"/>
@@ -18205,7 +18208,7 @@
       <c r="Y36" s="46"/>
       <c r="Z36" s="54"/>
       <c r="AA36" s="44" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AB36" s="44"/>
       <c r="AC36" s="44"/>
@@ -18231,14 +18234,14 @@
       <c r="I37" s="25"/>
       <c r="J37" s="25"/>
       <c r="K37" s="39" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L37" s="39"/>
       <c r="M37" s="39"/>
       <c r="N37" s="39"/>
       <c r="O37" s="39"/>
       <c r="P37" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q37" s="46"/>
       <c r="R37" s="46"/>
@@ -18251,7 +18254,7 @@
       <c r="Y37" s="46"/>
       <c r="Z37" s="54"/>
       <c r="AA37" s="44" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AB37" s="44"/>
       <c r="AC37" s="44"/>
@@ -18277,14 +18280,14 @@
       <c r="I38" s="25"/>
       <c r="J38" s="25"/>
       <c r="K38" s="39" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L38" s="39"/>
       <c r="M38" s="39"/>
       <c r="N38" s="39"/>
       <c r="O38" s="39"/>
       <c r="P38" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q38" s="46"/>
       <c r="R38" s="46"/>
@@ -18297,7 +18300,7 @@
       <c r="Y38" s="46"/>
       <c r="Z38" s="54"/>
       <c r="AA38" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB38" s="44"/>
       <c r="AC38" s="44"/>
@@ -18323,14 +18326,14 @@
       <c r="I39" s="25"/>
       <c r="J39" s="25"/>
       <c r="K39" s="39" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
       <c r="N39" s="39"/>
       <c r="O39" s="39"/>
       <c r="P39" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q39" s="46"/>
       <c r="R39" s="46"/>
@@ -18343,7 +18346,7 @@
       <c r="Y39" s="46"/>
       <c r="Z39" s="54"/>
       <c r="AA39" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB39" s="44"/>
       <c r="AC39" s="44"/>
@@ -18369,14 +18372,14 @@
       <c r="I40" s="25"/>
       <c r="J40" s="25"/>
       <c r="K40" s="39" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L40" s="39"/>
       <c r="M40" s="39"/>
       <c r="N40" s="39"/>
       <c r="O40" s="39"/>
       <c r="P40" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q40" s="46"/>
       <c r="R40" s="46"/>
@@ -18389,7 +18392,7 @@
       <c r="Y40" s="46"/>
       <c r="Z40" s="54"/>
       <c r="AA40" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB40" s="44"/>
       <c r="AC40" s="44"/>
@@ -18415,14 +18418,14 @@
       <c r="I41" s="25"/>
       <c r="J41" s="25"/>
       <c r="K41" s="39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L41" s="39"/>
       <c r="M41" s="39"/>
       <c r="N41" s="39"/>
       <c r="O41" s="39"/>
       <c r="P41" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q41" s="46"/>
       <c r="R41" s="46"/>
@@ -18435,7 +18438,7 @@
       <c r="Y41" s="46"/>
       <c r="Z41" s="54"/>
       <c r="AA41" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB41" s="44"/>
       <c r="AC41" s="44"/>
@@ -18461,14 +18464,14 @@
       <c r="I42" s="25"/>
       <c r="J42" s="25"/>
       <c r="K42" s="256" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L42" s="39"/>
       <c r="M42" s="39"/>
       <c r="N42" s="39"/>
       <c r="O42" s="39"/>
       <c r="P42" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q42" s="46"/>
       <c r="R42" s="46"/>
@@ -18481,7 +18484,7 @@
       <c r="Y42" s="46"/>
       <c r="Z42" s="54"/>
       <c r="AA42" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB42" s="44"/>
       <c r="AC42" s="44"/>
@@ -18507,14 +18510,14 @@
       <c r="I43" s="25"/>
       <c r="J43" s="25"/>
       <c r="K43" s="256" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L43" s="39"/>
       <c r="M43" s="39"/>
       <c r="N43" s="39"/>
       <c r="O43" s="39"/>
       <c r="P43" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q43" s="46"/>
       <c r="R43" s="46"/>
@@ -18527,7 +18530,7 @@
       <c r="Y43" s="46"/>
       <c r="Z43" s="54"/>
       <c r="AA43" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB43" s="44"/>
       <c r="AC43" s="44"/>
@@ -18553,14 +18556,14 @@
       <c r="I44" s="25"/>
       <c r="J44" s="25"/>
       <c r="K44" s="256" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L44" s="39"/>
       <c r="M44" s="39"/>
       <c r="N44" s="39"/>
       <c r="O44" s="39"/>
       <c r="P44" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q44" s="46"/>
       <c r="R44" s="46"/>
@@ -18573,7 +18576,7 @@
       <c r="Y44" s="46"/>
       <c r="Z44" s="54"/>
       <c r="AA44" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB44" s="44"/>
       <c r="AC44" s="44"/>
@@ -18599,14 +18602,14 @@
       <c r="I45" s="25"/>
       <c r="J45" s="25"/>
       <c r="K45" s="256" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L45" s="39"/>
       <c r="M45" s="39"/>
       <c r="N45" s="39"/>
       <c r="O45" s="39"/>
       <c r="P45" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q45" s="46"/>
       <c r="R45" s="46"/>
@@ -18619,7 +18622,7 @@
       <c r="Y45" s="46"/>
       <c r="Z45" s="54"/>
       <c r="AA45" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB45" s="44"/>
       <c r="AC45" s="44"/>
@@ -18645,14 +18648,14 @@
       <c r="I46" s="25"/>
       <c r="J46" s="25"/>
       <c r="K46" s="256" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L46" s="39"/>
       <c r="M46" s="39"/>
       <c r="N46" s="39"/>
       <c r="O46" s="39"/>
       <c r="P46" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q46" s="46"/>
       <c r="R46" s="46"/>
@@ -18665,7 +18668,7 @@
       <c r="Y46" s="46"/>
       <c r="Z46" s="54"/>
       <c r="AA46" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB46" s="44"/>
       <c r="AC46" s="44"/>
@@ -18691,14 +18694,14 @@
       <c r="I47" s="25"/>
       <c r="J47" s="25"/>
       <c r="K47" s="256" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L47" s="39"/>
       <c r="M47" s="39"/>
       <c r="N47" s="39"/>
       <c r="O47" s="39"/>
       <c r="P47" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q47" s="46"/>
       <c r="R47" s="46"/>
@@ -18711,7 +18714,7 @@
       <c r="Y47" s="46"/>
       <c r="Z47" s="54"/>
       <c r="AA47" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB47" s="44"/>
       <c r="AC47" s="44"/>
@@ -18777,7 +18780,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L49" s="25"/>
       <c r="M49" s="25"/>
@@ -18819,14 +18822,14 @@
       <c r="I50" s="25"/>
       <c r="J50" s="25"/>
       <c r="K50" s="29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L50" s="29"/>
       <c r="M50" s="29"/>
       <c r="N50" s="29"/>
       <c r="O50" s="29"/>
       <c r="P50" s="37" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q50" s="45"/>
       <c r="R50" s="45"/>
@@ -18839,7 +18842,7 @@
       <c r="Y50" s="45"/>
       <c r="Z50" s="53"/>
       <c r="AA50" s="29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AB50" s="29"/>
       <c r="AC50" s="29"/>
@@ -18865,14 +18868,14 @@
       <c r="I51" s="25"/>
       <c r="J51" s="25"/>
       <c r="K51" s="39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L51" s="39"/>
       <c r="M51" s="39"/>
       <c r="N51" s="39"/>
       <c r="O51" s="39"/>
       <c r="P51" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="46"/>
       <c r="R51" s="46"/>
@@ -18885,7 +18888,7 @@
       <c r="Y51" s="46"/>
       <c r="Z51" s="54"/>
       <c r="AA51" s="44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB51" s="44"/>
       <c r="AC51" s="44"/>
@@ -18911,7 +18914,7 @@
       <c r="I52" s="25"/>
       <c r="J52" s="25"/>
       <c r="K52" s="257" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L52" s="25"/>
       <c r="M52" s="25"/>
@@ -18993,7 +18996,7 @@
       <c r="I54" s="25"/>
       <c r="J54" s="25"/>
       <c r="K54" s="257" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L54" s="25"/>
       <c r="M54" s="25"/>
@@ -19036,7 +19039,7 @@
       <c r="J55" s="25"/>
       <c r="K55" s="41"/>
       <c r="L55" s="25" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M55" s="25"/>
       <c r="N55" s="25"/>
@@ -19078,7 +19081,7 @@
       <c r="J56" s="25"/>
       <c r="K56" s="41"/>
       <c r="L56" s="25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M56" s="25"/>
       <c r="N56" s="25"/>
@@ -19159,7 +19162,7 @@
       <c r="I58" s="25"/>
       <c r="J58" s="25"/>
       <c r="K58" s="257" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L58" s="25"/>
       <c r="M58" s="25"/>
@@ -19182,7 +19185,7 @@
       <c r="AD58" s="25"/>
       <c r="AE58" s="52"/>
       <c r="AF58" s="41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG58" s="27"/>
       <c r="AH58" s="27"/>
@@ -19203,7 +19206,7 @@
       <c r="I59" s="25"/>
       <c r="J59" s="25"/>
       <c r="K59" s="25" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L59" s="25"/>
       <c r="M59" s="25"/>
@@ -19235,7 +19238,7 @@
     </row>
     <row r="60" customHeight="1" spans="1:38">
       <c r="A60" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -19246,7 +19249,7 @@
       <c r="H60" s="24"/>
       <c r="I60" s="25"/>
       <c r="J60" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K60" s="25"/>
       <c r="L60" s="25"/>
@@ -19270,7 +19273,7 @@
       <c r="AD60" s="25"/>
       <c r="AE60" s="52"/>
       <c r="AF60" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG60" s="1"/>
       <c r="AH60" s="1"/>
@@ -19282,7 +19285,7 @@
     <row r="61" customHeight="1" spans="1:38">
       <c r="A61" s="18"/>
       <c r="B61" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
@@ -19293,7 +19296,7 @@
       <c r="I61" s="25"/>
       <c r="J61" s="25"/>
       <c r="K61" s="25" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L61" s="36"/>
       <c r="M61" s="36"/>
@@ -19326,7 +19329,7 @@
     <row r="62" customHeight="1" spans="1:38">
       <c r="A62" s="20"/>
       <c r="B62" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -19337,7 +19340,7 @@
       <c r="I62" s="25"/>
       <c r="J62" s="25"/>
       <c r="K62" s="25" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L62" s="25"/>
       <c r="M62" s="25"/>
@@ -19419,7 +19422,7 @@
       <c r="I64" s="25"/>
       <c r="J64" s="25"/>
       <c r="K64" s="25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L64" s="25"/>
       <c r="M64" s="25"/>
@@ -19462,7 +19465,7 @@
       <c r="J65" s="25"/>
       <c r="K65" s="25"/>
       <c r="L65" s="25" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M65" s="25"/>
       <c r="N65" s="25"/>
@@ -19504,7 +19507,7 @@
       <c r="J66" s="25"/>
       <c r="K66" s="25"/>
       <c r="L66" s="25" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M66" s="25"/>
       <c r="N66" s="25"/>
@@ -19546,7 +19549,7 @@
       <c r="J67" s="25"/>
       <c r="K67" s="25"/>
       <c r="L67" s="25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M67" s="25"/>
       <c r="N67" s="25"/>
@@ -19627,7 +19630,7 @@
       <c r="I69" s="25"/>
       <c r="J69" s="25"/>
       <c r="K69" s="25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L69" s="25"/>
       <c r="M69" s="25"/>
@@ -19670,7 +19673,7 @@
       <c r="J70" s="25"/>
       <c r="K70" s="25"/>
       <c r="L70" s="25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M70" s="25"/>
       <c r="N70" s="25"/>
@@ -19712,7 +19715,7 @@
       <c r="J71" s="25"/>
       <c r="K71" s="25"/>
       <c r="L71" s="25" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M71" s="25"/>
       <c r="N71" s="25"/>
@@ -19783,7 +19786,7 @@
     </row>
     <row r="73" customHeight="1" spans="1:38">
       <c r="A73" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -19794,7 +19797,7 @@
       <c r="H73" s="24"/>
       <c r="I73" s="25"/>
       <c r="J73" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K73" s="25"/>
       <c r="L73" s="25"/>
@@ -19876,7 +19879,7 @@
       <c r="H75" s="24"/>
       <c r="I75" s="25"/>
       <c r="J75" s="25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K75" s="25"/>
       <c r="L75" s="25"/>
@@ -19919,7 +19922,7 @@
       <c r="I76" s="25"/>
       <c r="J76" s="25"/>
       <c r="K76" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
@@ -19953,7 +19956,7 @@
       <c r="A77" s="20"/>
       <c r="H77" s="20"/>
       <c r="K77" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AE77" s="51"/>
       <c r="AL77" s="51"/>
@@ -20002,11 +20005,11 @@
       <c r="A79" s="20"/>
       <c r="H79" s="20"/>
       <c r="J79" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AE79" s="51"/>
       <c r="AF79" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL79" s="51"/>
     </row>

--- a/docs/詳細設計書/詳細設計書_在庫センター情報画面.xlsx
+++ b/docs/詳細設計書/詳細設計書_在庫センター情報画面.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="7575"/>
+    <workbookView windowWidth="19815" windowHeight="7575" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="19" r:id="rId1"/>
@@ -1057,9 +1057,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="45">
     <font>
@@ -1199,8 +1199,30 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -1221,66 +1243,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
@@ -1296,17 +1267,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1320,6 +1290,35 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
@@ -1328,15 +1327,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="游ゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1414,6 +1414,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1426,7 +1444,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1438,13 +1498,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1456,7 +1516,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1468,73 +1540,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1546,19 +1552,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1884,9 +1884,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1909,8 +1920,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1926,15 +1937,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1956,11 +1958,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1984,148 +1984,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="30" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="31" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="26" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="20" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="23" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">

--- a/docs/詳細設計書/詳細設計書_在庫センター情報画面.xlsx
+++ b/docs/詳細設計書/詳細設計書_在庫センター情報画面.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19815" windowHeight="7575" activeTab="2"/>
+    <workbookView windowWidth="19815" windowHeight="7575"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="19" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="286">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -53,23 +53,23 @@
   </si>
   <si>
     <t>◆画面項目仕様シート
-以下を画面項目を新規追加
-・在庫センター情報 登録画面
-・在庫センター情報 更新/削除画面
+　以下を画面項目を新規追加
+　・在庫センター情報 登録画面
+　・在庫センター情報 更新/削除画面
 ◆画面イメージ
-以下、画面イメージを新規追加
-・在庫センター画面 登録画面
-・在庫センター画面 更新/削除画面
-・在庫センター画面 登録/更新/削除画面でのエラー時の画面表示内容</t>
+　以下、画面イメージを新規追加
+　・在庫センター画面 登録画面
+　・在庫センター画面 更新/削除画面
+　・在庫センター画面 登録/更新/削除画面でのエラー時の画面表示内容</t>
   </si>
   <si>
     <t>1.2</t>
   </si>
   <si>
     <t>◆画面項目仕様シート
-画面項目に「イベント処理」の記載欄を追加
+　・画面項目に「イベント処理」の記載欄を追加
 ◆処理詳細
-使用クラスを追加記載</t>
+　・使用クラスを追加記載</t>
   </si>
   <si>
     <t>機能概要</t>
@@ -210,7 +210,7 @@
     <t>文字数制限：20文字</t>
   </si>
   <si>
-    <t>入力時: 制限を超えたら警告を表示</t>
+    <t>文字数を超えた状態でフォーカスを抜けた際に、警告メッセージを表示する。</t>
   </si>
   <si>
     <t>　都道府県名</t>
@@ -225,9 +225,6 @@
     <t>想定外エラー：都道府県リスト外の文字</t>
   </si>
   <si>
-    <t>クリック時：都道府県リスト外を表示</t>
-  </si>
-  <si>
     <t>　検索</t>
   </si>
   <si>
@@ -237,7 +234,7 @@
     <t>センター検索を行うフォームを送信するボタン</t>
   </si>
   <si>
-    <t>クリック時: 検索結果を表示</t>
+    <t>押下時: バリデーションチェックを実行し、検索条件を送信</t>
   </si>
   <si>
     <t>　新規登録</t>
@@ -246,7 +243,7 @@
     <t>在庫センター情報（新規登録）画面に遷移</t>
   </si>
   <si>
-    <t>クリック時: 登録画面へ遷移</t>
+    <t>押下時: 登録画面へ遷移</t>
   </si>
   <si>
     <t>在庫センター テーブル</t>
@@ -276,7 +273,7 @@
     <t>センターの名称（更新/削除画面へ遷移するリンク）</t>
   </si>
   <si>
-    <t>クリック時: 更新/削除画面へ遷移</t>
+    <t>押下時: 更新/削除画面へ遷移</t>
   </si>
   <si>
     <t>　　住所</t>
@@ -1056,10 +1053,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="45">
     <font>
@@ -1199,16 +1196,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1221,8 +1211,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -1230,7 +1228,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1245,25 +1250,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1282,29 +1286,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="游ゴシック"/>
@@ -1312,8 +1293,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1327,7 +1324,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
@@ -1336,15 +1341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1408,7 +1405,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1420,19 +1495,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1444,85 +1537,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1540,25 +1555,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1882,22 +1879,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1913,6 +1905,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1941,6 +1942,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1958,24 +1968,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1984,155 +1981,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="31" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="31" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="32" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="33" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="33" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="26" borderId="34" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="256">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2815,6 +2812,9 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3453,7 +3453,7 @@
   <sheetFormatPr defaultColWidth="3.77777777777778" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.77777777777778" style="79"/>
-    <col min="2" max="2" width="5.11111111111111" style="250" customWidth="1"/>
+    <col min="2" max="2" width="5.11111111111111" style="251" customWidth="1"/>
     <col min="3" max="3" width="12.2222222222222" style="79" customWidth="1"/>
     <col min="4" max="4" width="6.88888888888889" style="79" customWidth="1"/>
     <col min="5" max="5" width="66.1111111111111" style="79" customWidth="1"/>
@@ -3466,7 +3466,7 @@
       </c>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="252" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="94" t="s">
@@ -3480,430 +3480,430 @@
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="252" t="s">
+      <c r="B3" s="253" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="253">
+      <c r="C3" s="254">
         <v>45636</v>
       </c>
-      <c r="D3" s="254" t="s">
+      <c r="D3" s="255" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="254" t="s">
+      <c r="E3" s="255" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="165" spans="2:5">
-      <c r="B4" s="252" t="s">
+      <c r="B4" s="253" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="253">
+      <c r="C4" s="254">
         <v>45705</v>
       </c>
-      <c r="D4" s="254" t="s">
+      <c r="D4" s="255" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="255" t="s">
+      <c r="E4" s="256" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" ht="82.5" spans="2:5">
-      <c r="B5" s="252" t="s">
+      <c r="B5" s="253" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="253">
+      <c r="C5" s="254">
         <v>45729</v>
       </c>
-      <c r="D5" s="254" t="s">
+      <c r="D5" s="255" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="255" t="s">
+      <c r="E5" s="256" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="252"/>
-      <c r="C6" s="254"/>
-      <c r="D6" s="254"/>
-      <c r="E6" s="254"/>
+      <c r="B6" s="253"/>
+      <c r="C6" s="255"/>
+      <c r="D6" s="255"/>
+      <c r="E6" s="255"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="252"/>
-      <c r="C7" s="254"/>
-      <c r="D7" s="254"/>
-      <c r="E7" s="254"/>
+      <c r="B7" s="253"/>
+      <c r="C7" s="255"/>
+      <c r="D7" s="255"/>
+      <c r="E7" s="255"/>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="252"/>
-      <c r="C8" s="254"/>
-      <c r="D8" s="254"/>
-      <c r="E8" s="254"/>
+      <c r="B8" s="253"/>
+      <c r="C8" s="255"/>
+      <c r="D8" s="255"/>
+      <c r="E8" s="255"/>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="252"/>
-      <c r="C9" s="254"/>
-      <c r="D9" s="254"/>
-      <c r="E9" s="254"/>
+      <c r="B9" s="253"/>
+      <c r="C9" s="255"/>
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="252"/>
-      <c r="C10" s="254"/>
-      <c r="D10" s="254"/>
-      <c r="E10" s="254"/>
+      <c r="B10" s="253"/>
+      <c r="C10" s="255"/>
+      <c r="D10" s="255"/>
+      <c r="E10" s="255"/>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="252"/>
-      <c r="C11" s="254"/>
-      <c r="D11" s="254"/>
-      <c r="E11" s="254"/>
+      <c r="B11" s="253"/>
+      <c r="C11" s="255"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="252"/>
-      <c r="C12" s="254"/>
-      <c r="D12" s="254"/>
-      <c r="E12" s="254"/>
+      <c r="B12" s="253"/>
+      <c r="C12" s="255"/>
+      <c r="D12" s="255"/>
+      <c r="E12" s="255"/>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="252"/>
-      <c r="C13" s="254"/>
-      <c r="D13" s="254"/>
-      <c r="E13" s="254"/>
+      <c r="B13" s="253"/>
+      <c r="C13" s="255"/>
+      <c r="D13" s="255"/>
+      <c r="E13" s="255"/>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="252"/>
-      <c r="C14" s="254"/>
-      <c r="D14" s="254"/>
-      <c r="E14" s="254"/>
+      <c r="B14" s="253"/>
+      <c r="C14" s="255"/>
+      <c r="D14" s="255"/>
+      <c r="E14" s="255"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="252"/>
-      <c r="C15" s="254"/>
-      <c r="D15" s="254"/>
-      <c r="E15" s="254"/>
+      <c r="B15" s="253"/>
+      <c r="C15" s="255"/>
+      <c r="D15" s="255"/>
+      <c r="E15" s="255"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="252"/>
-      <c r="C16" s="254"/>
-      <c r="D16" s="254"/>
-      <c r="E16" s="254"/>
+      <c r="B16" s="253"/>
+      <c r="C16" s="255"/>
+      <c r="D16" s="255"/>
+      <c r="E16" s="255"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="252"/>
-      <c r="C17" s="254"/>
-      <c r="D17" s="254"/>
-      <c r="E17" s="254"/>
+      <c r="B17" s="253"/>
+      <c r="C17" s="255"/>
+      <c r="D17" s="255"/>
+      <c r="E17" s="255"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="252"/>
-      <c r="C18" s="254"/>
-      <c r="D18" s="254"/>
-      <c r="E18" s="254"/>
+      <c r="B18" s="253"/>
+      <c r="C18" s="255"/>
+      <c r="D18" s="255"/>
+      <c r="E18" s="255"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="252"/>
-      <c r="C19" s="254"/>
-      <c r="D19" s="254"/>
-      <c r="E19" s="254"/>
+      <c r="B19" s="253"/>
+      <c r="C19" s="255"/>
+      <c r="D19" s="255"/>
+      <c r="E19" s="255"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="252"/>
-      <c r="C20" s="254"/>
-      <c r="D20" s="254"/>
-      <c r="E20" s="254"/>
+      <c r="B20" s="253"/>
+      <c r="C20" s="255"/>
+      <c r="D20" s="255"/>
+      <c r="E20" s="255"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="252"/>
-      <c r="C21" s="254"/>
-      <c r="D21" s="254"/>
-      <c r="E21" s="254"/>
+      <c r="B21" s="253"/>
+      <c r="C21" s="255"/>
+      <c r="D21" s="255"/>
+      <c r="E21" s="255"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="252"/>
-      <c r="C22" s="254"/>
-      <c r="D22" s="254"/>
-      <c r="E22" s="254"/>
+      <c r="B22" s="253"/>
+      <c r="C22" s="255"/>
+      <c r="D22" s="255"/>
+      <c r="E22" s="255"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="252"/>
-      <c r="C23" s="254"/>
-      <c r="D23" s="254"/>
-      <c r="E23" s="254"/>
+      <c r="B23" s="253"/>
+      <c r="C23" s="255"/>
+      <c r="D23" s="255"/>
+      <c r="E23" s="255"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="252"/>
-      <c r="C24" s="254"/>
-      <c r="D24" s="254"/>
-      <c r="E24" s="254"/>
+      <c r="B24" s="253"/>
+      <c r="C24" s="255"/>
+      <c r="D24" s="255"/>
+      <c r="E24" s="255"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="252"/>
-      <c r="C25" s="254"/>
-      <c r="D25" s="254"/>
-      <c r="E25" s="254"/>
+      <c r="B25" s="253"/>
+      <c r="C25" s="255"/>
+      <c r="D25" s="255"/>
+      <c r="E25" s="255"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="252"/>
-      <c r="C26" s="254"/>
-      <c r="D26" s="254"/>
-      <c r="E26" s="254"/>
+      <c r="B26" s="253"/>
+      <c r="C26" s="255"/>
+      <c r="D26" s="255"/>
+      <c r="E26" s="255"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="252"/>
-      <c r="C27" s="254"/>
-      <c r="D27" s="254"/>
-      <c r="E27" s="254"/>
+      <c r="B27" s="253"/>
+      <c r="C27" s="255"/>
+      <c r="D27" s="255"/>
+      <c r="E27" s="255"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="252"/>
-      <c r="C28" s="254"/>
-      <c r="D28" s="254"/>
-      <c r="E28" s="254"/>
+      <c r="B28" s="253"/>
+      <c r="C28" s="255"/>
+      <c r="D28" s="255"/>
+      <c r="E28" s="255"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="252"/>
-      <c r="C29" s="254"/>
-      <c r="D29" s="254"/>
-      <c r="E29" s="254"/>
+      <c r="B29" s="253"/>
+      <c r="C29" s="255"/>
+      <c r="D29" s="255"/>
+      <c r="E29" s="255"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="252"/>
-      <c r="C30" s="254"/>
-      <c r="D30" s="254"/>
-      <c r="E30" s="254"/>
+      <c r="B30" s="253"/>
+      <c r="C30" s="255"/>
+      <c r="D30" s="255"/>
+      <c r="E30" s="255"/>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="252"/>
-      <c r="C31" s="254"/>
-      <c r="D31" s="254"/>
-      <c r="E31" s="254"/>
+      <c r="B31" s="253"/>
+      <c r="C31" s="255"/>
+      <c r="D31" s="255"/>
+      <c r="E31" s="255"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="252"/>
-      <c r="C32" s="254"/>
-      <c r="D32" s="254"/>
-      <c r="E32" s="254"/>
+      <c r="B32" s="253"/>
+      <c r="C32" s="255"/>
+      <c r="D32" s="255"/>
+      <c r="E32" s="255"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="252"/>
-      <c r="C33" s="254"/>
-      <c r="D33" s="254"/>
-      <c r="E33" s="254"/>
+      <c r="B33" s="253"/>
+      <c r="C33" s="255"/>
+      <c r="D33" s="255"/>
+      <c r="E33" s="255"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="252"/>
-      <c r="C34" s="254"/>
-      <c r="D34" s="254"/>
-      <c r="E34" s="254"/>
+      <c r="B34" s="253"/>
+      <c r="C34" s="255"/>
+      <c r="D34" s="255"/>
+      <c r="E34" s="255"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="252"/>
-      <c r="C35" s="254"/>
-      <c r="D35" s="254"/>
-      <c r="E35" s="254"/>
+      <c r="B35" s="253"/>
+      <c r="C35" s="255"/>
+      <c r="D35" s="255"/>
+      <c r="E35" s="255"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="252"/>
-      <c r="C36" s="254"/>
-      <c r="D36" s="254"/>
-      <c r="E36" s="254"/>
+      <c r="B36" s="253"/>
+      <c r="C36" s="255"/>
+      <c r="D36" s="255"/>
+      <c r="E36" s="255"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="252"/>
-      <c r="C37" s="254"/>
-      <c r="D37" s="254"/>
-      <c r="E37" s="254"/>
+      <c r="B37" s="253"/>
+      <c r="C37" s="255"/>
+      <c r="D37" s="255"/>
+      <c r="E37" s="255"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="252"/>
-      <c r="C38" s="254"/>
-      <c r="D38" s="254"/>
-      <c r="E38" s="254"/>
+      <c r="B38" s="253"/>
+      <c r="C38" s="255"/>
+      <c r="D38" s="255"/>
+      <c r="E38" s="255"/>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="252"/>
-      <c r="C39" s="254"/>
-      <c r="D39" s="254"/>
-      <c r="E39" s="254"/>
+      <c r="B39" s="253"/>
+      <c r="C39" s="255"/>
+      <c r="D39" s="255"/>
+      <c r="E39" s="255"/>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="252"/>
-      <c r="C40" s="254"/>
-      <c r="D40" s="254"/>
-      <c r="E40" s="254"/>
+      <c r="B40" s="253"/>
+      <c r="C40" s="255"/>
+      <c r="D40" s="255"/>
+      <c r="E40" s="255"/>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="252"/>
-      <c r="C41" s="254"/>
-      <c r="D41" s="254"/>
-      <c r="E41" s="254"/>
+      <c r="B41" s="253"/>
+      <c r="C41" s="255"/>
+      <c r="D41" s="255"/>
+      <c r="E41" s="255"/>
     </row>
     <row r="42" spans="2:5">
-      <c r="B42" s="252"/>
-      <c r="C42" s="254"/>
-      <c r="D42" s="254"/>
-      <c r="E42" s="254"/>
+      <c r="B42" s="253"/>
+      <c r="C42" s="255"/>
+      <c r="D42" s="255"/>
+      <c r="E42" s="255"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="252"/>
-      <c r="C43" s="254"/>
-      <c r="D43" s="254"/>
-      <c r="E43" s="254"/>
+      <c r="B43" s="253"/>
+      <c r="C43" s="255"/>
+      <c r="D43" s="255"/>
+      <c r="E43" s="255"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="B44" s="252"/>
-      <c r="C44" s="254"/>
-      <c r="D44" s="254"/>
-      <c r="E44" s="254"/>
+      <c r="B44" s="253"/>
+      <c r="C44" s="255"/>
+      <c r="D44" s="255"/>
+      <c r="E44" s="255"/>
     </row>
     <row r="45" spans="2:5">
-      <c r="B45" s="252"/>
-      <c r="C45" s="254"/>
-      <c r="D45" s="254"/>
-      <c r="E45" s="254"/>
+      <c r="B45" s="253"/>
+      <c r="C45" s="255"/>
+      <c r="D45" s="255"/>
+      <c r="E45" s="255"/>
     </row>
     <row r="46" spans="2:5">
-      <c r="B46" s="252"/>
-      <c r="C46" s="254"/>
-      <c r="D46" s="254"/>
-      <c r="E46" s="254"/>
+      <c r="B46" s="253"/>
+      <c r="C46" s="255"/>
+      <c r="D46" s="255"/>
+      <c r="E46" s="255"/>
     </row>
     <row r="47" spans="2:5">
-      <c r="B47" s="252"/>
-      <c r="C47" s="254"/>
-      <c r="D47" s="254"/>
-      <c r="E47" s="254"/>
+      <c r="B47" s="253"/>
+      <c r="C47" s="255"/>
+      <c r="D47" s="255"/>
+      <c r="E47" s="255"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="252"/>
-      <c r="C48" s="254"/>
-      <c r="D48" s="254"/>
-      <c r="E48" s="254"/>
+      <c r="B48" s="253"/>
+      <c r="C48" s="255"/>
+      <c r="D48" s="255"/>
+      <c r="E48" s="255"/>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="252"/>
-      <c r="C49" s="254"/>
-      <c r="D49" s="254"/>
-      <c r="E49" s="254"/>
+      <c r="B49" s="253"/>
+      <c r="C49" s="255"/>
+      <c r="D49" s="255"/>
+      <c r="E49" s="255"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="252"/>
-      <c r="C50" s="254"/>
-      <c r="D50" s="254"/>
-      <c r="E50" s="254"/>
+      <c r="B50" s="253"/>
+      <c r="C50" s="255"/>
+      <c r="D50" s="255"/>
+      <c r="E50" s="255"/>
     </row>
     <row r="51" spans="2:5">
-      <c r="B51" s="252"/>
-      <c r="C51" s="254"/>
-      <c r="D51" s="254"/>
-      <c r="E51" s="254"/>
+      <c r="B51" s="253"/>
+      <c r="C51" s="255"/>
+      <c r="D51" s="255"/>
+      <c r="E51" s="255"/>
     </row>
     <row r="52" spans="2:5">
-      <c r="B52" s="252"/>
-      <c r="C52" s="254"/>
-      <c r="D52" s="254"/>
-      <c r="E52" s="254"/>
+      <c r="B52" s="253"/>
+      <c r="C52" s="255"/>
+      <c r="D52" s="255"/>
+      <c r="E52" s="255"/>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="252"/>
-      <c r="C53" s="254"/>
-      <c r="D53" s="254"/>
-      <c r="E53" s="254"/>
+      <c r="B53" s="253"/>
+      <c r="C53" s="255"/>
+      <c r="D53" s="255"/>
+      <c r="E53" s="255"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="252"/>
-      <c r="C54" s="254"/>
-      <c r="D54" s="254"/>
-      <c r="E54" s="254"/>
+      <c r="B54" s="253"/>
+      <c r="C54" s="255"/>
+      <c r="D54" s="255"/>
+      <c r="E54" s="255"/>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="252"/>
-      <c r="C55" s="254"/>
-      <c r="D55" s="254"/>
-      <c r="E55" s="254"/>
+      <c r="B55" s="253"/>
+      <c r="C55" s="255"/>
+      <c r="D55" s="255"/>
+      <c r="E55" s="255"/>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="252"/>
-      <c r="C56" s="254"/>
-      <c r="D56" s="254"/>
-      <c r="E56" s="254"/>
+      <c r="B56" s="253"/>
+      <c r="C56" s="255"/>
+      <c r="D56" s="255"/>
+      <c r="E56" s="255"/>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="252"/>
-      <c r="C57" s="254"/>
-      <c r="D57" s="254"/>
-      <c r="E57" s="254"/>
+      <c r="B57" s="253"/>
+      <c r="C57" s="255"/>
+      <c r="D57" s="255"/>
+      <c r="E57" s="255"/>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="252"/>
-      <c r="C58" s="254"/>
-      <c r="D58" s="254"/>
-      <c r="E58" s="254"/>
+      <c r="B58" s="253"/>
+      <c r="C58" s="255"/>
+      <c r="D58" s="255"/>
+      <c r="E58" s="255"/>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="252"/>
-      <c r="C59" s="254"/>
-      <c r="D59" s="254"/>
-      <c r="E59" s="254"/>
+      <c r="B59" s="253"/>
+      <c r="C59" s="255"/>
+      <c r="D59" s="255"/>
+      <c r="E59" s="255"/>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="252"/>
-      <c r="C60" s="254"/>
-      <c r="D60" s="254"/>
-      <c r="E60" s="254"/>
+      <c r="B60" s="253"/>
+      <c r="C60" s="255"/>
+      <c r="D60" s="255"/>
+      <c r="E60" s="255"/>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="252"/>
-      <c r="C61" s="254"/>
-      <c r="D61" s="254"/>
-      <c r="E61" s="254"/>
+      <c r="B61" s="253"/>
+      <c r="C61" s="255"/>
+      <c r="D61" s="255"/>
+      <c r="E61" s="255"/>
     </row>
     <row r="62" spans="2:5">
-      <c r="B62" s="252"/>
-      <c r="C62" s="254"/>
-      <c r="D62" s="254"/>
-      <c r="E62" s="254"/>
+      <c r="B62" s="253"/>
+      <c r="C62" s="255"/>
+      <c r="D62" s="255"/>
+      <c r="E62" s="255"/>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="252"/>
-      <c r="C63" s="254"/>
-      <c r="D63" s="254"/>
-      <c r="E63" s="254"/>
+      <c r="B63" s="253"/>
+      <c r="C63" s="255"/>
+      <c r="D63" s="255"/>
+      <c r="E63" s="255"/>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="252"/>
-      <c r="C64" s="254"/>
-      <c r="D64" s="254"/>
-      <c r="E64" s="254"/>
+      <c r="B64" s="253"/>
+      <c r="C64" s="255"/>
+      <c r="D64" s="255"/>
+      <c r="E64" s="255"/>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="252"/>
-      <c r="C65" s="254"/>
-      <c r="D65" s="254"/>
-      <c r="E65" s="254"/>
+      <c r="B65" s="253"/>
+      <c r="C65" s="255"/>
+      <c r="D65" s="255"/>
+      <c r="E65" s="255"/>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="252"/>
-      <c r="C66" s="254"/>
-      <c r="D66" s="254"/>
-      <c r="E66" s="254"/>
+      <c r="B66" s="253"/>
+      <c r="C66" s="255"/>
+      <c r="D66" s="255"/>
+      <c r="E66" s="255"/>
     </row>
     <row r="67" spans="2:5">
-      <c r="B67" s="252"/>
-      <c r="C67" s="254"/>
-      <c r="D67" s="254"/>
-      <c r="E67" s="254"/>
+      <c r="B67" s="253"/>
+      <c r="C67" s="255"/>
+      <c r="D67" s="255"/>
+      <c r="E67" s="255"/>
     </row>
     <row r="68" spans="2:5">
-      <c r="B68" s="252"/>
-      <c r="C68" s="254"/>
-      <c r="D68" s="254"/>
-      <c r="E68" s="254"/>
+      <c r="B68" s="253"/>
+      <c r="C68" s="255"/>
+      <c r="D68" s="255"/>
+      <c r="E68" s="255"/>
     </row>
     <row r="69" spans="2:5">
-      <c r="B69" s="252"/>
-      <c r="C69" s="254"/>
-      <c r="D69" s="254"/>
-      <c r="E69" s="254"/>
+      <c r="B69" s="253"/>
+      <c r="C69" s="255"/>
+      <c r="D69" s="255"/>
+      <c r="E69" s="255"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4172,28 +4172,28 @@
       <c r="AO5" s="71"/>
     </row>
     <row r="6" customHeight="1" spans="1:41">
-      <c r="A6" s="237"/>
-      <c r="B6" s="238"/>
-      <c r="C6" s="238"/>
-      <c r="D6" s="238"/>
-      <c r="E6" s="238"/>
-      <c r="F6" s="238"/>
-      <c r="G6" s="238"/>
-      <c r="H6" s="238"/>
-      <c r="I6" s="238"/>
-      <c r="J6" s="238"/>
-      <c r="K6" s="238"/>
-      <c r="L6" s="238"/>
-      <c r="M6" s="238"/>
-      <c r="N6" s="238"/>
-      <c r="O6" s="238"/>
-      <c r="P6" s="238"/>
-      <c r="Q6" s="238"/>
-      <c r="R6" s="238"/>
-      <c r="S6" s="238"/>
-      <c r="T6" s="238"/>
-      <c r="U6" s="238"/>
-      <c r="V6" s="245"/>
+      <c r="A6" s="238"/>
+      <c r="B6" s="239"/>
+      <c r="C6" s="239"/>
+      <c r="D6" s="239"/>
+      <c r="E6" s="239"/>
+      <c r="F6" s="239"/>
+      <c r="G6" s="239"/>
+      <c r="H6" s="239"/>
+      <c r="I6" s="239"/>
+      <c r="J6" s="239"/>
+      <c r="K6" s="239"/>
+      <c r="L6" s="239"/>
+      <c r="M6" s="239"/>
+      <c r="N6" s="239"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="239"/>
+      <c r="Q6" s="239"/>
+      <c r="R6" s="239"/>
+      <c r="S6" s="239"/>
+      <c r="T6" s="239"/>
+      <c r="U6" s="239"/>
+      <c r="V6" s="246"/>
       <c r="W6" s="83" t="s">
         <v>26</v>
       </c>
@@ -4212,13 +4212,13 @@
       <c r="AJ6" s="84"/>
       <c r="AK6" s="84"/>
       <c r="AL6" s="129"/>
-      <c r="AM6" s="237"/>
-      <c r="AN6" s="238"/>
-      <c r="AO6" s="245"/>
+      <c r="AM6" s="238"/>
+      <c r="AN6" s="239"/>
+      <c r="AO6" s="246"/>
     </row>
     <row r="7" customHeight="1" spans="1:41">
-      <c r="A7" s="239"/>
-      <c r="V7" s="246"/>
+      <c r="A7" s="240"/>
+      <c r="V7" s="247"/>
       <c r="W7" s="78" t="s">
         <v>27</v>
       </c>
@@ -4237,18 +4237,18 @@
       <c r="AJ7" s="79"/>
       <c r="AK7" s="79"/>
       <c r="AL7" s="90"/>
-      <c r="AM7" s="239"/>
-      <c r="AO7" s="246"/>
+      <c r="AM7" s="240"/>
+      <c r="AO7" s="247"/>
     </row>
     <row r="8" customHeight="1" spans="1:41">
-      <c r="A8" s="239"/>
-      <c r="V8" s="246"/>
-      <c r="AM8" s="239"/>
-      <c r="AO8" s="246"/>
+      <c r="A8" s="240"/>
+      <c r="V8" s="247"/>
+      <c r="AM8" s="240"/>
+      <c r="AO8" s="247"/>
     </row>
     <row r="9" customHeight="1" spans="1:41">
-      <c r="A9" s="239"/>
-      <c r="V9" s="246"/>
+      <c r="A9" s="240"/>
+      <c r="V9" s="247"/>
       <c r="W9" s="78"/>
       <c r="X9" s="79"/>
       <c r="Y9" s="79"/>
@@ -4265,12 +4265,12 @@
       <c r="AJ9" s="79"/>
       <c r="AK9" s="79"/>
       <c r="AL9" s="90"/>
-      <c r="AM9" s="239"/>
-      <c r="AO9" s="246"/>
+      <c r="AM9" s="240"/>
+      <c r="AO9" s="247"/>
     </row>
     <row r="10" customHeight="1" spans="1:41">
-      <c r="A10" s="239"/>
-      <c r="V10" s="246"/>
+      <c r="A10" s="240"/>
+      <c r="V10" s="247"/>
       <c r="W10" s="78"/>
       <c r="X10" s="79"/>
       <c r="Y10" s="79"/>
@@ -4287,12 +4287,12 @@
       <c r="AJ10" s="79"/>
       <c r="AK10" s="79"/>
       <c r="AL10" s="90"/>
-      <c r="AM10" s="239"/>
-      <c r="AO10" s="246"/>
+      <c r="AM10" s="240"/>
+      <c r="AO10" s="247"/>
     </row>
     <row r="11" customHeight="1" spans="1:41">
-      <c r="A11" s="239"/>
-      <c r="V11" s="246"/>
+      <c r="A11" s="240"/>
+      <c r="V11" s="247"/>
       <c r="W11" s="78"/>
       <c r="X11" s="79"/>
       <c r="Y11" s="79"/>
@@ -4309,14 +4309,14 @@
       <c r="AJ11" s="79"/>
       <c r="AK11" s="79"/>
       <c r="AL11" s="90"/>
-      <c r="AM11" s="239"/>
-      <c r="AO11" s="246"/>
+      <c r="AM11" s="240"/>
+      <c r="AO11" s="247"/>
     </row>
     <row r="12" customHeight="1" spans="1:41">
-      <c r="A12" s="239"/>
-      <c r="V12" s="246"/>
+      <c r="A12" s="240"/>
+      <c r="V12" s="247"/>
       <c r="W12" s="78"/>
-      <c r="X12" s="247"/>
+      <c r="X12" s="248"/>
       <c r="Y12" s="79"/>
       <c r="Z12" s="79"/>
       <c r="AA12" s="79"/>
@@ -4331,12 +4331,12 @@
       <c r="AJ12" s="79"/>
       <c r="AK12" s="79"/>
       <c r="AL12" s="90"/>
-      <c r="AM12" s="239"/>
-      <c r="AO12" s="246"/>
+      <c r="AM12" s="240"/>
+      <c r="AO12" s="247"/>
     </row>
     <row r="13" customHeight="1" spans="1:41">
-      <c r="A13" s="239"/>
-      <c r="V13" s="246"/>
+      <c r="A13" s="240"/>
+      <c r="V13" s="247"/>
       <c r="W13" s="78"/>
       <c r="X13" s="79"/>
       <c r="Y13" s="79"/>
@@ -4353,12 +4353,12 @@
       <c r="AJ13" s="79"/>
       <c r="AK13" s="79"/>
       <c r="AL13" s="90"/>
-      <c r="AM13" s="239"/>
-      <c r="AO13" s="246"/>
+      <c r="AM13" s="240"/>
+      <c r="AO13" s="247"/>
     </row>
     <row r="14" customHeight="1" spans="1:41">
-      <c r="A14" s="239"/>
-      <c r="V14" s="246"/>
+      <c r="A14" s="240"/>
+      <c r="V14" s="247"/>
       <c r="W14" s="78"/>
       <c r="X14" s="79"/>
       <c r="Y14" s="79"/>
@@ -4375,12 +4375,12 @@
       <c r="AJ14" s="79"/>
       <c r="AK14" s="79"/>
       <c r="AL14" s="90"/>
-      <c r="AM14" s="239"/>
-      <c r="AO14" s="246"/>
+      <c r="AM14" s="240"/>
+      <c r="AO14" s="247"/>
     </row>
     <row r="15" customHeight="1" spans="1:41">
-      <c r="A15" s="239"/>
-      <c r="V15" s="246"/>
+      <c r="A15" s="240"/>
+      <c r="V15" s="247"/>
       <c r="W15" s="78"/>
       <c r="X15" s="79"/>
       <c r="Y15" s="79"/>
@@ -4397,12 +4397,12 @@
       <c r="AJ15" s="79"/>
       <c r="AK15" s="79"/>
       <c r="AL15" s="90"/>
-      <c r="AM15" s="239"/>
-      <c r="AO15" s="246"/>
+      <c r="AM15" s="240"/>
+      <c r="AO15" s="247"/>
     </row>
     <row r="16" customHeight="1" spans="1:41">
-      <c r="A16" s="239"/>
-      <c r="V16" s="246"/>
+      <c r="A16" s="240"/>
+      <c r="V16" s="247"/>
       <c r="W16" s="78"/>
       <c r="X16" s="79"/>
       <c r="Y16" s="79"/>
@@ -4419,12 +4419,12 @@
       <c r="AJ16" s="79"/>
       <c r="AK16" s="79"/>
       <c r="AL16" s="90"/>
-      <c r="AM16" s="239"/>
-      <c r="AO16" s="246"/>
+      <c r="AM16" s="240"/>
+      <c r="AO16" s="247"/>
     </row>
     <row r="17" customHeight="1" spans="1:41">
-      <c r="A17" s="239"/>
-      <c r="V17" s="246"/>
+      <c r="A17" s="240"/>
+      <c r="V17" s="247"/>
       <c r="W17" s="78"/>
       <c r="X17" s="79"/>
       <c r="Y17" s="79"/>
@@ -4441,12 +4441,12 @@
       <c r="AJ17" s="79"/>
       <c r="AK17" s="79"/>
       <c r="AL17" s="90"/>
-      <c r="AM17" s="239"/>
-      <c r="AO17" s="246"/>
+      <c r="AM17" s="240"/>
+      <c r="AO17" s="247"/>
     </row>
     <row r="18" customHeight="1" spans="1:41">
-      <c r="A18" s="239"/>
-      <c r="V18" s="246"/>
+      <c r="A18" s="240"/>
+      <c r="V18" s="247"/>
       <c r="W18" s="78"/>
       <c r="X18" s="79"/>
       <c r="Y18" s="79"/>
@@ -4463,32 +4463,32 @@
       <c r="AJ18" s="79"/>
       <c r="AK18" s="79"/>
       <c r="AL18" s="90"/>
-      <c r="AM18" s="239"/>
-      <c r="AO18" s="246"/>
+      <c r="AM18" s="240"/>
+      <c r="AO18" s="247"/>
     </row>
     <row r="19" customHeight="1" spans="1:41">
-      <c r="A19" s="240"/>
-      <c r="B19" s="241"/>
-      <c r="C19" s="241"/>
-      <c r="D19" s="241"/>
-      <c r="E19" s="241"/>
-      <c r="F19" s="241"/>
-      <c r="G19" s="241"/>
-      <c r="H19" s="241"/>
-      <c r="I19" s="241"/>
-      <c r="J19" s="241"/>
-      <c r="K19" s="241"/>
-      <c r="L19" s="241"/>
-      <c r="M19" s="241"/>
-      <c r="N19" s="241"/>
-      <c r="O19" s="241"/>
-      <c r="P19" s="241"/>
-      <c r="Q19" s="241"/>
-      <c r="R19" s="241"/>
-      <c r="S19" s="241"/>
-      <c r="T19" s="241"/>
-      <c r="U19" s="241"/>
-      <c r="V19" s="248"/>
+      <c r="A19" s="241"/>
+      <c r="B19" s="242"/>
+      <c r="C19" s="242"/>
+      <c r="D19" s="242"/>
+      <c r="E19" s="242"/>
+      <c r="F19" s="242"/>
+      <c r="G19" s="242"/>
+      <c r="H19" s="242"/>
+      <c r="I19" s="242"/>
+      <c r="J19" s="242"/>
+      <c r="K19" s="242"/>
+      <c r="L19" s="242"/>
+      <c r="M19" s="242"/>
+      <c r="N19" s="242"/>
+      <c r="O19" s="242"/>
+      <c r="P19" s="242"/>
+      <c r="Q19" s="242"/>
+      <c r="R19" s="242"/>
+      <c r="S19" s="242"/>
+      <c r="T19" s="242"/>
+      <c r="U19" s="242"/>
+      <c r="V19" s="249"/>
       <c r="W19" s="88"/>
       <c r="X19" s="89"/>
       <c r="Y19" s="89"/>
@@ -4505,9 +4505,9 @@
       <c r="AJ19" s="89"/>
       <c r="AK19" s="89"/>
       <c r="AL19" s="92"/>
-      <c r="AM19" s="240"/>
-      <c r="AN19" s="241"/>
-      <c r="AO19" s="248"/>
+      <c r="AM19" s="241"/>
+      <c r="AN19" s="242"/>
+      <c r="AO19" s="249"/>
     </row>
     <row r="20" customHeight="1" spans="1:41">
       <c r="A20" s="71" t="s">
@@ -4572,17 +4572,17 @@
       <c r="A21" s="113">
         <v>1</v>
       </c>
-      <c r="B21" s="242"/>
-      <c r="C21" s="243" t="s">
+      <c r="B21" s="243"/>
+      <c r="C21" s="244" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="244"/>
-      <c r="E21" s="244"/>
-      <c r="F21" s="244"/>
-      <c r="G21" s="244"/>
-      <c r="H21" s="244"/>
-      <c r="I21" s="244"/>
-      <c r="J21" s="244"/>
+      <c r="D21" s="245"/>
+      <c r="E21" s="245"/>
+      <c r="F21" s="245"/>
+      <c r="G21" s="245"/>
+      <c r="H21" s="245"/>
+      <c r="I21" s="245"/>
+      <c r="J21" s="245"/>
       <c r="K21" s="113" t="s">
         <v>37</v>
       </c>
@@ -4599,504 +4599,504 @@
       <c r="P21" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="Q21" s="243"/>
-      <c r="R21" s="244"/>
-      <c r="S21" s="244"/>
-      <c r="T21" s="244"/>
-      <c r="U21" s="244"/>
-      <c r="V21" s="244"/>
-      <c r="W21" s="244"/>
-      <c r="X21" s="244"/>
-      <c r="Y21" s="244"/>
-      <c r="Z21" s="244"/>
-      <c r="AA21" s="244"/>
-      <c r="AB21" s="244"/>
-      <c r="AC21" s="244"/>
-      <c r="AD21" s="244"/>
-      <c r="AE21" s="244"/>
-      <c r="AF21" s="244"/>
-      <c r="AG21" s="244"/>
-      <c r="AH21" s="244"/>
-      <c r="AI21" s="244"/>
-      <c r="AJ21" s="244"/>
-      <c r="AK21" s="244"/>
-      <c r="AL21" s="244"/>
-      <c r="AM21" s="244"/>
-      <c r="AN21" s="244"/>
-      <c r="AO21" s="249"/>
+      <c r="Q21" s="244"/>
+      <c r="R21" s="245"/>
+      <c r="S21" s="245"/>
+      <c r="T21" s="245"/>
+      <c r="U21" s="245"/>
+      <c r="V21" s="245"/>
+      <c r="W21" s="245"/>
+      <c r="X21" s="245"/>
+      <c r="Y21" s="245"/>
+      <c r="Z21" s="245"/>
+      <c r="AA21" s="245"/>
+      <c r="AB21" s="245"/>
+      <c r="AC21" s="245"/>
+      <c r="AD21" s="245"/>
+      <c r="AE21" s="245"/>
+      <c r="AF21" s="245"/>
+      <c r="AG21" s="245"/>
+      <c r="AH21" s="245"/>
+      <c r="AI21" s="245"/>
+      <c r="AJ21" s="245"/>
+      <c r="AK21" s="245"/>
+      <c r="AL21" s="245"/>
+      <c r="AM21" s="245"/>
+      <c r="AN21" s="245"/>
+      <c r="AO21" s="250"/>
     </row>
     <row r="22" customHeight="1" spans="1:41">
       <c r="A22" s="113"/>
-      <c r="B22" s="242"/>
-      <c r="C22" s="243"/>
-      <c r="D22" s="244"/>
-      <c r="E22" s="244"/>
-      <c r="F22" s="244"/>
-      <c r="G22" s="244"/>
-      <c r="H22" s="244"/>
-      <c r="I22" s="244"/>
-      <c r="J22" s="244"/>
+      <c r="B22" s="243"/>
+      <c r="C22" s="244"/>
+      <c r="D22" s="245"/>
+      <c r="E22" s="245"/>
+      <c r="F22" s="245"/>
+      <c r="G22" s="245"/>
+      <c r="H22" s="245"/>
+      <c r="I22" s="245"/>
+      <c r="J22" s="245"/>
       <c r="K22" s="113"/>
       <c r="L22" s="113"/>
       <c r="M22" s="113"/>
       <c r="N22" s="113"/>
       <c r="O22" s="113"/>
       <c r="P22" s="113"/>
-      <c r="Q22" s="243"/>
-      <c r="R22" s="244"/>
-      <c r="S22" s="244"/>
-      <c r="T22" s="244"/>
-      <c r="U22" s="244"/>
-      <c r="V22" s="244"/>
-      <c r="W22" s="244"/>
-      <c r="X22" s="244"/>
-      <c r="Y22" s="244"/>
-      <c r="Z22" s="244"/>
-      <c r="AA22" s="244"/>
-      <c r="AB22" s="244"/>
-      <c r="AC22" s="244"/>
-      <c r="AD22" s="244"/>
-      <c r="AE22" s="244"/>
-      <c r="AF22" s="244"/>
-      <c r="AG22" s="244"/>
-      <c r="AH22" s="244"/>
-      <c r="AI22" s="244"/>
-      <c r="AJ22" s="244"/>
-      <c r="AK22" s="244"/>
-      <c r="AL22" s="244"/>
-      <c r="AM22" s="244"/>
-      <c r="AN22" s="244"/>
-      <c r="AO22" s="249"/>
+      <c r="Q22" s="244"/>
+      <c r="R22" s="245"/>
+      <c r="S22" s="245"/>
+      <c r="T22" s="245"/>
+      <c r="U22" s="245"/>
+      <c r="V22" s="245"/>
+      <c r="W22" s="245"/>
+      <c r="X22" s="245"/>
+      <c r="Y22" s="245"/>
+      <c r="Z22" s="245"/>
+      <c r="AA22" s="245"/>
+      <c r="AB22" s="245"/>
+      <c r="AC22" s="245"/>
+      <c r="AD22" s="245"/>
+      <c r="AE22" s="245"/>
+      <c r="AF22" s="245"/>
+      <c r="AG22" s="245"/>
+      <c r="AH22" s="245"/>
+      <c r="AI22" s="245"/>
+      <c r="AJ22" s="245"/>
+      <c r="AK22" s="245"/>
+      <c r="AL22" s="245"/>
+      <c r="AM22" s="245"/>
+      <c r="AN22" s="245"/>
+      <c r="AO22" s="250"/>
     </row>
     <row r="23" customHeight="1" spans="1:41">
       <c r="A23" s="113"/>
-      <c r="B23" s="242"/>
-      <c r="C23" s="243"/>
-      <c r="D23" s="244"/>
-      <c r="E23" s="244"/>
-      <c r="F23" s="244"/>
-      <c r="G23" s="244"/>
-      <c r="H23" s="244"/>
-      <c r="I23" s="244"/>
-      <c r="J23" s="244"/>
+      <c r="B23" s="243"/>
+      <c r="C23" s="244"/>
+      <c r="D23" s="245"/>
+      <c r="E23" s="245"/>
+      <c r="F23" s="245"/>
+      <c r="G23" s="245"/>
+      <c r="H23" s="245"/>
+      <c r="I23" s="245"/>
+      <c r="J23" s="245"/>
       <c r="K23" s="113"/>
       <c r="L23" s="113"/>
       <c r="M23" s="113"/>
       <c r="N23" s="113"/>
       <c r="O23" s="113"/>
       <c r="P23" s="113"/>
-      <c r="Q23" s="243"/>
-      <c r="R23" s="244"/>
-      <c r="S23" s="244"/>
-      <c r="T23" s="244"/>
-      <c r="U23" s="244"/>
-      <c r="V23" s="244"/>
-      <c r="W23" s="244"/>
-      <c r="X23" s="244"/>
-      <c r="Y23" s="244"/>
-      <c r="Z23" s="244"/>
-      <c r="AA23" s="244"/>
-      <c r="AB23" s="244"/>
-      <c r="AC23" s="244"/>
-      <c r="AD23" s="244"/>
-      <c r="AE23" s="244"/>
-      <c r="AF23" s="244"/>
-      <c r="AG23" s="244"/>
-      <c r="AH23" s="244"/>
-      <c r="AI23" s="244"/>
-      <c r="AJ23" s="244"/>
-      <c r="AK23" s="244"/>
-      <c r="AL23" s="244"/>
-      <c r="AM23" s="244"/>
-      <c r="AN23" s="244"/>
-      <c r="AO23" s="249"/>
+      <c r="Q23" s="244"/>
+      <c r="R23" s="245"/>
+      <c r="S23" s="245"/>
+      <c r="T23" s="245"/>
+      <c r="U23" s="245"/>
+      <c r="V23" s="245"/>
+      <c r="W23" s="245"/>
+      <c r="X23" s="245"/>
+      <c r="Y23" s="245"/>
+      <c r="Z23" s="245"/>
+      <c r="AA23" s="245"/>
+      <c r="AB23" s="245"/>
+      <c r="AC23" s="245"/>
+      <c r="AD23" s="245"/>
+      <c r="AE23" s="245"/>
+      <c r="AF23" s="245"/>
+      <c r="AG23" s="245"/>
+      <c r="AH23" s="245"/>
+      <c r="AI23" s="245"/>
+      <c r="AJ23" s="245"/>
+      <c r="AK23" s="245"/>
+      <c r="AL23" s="245"/>
+      <c r="AM23" s="245"/>
+      <c r="AN23" s="245"/>
+      <c r="AO23" s="250"/>
     </row>
     <row r="24" customHeight="1" spans="1:41">
       <c r="A24" s="113"/>
       <c r="B24" s="113"/>
-      <c r="C24" s="243"/>
-      <c r="D24" s="244"/>
-      <c r="E24" s="244"/>
-      <c r="F24" s="244"/>
-      <c r="G24" s="244"/>
-      <c r="H24" s="244"/>
-      <c r="I24" s="244"/>
-      <c r="J24" s="244"/>
+      <c r="C24" s="244"/>
+      <c r="D24" s="245"/>
+      <c r="E24" s="245"/>
+      <c r="F24" s="245"/>
+      <c r="G24" s="245"/>
+      <c r="H24" s="245"/>
+      <c r="I24" s="245"/>
+      <c r="J24" s="245"/>
       <c r="K24" s="113"/>
       <c r="L24" s="113"/>
       <c r="M24" s="113"/>
       <c r="N24" s="113"/>
       <c r="O24" s="113"/>
       <c r="P24" s="113"/>
-      <c r="Q24" s="243"/>
-      <c r="R24" s="244"/>
-      <c r="S24" s="244"/>
-      <c r="T24" s="244"/>
-      <c r="U24" s="244"/>
-      <c r="V24" s="244"/>
-      <c r="W24" s="244"/>
-      <c r="X24" s="244"/>
-      <c r="Y24" s="244"/>
-      <c r="Z24" s="244"/>
-      <c r="AA24" s="244"/>
-      <c r="AB24" s="244"/>
-      <c r="AC24" s="244"/>
-      <c r="AD24" s="244"/>
-      <c r="AE24" s="244"/>
-      <c r="AF24" s="244"/>
-      <c r="AG24" s="244"/>
-      <c r="AH24" s="244"/>
-      <c r="AI24" s="244"/>
-      <c r="AJ24" s="244"/>
-      <c r="AK24" s="244"/>
-      <c r="AL24" s="244"/>
-      <c r="AM24" s="244"/>
-      <c r="AN24" s="244"/>
-      <c r="AO24" s="249"/>
+      <c r="Q24" s="244"/>
+      <c r="R24" s="245"/>
+      <c r="S24" s="245"/>
+      <c r="T24" s="245"/>
+      <c r="U24" s="245"/>
+      <c r="V24" s="245"/>
+      <c r="W24" s="245"/>
+      <c r="X24" s="245"/>
+      <c r="Y24" s="245"/>
+      <c r="Z24" s="245"/>
+      <c r="AA24" s="245"/>
+      <c r="AB24" s="245"/>
+      <c r="AC24" s="245"/>
+      <c r="AD24" s="245"/>
+      <c r="AE24" s="245"/>
+      <c r="AF24" s="245"/>
+      <c r="AG24" s="245"/>
+      <c r="AH24" s="245"/>
+      <c r="AI24" s="245"/>
+      <c r="AJ24" s="245"/>
+      <c r="AK24" s="245"/>
+      <c r="AL24" s="245"/>
+      <c r="AM24" s="245"/>
+      <c r="AN24" s="245"/>
+      <c r="AO24" s="250"/>
     </row>
     <row r="25" customHeight="1" spans="1:41">
       <c r="A25" s="113"/>
       <c r="B25" s="113"/>
-      <c r="C25" s="243"/>
-      <c r="D25" s="244"/>
-      <c r="E25" s="244"/>
-      <c r="F25" s="244"/>
-      <c r="G25" s="244"/>
-      <c r="H25" s="244"/>
-      <c r="I25" s="244"/>
-      <c r="J25" s="244"/>
+      <c r="C25" s="244"/>
+      <c r="D25" s="245"/>
+      <c r="E25" s="245"/>
+      <c r="F25" s="245"/>
+      <c r="G25" s="245"/>
+      <c r="H25" s="245"/>
+      <c r="I25" s="245"/>
+      <c r="J25" s="245"/>
       <c r="K25" s="113"/>
       <c r="L25" s="113"/>
       <c r="M25" s="113"/>
       <c r="N25" s="113"/>
       <c r="O25" s="113"/>
       <c r="P25" s="113"/>
-      <c r="Q25" s="243"/>
-      <c r="R25" s="244"/>
-      <c r="S25" s="244"/>
-      <c r="T25" s="244"/>
-      <c r="U25" s="244"/>
-      <c r="V25" s="244"/>
-      <c r="W25" s="244"/>
-      <c r="X25" s="244"/>
-      <c r="Y25" s="244"/>
-      <c r="Z25" s="244"/>
-      <c r="AA25" s="244"/>
-      <c r="AB25" s="244"/>
-      <c r="AC25" s="244"/>
-      <c r="AD25" s="244"/>
-      <c r="AE25" s="244"/>
-      <c r="AF25" s="244"/>
-      <c r="AG25" s="244"/>
-      <c r="AH25" s="244"/>
-      <c r="AI25" s="244"/>
-      <c r="AJ25" s="244"/>
-      <c r="AK25" s="244"/>
-      <c r="AL25" s="244"/>
-      <c r="AM25" s="244"/>
-      <c r="AN25" s="244"/>
-      <c r="AO25" s="249"/>
+      <c r="Q25" s="244"/>
+      <c r="R25" s="245"/>
+      <c r="S25" s="245"/>
+      <c r="T25" s="245"/>
+      <c r="U25" s="245"/>
+      <c r="V25" s="245"/>
+      <c r="W25" s="245"/>
+      <c r="X25" s="245"/>
+      <c r="Y25" s="245"/>
+      <c r="Z25" s="245"/>
+      <c r="AA25" s="245"/>
+      <c r="AB25" s="245"/>
+      <c r="AC25" s="245"/>
+      <c r="AD25" s="245"/>
+      <c r="AE25" s="245"/>
+      <c r="AF25" s="245"/>
+      <c r="AG25" s="245"/>
+      <c r="AH25" s="245"/>
+      <c r="AI25" s="245"/>
+      <c r="AJ25" s="245"/>
+      <c r="AK25" s="245"/>
+      <c r="AL25" s="245"/>
+      <c r="AM25" s="245"/>
+      <c r="AN25" s="245"/>
+      <c r="AO25" s="250"/>
     </row>
     <row r="26" customHeight="1" spans="1:41">
       <c r="A26" s="113"/>
       <c r="B26" s="113"/>
-      <c r="C26" s="243"/>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="244"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="244"/>
+      <c r="C26" s="244"/>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
       <c r="K26" s="113"/>
       <c r="L26" s="113"/>
       <c r="M26" s="113"/>
       <c r="N26" s="113"/>
       <c r="O26" s="113"/>
       <c r="P26" s="113"/>
-      <c r="Q26" s="243"/>
-      <c r="R26" s="244"/>
-      <c r="S26" s="244"/>
-      <c r="T26" s="244"/>
-      <c r="U26" s="244"/>
-      <c r="V26" s="244"/>
-      <c r="W26" s="244"/>
-      <c r="X26" s="244"/>
-      <c r="Y26" s="244"/>
-      <c r="Z26" s="244"/>
-      <c r="AA26" s="244"/>
-      <c r="AB26" s="244"/>
-      <c r="AC26" s="244"/>
-      <c r="AD26" s="244"/>
-      <c r="AE26" s="244"/>
-      <c r="AF26" s="244"/>
-      <c r="AG26" s="244"/>
-      <c r="AH26" s="244"/>
-      <c r="AI26" s="244"/>
-      <c r="AJ26" s="244"/>
-      <c r="AK26" s="244"/>
-      <c r="AL26" s="244"/>
-      <c r="AM26" s="244"/>
-      <c r="AN26" s="244"/>
-      <c r="AO26" s="249"/>
+      <c r="Q26" s="244"/>
+      <c r="R26" s="245"/>
+      <c r="S26" s="245"/>
+      <c r="T26" s="245"/>
+      <c r="U26" s="245"/>
+      <c r="V26" s="245"/>
+      <c r="W26" s="245"/>
+      <c r="X26" s="245"/>
+      <c r="Y26" s="245"/>
+      <c r="Z26" s="245"/>
+      <c r="AA26" s="245"/>
+      <c r="AB26" s="245"/>
+      <c r="AC26" s="245"/>
+      <c r="AD26" s="245"/>
+      <c r="AE26" s="245"/>
+      <c r="AF26" s="245"/>
+      <c r="AG26" s="245"/>
+      <c r="AH26" s="245"/>
+      <c r="AI26" s="245"/>
+      <c r="AJ26" s="245"/>
+      <c r="AK26" s="245"/>
+      <c r="AL26" s="245"/>
+      <c r="AM26" s="245"/>
+      <c r="AN26" s="245"/>
+      <c r="AO26" s="250"/>
     </row>
     <row r="27" customHeight="1" spans="1:41">
       <c r="A27" s="113"/>
       <c r="B27" s="113"/>
-      <c r="C27" s="243"/>
-      <c r="D27" s="244"/>
-      <c r="E27" s="244"/>
-      <c r="F27" s="244"/>
-      <c r="G27" s="244"/>
-      <c r="H27" s="244"/>
-      <c r="I27" s="244"/>
-      <c r="J27" s="244"/>
+      <c r="C27" s="244"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="245"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
       <c r="K27" s="113"/>
       <c r="L27" s="113"/>
       <c r="M27" s="113"/>
       <c r="N27" s="113"/>
       <c r="O27" s="113"/>
       <c r="P27" s="113"/>
-      <c r="Q27" s="243"/>
-      <c r="R27" s="244"/>
-      <c r="S27" s="244"/>
-      <c r="T27" s="244"/>
-      <c r="U27" s="244"/>
-      <c r="V27" s="244"/>
-      <c r="W27" s="244"/>
-      <c r="X27" s="244"/>
-      <c r="Y27" s="244"/>
-      <c r="Z27" s="244"/>
-      <c r="AA27" s="244"/>
-      <c r="AB27" s="244"/>
-      <c r="AC27" s="244"/>
-      <c r="AD27" s="244"/>
-      <c r="AE27" s="244"/>
-      <c r="AF27" s="244"/>
-      <c r="AG27" s="244"/>
-      <c r="AH27" s="244"/>
-      <c r="AI27" s="244"/>
-      <c r="AJ27" s="244"/>
-      <c r="AK27" s="244"/>
-      <c r="AL27" s="244"/>
-      <c r="AM27" s="244"/>
-      <c r="AN27" s="244"/>
-      <c r="AO27" s="249"/>
+      <c r="Q27" s="244"/>
+      <c r="R27" s="245"/>
+      <c r="S27" s="245"/>
+      <c r="T27" s="245"/>
+      <c r="U27" s="245"/>
+      <c r="V27" s="245"/>
+      <c r="W27" s="245"/>
+      <c r="X27" s="245"/>
+      <c r="Y27" s="245"/>
+      <c r="Z27" s="245"/>
+      <c r="AA27" s="245"/>
+      <c r="AB27" s="245"/>
+      <c r="AC27" s="245"/>
+      <c r="AD27" s="245"/>
+      <c r="AE27" s="245"/>
+      <c r="AF27" s="245"/>
+      <c r="AG27" s="245"/>
+      <c r="AH27" s="245"/>
+      <c r="AI27" s="245"/>
+      <c r="AJ27" s="245"/>
+      <c r="AK27" s="245"/>
+      <c r="AL27" s="245"/>
+      <c r="AM27" s="245"/>
+      <c r="AN27" s="245"/>
+      <c r="AO27" s="250"/>
     </row>
     <row r="28" customHeight="1" spans="1:41">
       <c r="A28" s="113"/>
       <c r="B28" s="113"/>
-      <c r="C28" s="243"/>
-      <c r="D28" s="244"/>
-      <c r="E28" s="244"/>
-      <c r="F28" s="244"/>
-      <c r="G28" s="244"/>
-      <c r="H28" s="244"/>
-      <c r="I28" s="244"/>
-      <c r="J28" s="244"/>
+      <c r="C28" s="244"/>
+      <c r="D28" s="245"/>
+      <c r="E28" s="245"/>
+      <c r="F28" s="245"/>
+      <c r="G28" s="245"/>
+      <c r="H28" s="245"/>
+      <c r="I28" s="245"/>
+      <c r="J28" s="245"/>
       <c r="K28" s="113"/>
       <c r="L28" s="113"/>
       <c r="M28" s="113"/>
       <c r="N28" s="113"/>
       <c r="O28" s="113"/>
       <c r="P28" s="113"/>
-      <c r="Q28" s="243"/>
-      <c r="R28" s="244"/>
-      <c r="S28" s="244"/>
-      <c r="T28" s="244"/>
-      <c r="U28" s="244"/>
-      <c r="V28" s="244"/>
-      <c r="W28" s="244"/>
-      <c r="X28" s="244"/>
-      <c r="Y28" s="244"/>
-      <c r="Z28" s="244"/>
-      <c r="AA28" s="244"/>
-      <c r="AB28" s="244"/>
-      <c r="AC28" s="244"/>
-      <c r="AD28" s="244"/>
-      <c r="AE28" s="244"/>
-      <c r="AF28" s="244"/>
-      <c r="AG28" s="244"/>
-      <c r="AH28" s="244"/>
-      <c r="AI28" s="244"/>
-      <c r="AJ28" s="244"/>
-      <c r="AK28" s="244"/>
-      <c r="AL28" s="244"/>
-      <c r="AM28" s="244"/>
-      <c r="AN28" s="244"/>
-      <c r="AO28" s="249"/>
+      <c r="Q28" s="244"/>
+      <c r="R28" s="245"/>
+      <c r="S28" s="245"/>
+      <c r="T28" s="245"/>
+      <c r="U28" s="245"/>
+      <c r="V28" s="245"/>
+      <c r="W28" s="245"/>
+      <c r="X28" s="245"/>
+      <c r="Y28" s="245"/>
+      <c r="Z28" s="245"/>
+      <c r="AA28" s="245"/>
+      <c r="AB28" s="245"/>
+      <c r="AC28" s="245"/>
+      <c r="AD28" s="245"/>
+      <c r="AE28" s="245"/>
+      <c r="AF28" s="245"/>
+      <c r="AG28" s="245"/>
+      <c r="AH28" s="245"/>
+      <c r="AI28" s="245"/>
+      <c r="AJ28" s="245"/>
+      <c r="AK28" s="245"/>
+      <c r="AL28" s="245"/>
+      <c r="AM28" s="245"/>
+      <c r="AN28" s="245"/>
+      <c r="AO28" s="250"/>
     </row>
     <row r="29" customHeight="1" spans="1:41">
       <c r="A29" s="113"/>
       <c r="B29" s="113"/>
-      <c r="C29" s="243"/>
-      <c r="D29" s="244"/>
-      <c r="E29" s="244"/>
-      <c r="F29" s="244"/>
-      <c r="G29" s="244"/>
-      <c r="H29" s="244"/>
-      <c r="I29" s="244"/>
-      <c r="J29" s="244"/>
+      <c r="C29" s="244"/>
+      <c r="D29" s="245"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
+      <c r="J29" s="245"/>
       <c r="K29" s="113"/>
       <c r="L29" s="113"/>
       <c r="M29" s="113"/>
       <c r="N29" s="113"/>
       <c r="O29" s="113"/>
       <c r="P29" s="113"/>
-      <c r="Q29" s="243"/>
-      <c r="R29" s="244"/>
-      <c r="S29" s="244"/>
-      <c r="T29" s="244"/>
-      <c r="U29" s="244"/>
-      <c r="V29" s="244"/>
-      <c r="W29" s="244"/>
-      <c r="X29" s="244"/>
-      <c r="Y29" s="244"/>
-      <c r="Z29" s="244"/>
-      <c r="AA29" s="244"/>
-      <c r="AB29" s="244"/>
-      <c r="AC29" s="244"/>
-      <c r="AD29" s="244"/>
-      <c r="AE29" s="244"/>
-      <c r="AF29" s="244"/>
-      <c r="AG29" s="244"/>
-      <c r="AH29" s="244"/>
-      <c r="AI29" s="244"/>
-      <c r="AJ29" s="244"/>
-      <c r="AK29" s="244"/>
-      <c r="AL29" s="244"/>
-      <c r="AM29" s="244"/>
-      <c r="AN29" s="244"/>
-      <c r="AO29" s="249"/>
+      <c r="Q29" s="244"/>
+      <c r="R29" s="245"/>
+      <c r="S29" s="245"/>
+      <c r="T29" s="245"/>
+      <c r="U29" s="245"/>
+      <c r="V29" s="245"/>
+      <c r="W29" s="245"/>
+      <c r="X29" s="245"/>
+      <c r="Y29" s="245"/>
+      <c r="Z29" s="245"/>
+      <c r="AA29" s="245"/>
+      <c r="AB29" s="245"/>
+      <c r="AC29" s="245"/>
+      <c r="AD29" s="245"/>
+      <c r="AE29" s="245"/>
+      <c r="AF29" s="245"/>
+      <c r="AG29" s="245"/>
+      <c r="AH29" s="245"/>
+      <c r="AI29" s="245"/>
+      <c r="AJ29" s="245"/>
+      <c r="AK29" s="245"/>
+      <c r="AL29" s="245"/>
+      <c r="AM29" s="245"/>
+      <c r="AN29" s="245"/>
+      <c r="AO29" s="250"/>
     </row>
     <row r="30" customHeight="1" spans="1:41">
       <c r="A30" s="113"/>
       <c r="B30" s="113"/>
-      <c r="C30" s="243"/>
-      <c r="D30" s="244"/>
-      <c r="E30" s="244"/>
-      <c r="F30" s="244"/>
-      <c r="G30" s="244"/>
-      <c r="H30" s="244"/>
-      <c r="I30" s="244"/>
-      <c r="J30" s="244"/>
+      <c r="C30" s="244"/>
+      <c r="D30" s="245"/>
+      <c r="E30" s="245"/>
+      <c r="F30" s="245"/>
+      <c r="G30" s="245"/>
+      <c r="H30" s="245"/>
+      <c r="I30" s="245"/>
+      <c r="J30" s="245"/>
       <c r="K30" s="113"/>
       <c r="L30" s="113"/>
       <c r="M30" s="113"/>
       <c r="N30" s="113"/>
       <c r="O30" s="113"/>
       <c r="P30" s="113"/>
-      <c r="Q30" s="243"/>
-      <c r="R30" s="244"/>
-      <c r="S30" s="244"/>
-      <c r="T30" s="244"/>
-      <c r="U30" s="244"/>
-      <c r="V30" s="244"/>
-      <c r="W30" s="244"/>
-      <c r="X30" s="244"/>
-      <c r="Y30" s="244"/>
-      <c r="Z30" s="244"/>
-      <c r="AA30" s="244"/>
-      <c r="AB30" s="244"/>
-      <c r="AC30" s="244"/>
-      <c r="AD30" s="244"/>
-      <c r="AE30" s="244"/>
-      <c r="AF30" s="244"/>
-      <c r="AG30" s="244"/>
-      <c r="AH30" s="244"/>
-      <c r="AI30" s="244"/>
-      <c r="AJ30" s="244"/>
-      <c r="AK30" s="244"/>
-      <c r="AL30" s="244"/>
-      <c r="AM30" s="244"/>
-      <c r="AN30" s="244"/>
-      <c r="AO30" s="249"/>
+      <c r="Q30" s="244"/>
+      <c r="R30" s="245"/>
+      <c r="S30" s="245"/>
+      <c r="T30" s="245"/>
+      <c r="U30" s="245"/>
+      <c r="V30" s="245"/>
+      <c r="W30" s="245"/>
+      <c r="X30" s="245"/>
+      <c r="Y30" s="245"/>
+      <c r="Z30" s="245"/>
+      <c r="AA30" s="245"/>
+      <c r="AB30" s="245"/>
+      <c r="AC30" s="245"/>
+      <c r="AD30" s="245"/>
+      <c r="AE30" s="245"/>
+      <c r="AF30" s="245"/>
+      <c r="AG30" s="245"/>
+      <c r="AH30" s="245"/>
+      <c r="AI30" s="245"/>
+      <c r="AJ30" s="245"/>
+      <c r="AK30" s="245"/>
+      <c r="AL30" s="245"/>
+      <c r="AM30" s="245"/>
+      <c r="AN30" s="245"/>
+      <c r="AO30" s="250"/>
     </row>
     <row r="31" customHeight="1" spans="1:41">
       <c r="A31" s="113"/>
       <c r="B31" s="113"/>
-      <c r="C31" s="243"/>
-      <c r="D31" s="244"/>
-      <c r="E31" s="244"/>
-      <c r="F31" s="244"/>
-      <c r="G31" s="244"/>
-      <c r="H31" s="244"/>
-      <c r="I31" s="244"/>
-      <c r="J31" s="244"/>
+      <c r="C31" s="244"/>
+      <c r="D31" s="245"/>
+      <c r="E31" s="245"/>
+      <c r="F31" s="245"/>
+      <c r="G31" s="245"/>
+      <c r="H31" s="245"/>
+      <c r="I31" s="245"/>
+      <c r="J31" s="245"/>
       <c r="K31" s="113"/>
       <c r="L31" s="113"/>
       <c r="M31" s="113"/>
       <c r="N31" s="113"/>
       <c r="O31" s="113"/>
       <c r="P31" s="113"/>
-      <c r="Q31" s="243"/>
-      <c r="R31" s="244"/>
-      <c r="S31" s="244"/>
-      <c r="T31" s="244"/>
-      <c r="U31" s="244"/>
-      <c r="V31" s="244"/>
-      <c r="W31" s="244"/>
-      <c r="X31" s="244"/>
-      <c r="Y31" s="244"/>
-      <c r="Z31" s="244"/>
-      <c r="AA31" s="244"/>
-      <c r="AB31" s="244"/>
-      <c r="AC31" s="244"/>
-      <c r="AD31" s="244"/>
-      <c r="AE31" s="244"/>
-      <c r="AF31" s="244"/>
-      <c r="AG31" s="244"/>
-      <c r="AH31" s="244"/>
-      <c r="AI31" s="244"/>
-      <c r="AJ31" s="244"/>
-      <c r="AK31" s="244"/>
-      <c r="AL31" s="244"/>
-      <c r="AM31" s="244"/>
-      <c r="AN31" s="244"/>
-      <c r="AO31" s="249"/>
+      <c r="Q31" s="244"/>
+      <c r="R31" s="245"/>
+      <c r="S31" s="245"/>
+      <c r="T31" s="245"/>
+      <c r="U31" s="245"/>
+      <c r="V31" s="245"/>
+      <c r="W31" s="245"/>
+      <c r="X31" s="245"/>
+      <c r="Y31" s="245"/>
+      <c r="Z31" s="245"/>
+      <c r="AA31" s="245"/>
+      <c r="AB31" s="245"/>
+      <c r="AC31" s="245"/>
+      <c r="AD31" s="245"/>
+      <c r="AE31" s="245"/>
+      <c r="AF31" s="245"/>
+      <c r="AG31" s="245"/>
+      <c r="AH31" s="245"/>
+      <c r="AI31" s="245"/>
+      <c r="AJ31" s="245"/>
+      <c r="AK31" s="245"/>
+      <c r="AL31" s="245"/>
+      <c r="AM31" s="245"/>
+      <c r="AN31" s="245"/>
+      <c r="AO31" s="250"/>
     </row>
     <row r="32" customHeight="1" spans="1:41">
       <c r="A32" s="113"/>
       <c r="B32" s="113"/>
-      <c r="C32" s="243"/>
-      <c r="D32" s="244"/>
-      <c r="E32" s="244"/>
-      <c r="F32" s="244"/>
-      <c r="G32" s="244"/>
-      <c r="H32" s="244"/>
-      <c r="I32" s="244"/>
-      <c r="J32" s="244"/>
+      <c r="C32" s="244"/>
+      <c r="D32" s="245"/>
+      <c r="E32" s="245"/>
+      <c r="F32" s="245"/>
+      <c r="G32" s="245"/>
+      <c r="H32" s="245"/>
+      <c r="I32" s="245"/>
+      <c r="J32" s="245"/>
       <c r="K32" s="113"/>
       <c r="L32" s="113"/>
       <c r="M32" s="113"/>
       <c r="N32" s="113"/>
       <c r="O32" s="113"/>
       <c r="P32" s="113"/>
-      <c r="Q32" s="243"/>
-      <c r="R32" s="244"/>
-      <c r="S32" s="244"/>
-      <c r="T32" s="244"/>
-      <c r="U32" s="244"/>
-      <c r="V32" s="244"/>
-      <c r="W32" s="244"/>
-      <c r="X32" s="244"/>
-      <c r="Y32" s="244"/>
-      <c r="Z32" s="244"/>
-      <c r="AA32" s="244"/>
-      <c r="AB32" s="244"/>
-      <c r="AC32" s="244"/>
-      <c r="AD32" s="244"/>
-      <c r="AE32" s="244"/>
-      <c r="AF32" s="244"/>
-      <c r="AG32" s="244"/>
-      <c r="AH32" s="244"/>
-      <c r="AI32" s="244"/>
-      <c r="AJ32" s="244"/>
-      <c r="AK32" s="244"/>
-      <c r="AL32" s="244"/>
-      <c r="AM32" s="244"/>
-      <c r="AN32" s="244"/>
-      <c r="AO32" s="249"/>
+      <c r="Q32" s="244"/>
+      <c r="R32" s="245"/>
+      <c r="S32" s="245"/>
+      <c r="T32" s="245"/>
+      <c r="U32" s="245"/>
+      <c r="V32" s="245"/>
+      <c r="W32" s="245"/>
+      <c r="X32" s="245"/>
+      <c r="Y32" s="245"/>
+      <c r="Z32" s="245"/>
+      <c r="AA32" s="245"/>
+      <c r="AB32" s="245"/>
+      <c r="AC32" s="245"/>
+      <c r="AD32" s="245"/>
+      <c r="AE32" s="245"/>
+      <c r="AF32" s="245"/>
+      <c r="AG32" s="245"/>
+      <c r="AH32" s="245"/>
+      <c r="AI32" s="245"/>
+      <c r="AJ32" s="245"/>
+      <c r="AK32" s="245"/>
+      <c r="AL32" s="245"/>
+      <c r="AM32" s="245"/>
+      <c r="AN32" s="245"/>
+      <c r="AO32" s="250"/>
     </row>
     <row r="33" customHeight="1" spans="1:41">
       <c r="A33" s="169"/>
@@ -5213,8 +5213,8 @@
     <col min="7" max="7" width="65.7037037037037" style="64" customWidth="1"/>
     <col min="8" max="8" width="20" style="64" customWidth="1"/>
     <col min="9" max="9" width="16.1925925925926" style="64" customWidth="1"/>
-    <col min="10" max="10" width="18.2444444444444" style="64" customWidth="1"/>
-    <col min="11" max="11" width="15.7111111111111" style="64" customWidth="1"/>
+    <col min="10" max="10" width="21.9037037037037" style="64" customWidth="1"/>
+    <col min="11" max="11" width="26.3407407407407" style="64" customWidth="1"/>
     <col min="12" max="16384" width="3.66666666666667" style="64"/>
   </cols>
   <sheetData>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="K10" s="228"/>
     </row>
-    <row r="11" s="98" customFormat="1" ht="27" customHeight="1" spans="1:11">
+    <row r="11" s="98" customFormat="1" ht="41" customHeight="1" spans="1:11">
       <c r="A11" s="178">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -5461,7 +5461,7 @@
         <v>57</v>
       </c>
       <c r="I11" s="182"/>
-      <c r="J11" s="227" t="s">
+      <c r="J11" s="229" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="228"/>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="I13" s="182"/>
       <c r="J13" s="227" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="K13" s="228"/>
     </row>
@@ -5524,23 +5524,23 @@
         <v>7</v>
       </c>
       <c r="B14" s="179" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="179"/>
       <c r="D14" s="179"/>
       <c r="E14" s="179"/>
       <c r="F14" s="179" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="179" t="s">
         <v>65</v>
-      </c>
-      <c r="G14" s="179" t="s">
-        <v>66</v>
       </c>
       <c r="H14" s="177" t="s">
         <v>52</v>
       </c>
       <c r="I14" s="224"/>
       <c r="J14" s="225" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K14" s="226"/>
     </row>
@@ -5550,23 +5550,23 @@
         <v>8</v>
       </c>
       <c r="B15" s="180" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15" s="181"/>
       <c r="D15" s="181"/>
       <c r="E15" s="182"/>
       <c r="F15" s="179" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15" s="179" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H15" s="177" t="s">
         <v>52</v>
       </c>
       <c r="I15" s="224"/>
       <c r="J15" s="225" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K15" s="226"/>
     </row>
@@ -5576,16 +5576,16 @@
         <v>9</v>
       </c>
       <c r="B16" s="179" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" s="179"/>
       <c r="D16" s="179"/>
       <c r="E16" s="179"/>
       <c r="F16" s="179" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="179" t="s">
         <v>72</v>
-      </c>
-      <c r="G16" s="179" t="s">
-        <v>73</v>
       </c>
       <c r="H16" s="177" t="s">
         <v>52</v>
@@ -5602,16 +5602,16 @@
         <v>10</v>
       </c>
       <c r="B17" s="179" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" s="179"/>
       <c r="D17" s="179"/>
       <c r="E17" s="179"/>
       <c r="F17" s="179" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="179" t="s">
         <v>75</v>
-      </c>
-      <c r="G17" s="179" t="s">
-        <v>76</v>
       </c>
       <c r="H17" s="177" t="s">
         <v>52</v>
@@ -5628,23 +5628,23 @@
         <v>11</v>
       </c>
       <c r="B18" s="179" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" s="179"/>
       <c r="D18" s="179"/>
       <c r="E18" s="179"/>
       <c r="F18" s="179" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="179" t="s">
         <v>78</v>
-      </c>
-      <c r="G18" s="179" t="s">
-        <v>79</v>
       </c>
       <c r="H18" s="177" t="s">
         <v>52</v>
       </c>
       <c r="I18" s="224"/>
       <c r="J18" s="225" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K18" s="226"/>
     </row>
@@ -5654,7 +5654,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="179" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C19" s="179"/>
       <c r="D19" s="179"/>
@@ -5663,7 +5663,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="179" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H19" s="177" t="s">
         <v>52</v>
@@ -5680,7 +5680,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="179" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" s="179"/>
       <c r="D20" s="179"/>
@@ -5689,7 +5689,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="179" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H20" s="177" t="s">
         <v>52</v>
@@ -5706,7 +5706,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="179" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" s="179"/>
       <c r="D21" s="179"/>
@@ -5715,7 +5715,7 @@
         <v>50</v>
       </c>
       <c r="G21" s="183" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H21" s="177" t="s">
         <v>52</v>
@@ -5732,7 +5732,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="179" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C22" s="179"/>
       <c r="D22" s="179"/>
@@ -5741,7 +5741,7 @@
         <v>50</v>
       </c>
       <c r="G22" s="183" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H22" s="177" t="s">
         <v>52</v>
@@ -5758,7 +5758,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="179" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C23" s="179"/>
       <c r="D23" s="179"/>
@@ -5767,7 +5767,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="183" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H23" s="177" t="s">
         <v>52</v>
@@ -5784,7 +5784,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="185" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C24" s="185"/>
       <c r="D24" s="185"/>
@@ -5793,16 +5793,16 @@
         <v>50</v>
       </c>
       <c r="G24" s="186" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H24" s="187" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="229"/>
-      <c r="J24" s="230" t="s">
+      <c r="I24" s="230"/>
+      <c r="J24" s="231" t="s">
         <v>52</v>
       </c>
-      <c r="K24" s="231"/>
+      <c r="K24" s="232"/>
     </row>
     <row r="25" s="98" customFormat="1" customHeight="1" spans="2:8">
       <c r="B25" s="188"/>
@@ -5823,18 +5823,18 @@
       <c r="C26" s="192"/>
       <c r="D26" s="192"/>
       <c r="E26" s="193" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F26" s="192" t="s">
         <v>43</v>
       </c>
       <c r="G26" s="194" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H26" s="195"/>
       <c r="I26" s="195"/>
       <c r="J26" s="195"/>
-      <c r="K26" s="232"/>
+      <c r="K26" s="233"/>
     </row>
     <row r="27" s="33" customFormat="1" customHeight="1" spans="1:11">
       <c r="A27" s="192"/>
@@ -5853,11 +5853,11 @@
       <c r="H27" s="197" t="s">
         <v>48</v>
       </c>
-      <c r="I27" s="233"/>
-      <c r="J27" s="234" t="s">
+      <c r="I27" s="234"/>
+      <c r="J27" s="235" t="s">
         <v>49</v>
       </c>
-      <c r="K27" s="235"/>
+      <c r="K27" s="236"/>
     </row>
     <row r="28" s="33" customFormat="1" ht="27" customHeight="1" spans="1:11">
       <c r="A28" s="198">
@@ -5873,7 +5873,7 @@
         <v>50</v>
       </c>
       <c r="G28" s="199" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H28" s="177"/>
       <c r="I28" s="224"/>
@@ -5886,7 +5886,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="203" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29" s="204"/>
       <c r="D29" s="204"/>
@@ -5895,7 +5895,7 @@
         <v>50</v>
       </c>
       <c r="G29" s="203" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H29" s="177"/>
       <c r="I29" s="224"/>
@@ -5908,16 +5908,16 @@
         <v>3</v>
       </c>
       <c r="B30" s="203" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C30" s="204"/>
       <c r="D30" s="204"/>
       <c r="E30" s="204"/>
       <c r="F30" s="205" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G30" s="203" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H30" s="180"/>
       <c r="I30" s="182"/>
@@ -5930,7 +5930,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="206" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" s="207"/>
       <c r="D31" s="207"/>
@@ -5939,7 +5939,7 @@
         <v>50</v>
       </c>
       <c r="G31" s="203" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H31" s="180"/>
       <c r="I31" s="182"/>
@@ -5956,10 +5956,10 @@
       <c r="D32" s="207"/>
       <c r="E32" s="207"/>
       <c r="F32" s="205" t="s">
+        <v>101</v>
+      </c>
+      <c r="G32" s="208" t="s">
         <v>102</v>
-      </c>
-      <c r="G32" s="208" t="s">
-        <v>103</v>
       </c>
       <c r="H32" s="180"/>
       <c r="I32" s="182"/>
@@ -5972,7 +5972,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="206" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C33" s="207"/>
       <c r="D33" s="207"/>
@@ -5981,7 +5981,7 @@
         <v>50</v>
       </c>
       <c r="G33" s="203" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H33" s="180"/>
       <c r="I33" s="182"/>
@@ -5998,10 +5998,10 @@
       <c r="D34" s="207"/>
       <c r="E34" s="207"/>
       <c r="F34" s="205" t="s">
+        <v>105</v>
+      </c>
+      <c r="G34" s="203" t="s">
         <v>106</v>
-      </c>
-      <c r="G34" s="203" t="s">
-        <v>107</v>
       </c>
       <c r="H34" s="177"/>
       <c r="I34" s="224"/>
@@ -6014,7 +6014,7 @@
         <v>8</v>
       </c>
       <c r="B35" s="206" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C35" s="207"/>
       <c r="D35" s="207"/>
@@ -6023,7 +6023,7 @@
         <v>50</v>
       </c>
       <c r="G35" s="203" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H35" s="177"/>
       <c r="I35" s="224"/>
@@ -6040,10 +6040,10 @@
       <c r="D36" s="207"/>
       <c r="E36" s="207"/>
       <c r="F36" s="205" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G36" s="203" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H36" s="177"/>
       <c r="I36" s="224"/>
@@ -6056,7 +6056,7 @@
         <v>10</v>
       </c>
       <c r="B37" s="206" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C37" s="207"/>
       <c r="D37" s="207"/>
@@ -6065,7 +6065,7 @@
         <v>50</v>
       </c>
       <c r="G37" s="203" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H37" s="177"/>
       <c r="I37" s="224"/>
@@ -6082,10 +6082,10 @@
       <c r="D38" s="207"/>
       <c r="E38" s="207"/>
       <c r="F38" s="205" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G38" s="203" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H38" s="177"/>
       <c r="I38" s="224"/>
@@ -6098,7 +6098,7 @@
         <v>12</v>
       </c>
       <c r="B39" s="206" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C39" s="207"/>
       <c r="D39" s="207"/>
@@ -6107,7 +6107,7 @@
         <v>50</v>
       </c>
       <c r="G39" s="203" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H39" s="180"/>
       <c r="I39" s="182"/>
@@ -6124,10 +6124,10 @@
       <c r="D40" s="207"/>
       <c r="E40" s="207"/>
       <c r="F40" s="205" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G40" s="203" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H40" s="180"/>
       <c r="I40" s="182"/>
@@ -6140,7 +6140,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="206" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C41" s="207"/>
       <c r="D41" s="207"/>
@@ -6149,7 +6149,7 @@
         <v>50</v>
       </c>
       <c r="G41" s="203" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H41" s="180"/>
       <c r="I41" s="182"/>
@@ -6166,10 +6166,10 @@
       <c r="D42" s="207"/>
       <c r="E42" s="207"/>
       <c r="F42" s="205" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42" s="203" t="s">
         <v>113</v>
-      </c>
-      <c r="G42" s="203" t="s">
-        <v>114</v>
       </c>
       <c r="H42" s="180"/>
       <c r="I42" s="182"/>
@@ -6182,7 +6182,7 @@
         <v>16</v>
       </c>
       <c r="B43" s="206" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C43" s="207"/>
       <c r="D43" s="207"/>
@@ -6191,7 +6191,7 @@
         <v>50</v>
       </c>
       <c r="G43" s="203" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H43" s="177"/>
       <c r="I43" s="224"/>
@@ -6208,10 +6208,10 @@
       <c r="D44" s="207"/>
       <c r="E44" s="207"/>
       <c r="F44" s="205" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G44" s="203" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H44" s="177"/>
       <c r="I44" s="224"/>
@@ -6224,7 +6224,7 @@
         <v>18</v>
       </c>
       <c r="B45" s="206" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C45" s="207"/>
       <c r="D45" s="207"/>
@@ -6233,7 +6233,7 @@
         <v>50</v>
       </c>
       <c r="G45" s="203" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H45" s="180"/>
       <c r="I45" s="182"/>
@@ -6250,10 +6250,10 @@
       <c r="D46" s="207"/>
       <c r="E46" s="207"/>
       <c r="F46" s="205" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G46" s="203" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H46" s="180"/>
       <c r="I46" s="182"/>
@@ -6266,7 +6266,7 @@
         <v>20</v>
       </c>
       <c r="B47" s="206" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C47" s="207"/>
       <c r="D47" s="207"/>
@@ -6275,7 +6275,7 @@
         <v>50</v>
       </c>
       <c r="G47" s="203" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H47" s="180"/>
       <c r="I47" s="182"/>
@@ -6292,10 +6292,10 @@
       <c r="D48" s="207"/>
       <c r="E48" s="207"/>
       <c r="F48" s="205" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G48" s="203" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H48" s="180"/>
       <c r="I48" s="182"/>
@@ -6308,16 +6308,16 @@
         <v>22</v>
       </c>
       <c r="B49" s="203" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C49" s="204"/>
       <c r="D49" s="204"/>
       <c r="E49" s="204"/>
       <c r="F49" s="205" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G49" s="207" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H49" s="177"/>
       <c r="I49" s="224"/>
@@ -6330,21 +6330,21 @@
         <v>23</v>
       </c>
       <c r="B50" s="210" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C50" s="211"/>
       <c r="D50" s="211"/>
       <c r="E50" s="211"/>
       <c r="F50" s="212" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G50" s="210" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H50" s="187"/>
-      <c r="I50" s="229"/>
+      <c r="I50" s="230"/>
       <c r="J50" s="187"/>
-      <c r="K50" s="229"/>
+      <c r="K50" s="230"/>
     </row>
     <row r="51" s="33" customFormat="1" customHeight="1" spans="1:8">
       <c r="A51" s="213"/>
@@ -6366,18 +6366,18 @@
       <c r="C52" s="192"/>
       <c r="D52" s="192"/>
       <c r="E52" s="193" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F52" s="192" t="s">
         <v>43</v>
       </c>
       <c r="G52" s="194" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H52" s="195"/>
       <c r="I52" s="195"/>
       <c r="J52" s="195"/>
-      <c r="K52" s="232"/>
+      <c r="K52" s="233"/>
     </row>
     <row r="53" s="33" customFormat="1" customHeight="1" spans="1:11">
       <c r="A53" s="192"/>
@@ -6396,18 +6396,18 @@
       <c r="H53" s="197" t="s">
         <v>48</v>
       </c>
-      <c r="I53" s="233"/>
-      <c r="J53" s="234" t="s">
+      <c r="I53" s="234"/>
+      <c r="J53" s="235" t="s">
         <v>49</v>
       </c>
-      <c r="K53" s="235"/>
+      <c r="K53" s="236"/>
     </row>
     <row r="54" s="33" customFormat="1" ht="27" customHeight="1" spans="1:11">
       <c r="A54" s="198">
         <v>1</v>
       </c>
       <c r="B54" s="199" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C54" s="200"/>
       <c r="D54" s="200"/>
@@ -6416,7 +6416,7 @@
         <v>50</v>
       </c>
       <c r="G54" s="199" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H54" s="177"/>
       <c r="I54" s="224"/>
@@ -6429,16 +6429,16 @@
         <v>2</v>
       </c>
       <c r="B55" s="203" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C55" s="204"/>
       <c r="D55" s="204"/>
       <c r="E55" s="204"/>
       <c r="F55" s="205" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G55" s="203" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H55" s="177"/>
       <c r="I55" s="224"/>
@@ -6451,7 +6451,7 @@
         <v>3</v>
       </c>
       <c r="B56" s="206" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C56" s="207"/>
       <c r="D56" s="207"/>
@@ -6460,7 +6460,7 @@
         <v>50</v>
       </c>
       <c r="G56" s="203" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H56" s="180"/>
       <c r="I56" s="182"/>
@@ -6477,10 +6477,10 @@
       <c r="D57" s="207"/>
       <c r="E57" s="207"/>
       <c r="F57" s="205" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G57" s="203" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H57" s="180"/>
       <c r="I57" s="182"/>
@@ -6493,7 +6493,7 @@
         <v>5</v>
       </c>
       <c r="B58" s="206" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C58" s="207"/>
       <c r="D58" s="207"/>
@@ -6502,7 +6502,7 @@
         <v>50</v>
       </c>
       <c r="G58" s="203" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H58" s="180"/>
       <c r="I58" s="182"/>
@@ -6519,10 +6519,10 @@
       <c r="D59" s="207"/>
       <c r="E59" s="207"/>
       <c r="F59" s="205" t="s">
+        <v>105</v>
+      </c>
+      <c r="G59" s="203" t="s">
         <v>106</v>
-      </c>
-      <c r="G59" s="203" t="s">
-        <v>107</v>
       </c>
       <c r="H59" s="180"/>
       <c r="I59" s="182"/>
@@ -6535,7 +6535,7 @@
         <v>7</v>
       </c>
       <c r="B60" s="206" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C60" s="207"/>
       <c r="D60" s="207"/>
@@ -6544,7 +6544,7 @@
         <v>50</v>
       </c>
       <c r="G60" s="203" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H60" s="177"/>
       <c r="I60" s="224"/>
@@ -6561,10 +6561,10 @@
       <c r="D61" s="207"/>
       <c r="E61" s="207"/>
       <c r="F61" s="205" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G61" s="203" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H61" s="177"/>
       <c r="I61" s="224"/>
@@ -6577,7 +6577,7 @@
         <v>9</v>
       </c>
       <c r="B62" s="206" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C62" s="207"/>
       <c r="D62" s="207"/>
@@ -6586,7 +6586,7 @@
         <v>50</v>
       </c>
       <c r="G62" s="203" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H62" s="177"/>
       <c r="I62" s="224"/>
@@ -6603,10 +6603,10 @@
       <c r="D63" s="207"/>
       <c r="E63" s="207"/>
       <c r="F63" s="205" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G63" s="203" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H63" s="177"/>
       <c r="I63" s="224"/>
@@ -6619,7 +6619,7 @@
         <v>11</v>
       </c>
       <c r="B64" s="206" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C64" s="207"/>
       <c r="D64" s="207"/>
@@ -6628,7 +6628,7 @@
         <v>50</v>
       </c>
       <c r="G64" s="203" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H64" s="177"/>
       <c r="I64" s="224"/>
@@ -6645,10 +6645,10 @@
       <c r="D65" s="207"/>
       <c r="E65" s="207"/>
       <c r="F65" s="205" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G65" s="203" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H65" s="180"/>
       <c r="I65" s="182"/>
@@ -6661,7 +6661,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="206" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C66" s="207"/>
       <c r="D66" s="207"/>
@@ -6670,7 +6670,7 @@
         <v>50</v>
       </c>
       <c r="G66" s="203" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H66" s="180"/>
       <c r="I66" s="182"/>
@@ -6687,10 +6687,10 @@
       <c r="D67" s="207"/>
       <c r="E67" s="207"/>
       <c r="F67" s="205" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G67" s="203" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H67" s="180"/>
       <c r="I67" s="182"/>
@@ -6703,7 +6703,7 @@
         <v>15</v>
       </c>
       <c r="B68" s="206" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C68" s="207"/>
       <c r="D68" s="207"/>
@@ -6712,7 +6712,7 @@
         <v>50</v>
       </c>
       <c r="G68" s="203" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H68" s="180"/>
       <c r="I68" s="182"/>
@@ -6729,10 +6729,10 @@
       <c r="D69" s="207"/>
       <c r="E69" s="207"/>
       <c r="F69" s="205" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G69" s="203" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H69" s="177"/>
       <c r="I69" s="224"/>
@@ -6745,7 +6745,7 @@
         <v>17</v>
       </c>
       <c r="B70" s="206" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C70" s="207"/>
       <c r="D70" s="207"/>
@@ -6754,7 +6754,7 @@
         <v>50</v>
       </c>
       <c r="G70" s="203" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H70" s="177"/>
       <c r="I70" s="224"/>
@@ -6771,10 +6771,10 @@
       <c r="D71" s="207"/>
       <c r="E71" s="207"/>
       <c r="F71" s="205" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G71" s="203" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H71" s="180"/>
       <c r="I71" s="182"/>
@@ -6787,7 +6787,7 @@
         <v>19</v>
       </c>
       <c r="B72" s="206" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C72" s="207"/>
       <c r="D72" s="207"/>
@@ -6796,7 +6796,7 @@
         <v>50</v>
       </c>
       <c r="G72" s="203" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H72" s="180"/>
       <c r="I72" s="182"/>
@@ -6813,10 +6813,10 @@
       <c r="D73" s="207"/>
       <c r="E73" s="207"/>
       <c r="F73" s="205" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G73" s="203" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H73" s="180"/>
       <c r="I73" s="182"/>
@@ -6829,16 +6829,16 @@
         <v>21</v>
       </c>
       <c r="B74" s="203" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C74" s="204"/>
       <c r="D74" s="204"/>
       <c r="E74" s="204"/>
       <c r="F74" s="205" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G74" s="207" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H74" s="180"/>
       <c r="I74" s="182"/>
@@ -6851,16 +6851,16 @@
         <v>22</v>
       </c>
       <c r="B75" s="203" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C75" s="204"/>
       <c r="D75" s="204"/>
       <c r="E75" s="204"/>
       <c r="F75" s="205" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G75" s="208" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H75" s="177"/>
       <c r="I75" s="224"/>
@@ -6873,21 +6873,21 @@
         <v>23</v>
       </c>
       <c r="B76" s="210" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C76" s="211"/>
       <c r="D76" s="211"/>
       <c r="E76" s="211"/>
       <c r="F76" s="212" t="s">
-        <v>65</v>
-      </c>
-      <c r="G76" s="236" t="s">
-        <v>137</v>
+        <v>64</v>
+      </c>
+      <c r="G76" s="237" t="s">
+        <v>136</v>
       </c>
       <c r="H76" s="187"/>
-      <c r="I76" s="229"/>
+      <c r="I76" s="230"/>
       <c r="J76" s="187"/>
-      <c r="K76" s="229"/>
+      <c r="K76" s="230"/>
     </row>
   </sheetData>
   <mergeCells count="181">
@@ -7099,7 +7099,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:38">
       <c r="A1" s="65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -7337,7 +7337,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:38">
       <c r="A6" s="75" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B6" s="76"/>
       <c r="C6" s="76"/>
@@ -7379,7 +7379,7 @@
     </row>
     <row r="7" customHeight="1" spans="1:38">
       <c r="A7" s="77" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B7" s="77"/>
       <c r="C7" s="77"/>
@@ -7422,7 +7422,7 @@
     <row r="8" customHeight="1" spans="1:38">
       <c r="A8" s="78"/>
       <c r="B8" s="79" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C8" s="79"/>
       <c r="D8" s="79"/>
@@ -7465,7 +7465,7 @@
       <c r="A9" s="78"/>
       <c r="B9" s="79"/>
       <c r="C9" s="80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9" s="81"/>
       <c r="E9" s="81"/>
@@ -7547,7 +7547,7 @@
       <c r="A11" s="78"/>
       <c r="B11" s="79"/>
       <c r="C11" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D11" s="79"/>
       <c r="E11" s="79"/>
@@ -7612,7 +7612,7 @@
       <c r="A13" s="78"/>
       <c r="B13" s="79"/>
       <c r="C13" s="78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D13" s="79"/>
       <c r="E13" s="79"/>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="79"/>
       <c r="L13" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N13" s="99"/>
       <c r="O13" s="99"/>
@@ -7631,15 +7631,15 @@
       <c r="Q13" s="99"/>
       <c r="R13" s="99"/>
       <c r="U13" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W13" s="99"/>
       <c r="X13" s="99"/>
       <c r="Y13" s="125" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF13" s="126" t="s">
         <v>146</v>
-      </c>
-      <c r="AF13" s="126" t="s">
-        <v>147</v>
       </c>
       <c r="AG13" s="126"/>
       <c r="AJ13" s="90"/>
@@ -7664,44 +7664,44 @@
       <c r="A15" s="78"/>
       <c r="B15" s="79"/>
       <c r="C15" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" s="79"/>
       <c r="E15" s="79"/>
       <c r="F15" s="90"/>
       <c r="G15" s="79"/>
       <c r="J15" s="100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K15" s="101"/>
       <c r="L15" s="101"/>
       <c r="M15" s="102"/>
       <c r="N15" s="100" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O15" s="101"/>
       <c r="P15" s="101"/>
       <c r="Q15" s="102"/>
       <c r="R15" s="114" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S15" s="115"/>
       <c r="T15" s="115"/>
       <c r="U15" s="116"/>
       <c r="V15" s="114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="W15" s="115"/>
       <c r="X15" s="115"/>
       <c r="Y15" s="116"/>
       <c r="Z15" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA15" s="115"/>
       <c r="AB15" s="115"/>
       <c r="AC15" s="116"/>
       <c r="AD15" s="114" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AE15" s="115"/>
       <c r="AF15" s="115"/>
@@ -7721,25 +7721,25 @@
       <c r="F16" s="90"/>
       <c r="G16" s="79"/>
       <c r="J16" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K16" s="104"/>
       <c r="L16" s="104"/>
       <c r="M16" s="105"/>
       <c r="N16" s="106" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O16" s="107"/>
       <c r="P16" s="107"/>
       <c r="Q16" s="117"/>
       <c r="R16" s="118" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="S16" s="119"/>
       <c r="T16" s="119"/>
       <c r="U16" s="120"/>
       <c r="V16" s="106" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W16" s="107"/>
       <c r="X16" s="107"/>
@@ -7766,32 +7766,32 @@
       <c r="A17" s="78"/>
       <c r="B17" s="79"/>
       <c r="C17" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D17" s="79"/>
       <c r="E17" s="79"/>
       <c r="F17" s="90"/>
       <c r="G17" s="79"/>
       <c r="J17" s="103" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K17" s="104"/>
       <c r="L17" s="104"/>
       <c r="M17" s="105"/>
       <c r="N17" s="106" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O17" s="107"/>
       <c r="P17" s="107"/>
       <c r="Q17" s="117"/>
       <c r="R17" s="118" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S17" s="119"/>
       <c r="T17" s="119"/>
       <c r="U17" s="120"/>
       <c r="V17" s="106" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="W17" s="107"/>
       <c r="X17" s="107"/>
@@ -7823,25 +7823,25 @@
       <c r="F18" s="90"/>
       <c r="G18" s="79"/>
       <c r="J18" s="103" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K18" s="104"/>
       <c r="L18" s="104"/>
       <c r="M18" s="105"/>
       <c r="N18" s="106" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O18" s="107"/>
       <c r="P18" s="107"/>
       <c r="Q18" s="117"/>
       <c r="R18" s="118" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S18" s="119"/>
       <c r="T18" s="119"/>
       <c r="U18" s="120"/>
       <c r="V18" s="106" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W18" s="107"/>
       <c r="X18" s="107"/>
@@ -7873,25 +7873,25 @@
       <c r="F19" s="90"/>
       <c r="G19" s="79"/>
       <c r="J19" s="103" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K19" s="104"/>
       <c r="L19" s="104"/>
       <c r="M19" s="105"/>
       <c r="N19" s="106" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O19" s="107"/>
       <c r="P19" s="107"/>
       <c r="Q19" s="117"/>
       <c r="R19" s="118" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S19" s="119"/>
       <c r="T19" s="119"/>
       <c r="U19" s="120"/>
       <c r="V19" s="106" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W19" s="107"/>
       <c r="X19" s="107"/>
@@ -7923,25 +7923,25 @@
       <c r="F20" s="90"/>
       <c r="G20" s="79"/>
       <c r="J20" s="103" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K20" s="104"/>
       <c r="L20" s="104"/>
       <c r="M20" s="105"/>
       <c r="N20" s="106" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O20" s="107"/>
       <c r="P20" s="107"/>
       <c r="Q20" s="117"/>
       <c r="R20" s="118" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S20" s="119"/>
       <c r="T20" s="119"/>
       <c r="U20" s="120"/>
       <c r="V20" s="106" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W20" s="107"/>
       <c r="X20" s="107"/>
@@ -7973,25 +7973,25 @@
       <c r="F21" s="90"/>
       <c r="G21" s="79"/>
       <c r="J21" s="103" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K21" s="104"/>
       <c r="L21" s="104"/>
       <c r="M21" s="105"/>
       <c r="N21" s="106" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O21" s="107"/>
       <c r="P21" s="107"/>
       <c r="Q21" s="117"/>
       <c r="R21" s="118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S21" s="119"/>
       <c r="T21" s="119"/>
       <c r="U21" s="120"/>
       <c r="V21" s="106" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W21" s="107"/>
       <c r="X21" s="107"/>
@@ -8023,37 +8023,37 @@
       <c r="F22" s="90"/>
       <c r="G22" s="79"/>
       <c r="J22" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K22" s="109"/>
       <c r="L22" s="109"/>
       <c r="M22" s="110"/>
       <c r="N22" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O22" s="109"/>
       <c r="P22" s="109"/>
       <c r="Q22" s="110"/>
       <c r="R22" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S22" s="122"/>
       <c r="T22" s="122"/>
       <c r="U22" s="123"/>
       <c r="V22" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W22" s="109"/>
       <c r="X22" s="109"/>
       <c r="Y22" s="110"/>
       <c r="Z22" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA22" s="109"/>
       <c r="AB22" s="109"/>
       <c r="AC22" s="110"/>
       <c r="AD22" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE22" s="109"/>
       <c r="AF22" s="109"/>
@@ -8073,37 +8073,37 @@
       <c r="F23" s="90"/>
       <c r="G23" s="79"/>
       <c r="J23" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K23" s="109"/>
       <c r="L23" s="109"/>
       <c r="M23" s="110"/>
       <c r="N23" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O23" s="109"/>
       <c r="P23" s="109"/>
       <c r="Q23" s="110"/>
       <c r="R23" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S23" s="122"/>
       <c r="T23" s="122"/>
       <c r="U23" s="123"/>
       <c r="V23" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W23" s="109"/>
       <c r="X23" s="109"/>
       <c r="Y23" s="110"/>
       <c r="Z23" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA23" s="109"/>
       <c r="AB23" s="109"/>
       <c r="AC23" s="110"/>
       <c r="AD23" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE23" s="109"/>
       <c r="AF23" s="109"/>
@@ -8123,37 +8123,37 @@
       <c r="F24" s="90"/>
       <c r="G24" s="79"/>
       <c r="J24" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K24" s="109"/>
       <c r="L24" s="109"/>
       <c r="M24" s="110"/>
       <c r="N24" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O24" s="109"/>
       <c r="P24" s="109"/>
       <c r="Q24" s="110"/>
       <c r="R24" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S24" s="122"/>
       <c r="T24" s="122"/>
       <c r="U24" s="123"/>
       <c r="V24" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W24" s="109"/>
       <c r="X24" s="109"/>
       <c r="Y24" s="110"/>
       <c r="Z24" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA24" s="109"/>
       <c r="AB24" s="109"/>
       <c r="AC24" s="110"/>
       <c r="AD24" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE24" s="109"/>
       <c r="AF24" s="109"/>
@@ -8173,37 +8173,37 @@
       <c r="F25" s="90"/>
       <c r="G25" s="79"/>
       <c r="J25" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K25" s="109"/>
       <c r="L25" s="109"/>
       <c r="M25" s="110"/>
       <c r="N25" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O25" s="109"/>
       <c r="P25" s="109"/>
       <c r="Q25" s="110"/>
       <c r="R25" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S25" s="122"/>
       <c r="T25" s="122"/>
       <c r="U25" s="123"/>
       <c r="V25" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W25" s="109"/>
       <c r="X25" s="109"/>
       <c r="Y25" s="110"/>
       <c r="Z25" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA25" s="109"/>
       <c r="AB25" s="109"/>
       <c r="AC25" s="110"/>
       <c r="AD25" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE25" s="109"/>
       <c r="AF25" s="109"/>
@@ -8223,37 +8223,37 @@
       <c r="F26" s="90"/>
       <c r="G26" s="79"/>
       <c r="J26" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K26" s="109"/>
       <c r="L26" s="109"/>
       <c r="M26" s="110"/>
       <c r="N26" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O26" s="109"/>
       <c r="P26" s="109"/>
       <c r="Q26" s="110"/>
       <c r="R26" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S26" s="122"/>
       <c r="T26" s="122"/>
       <c r="U26" s="123"/>
       <c r="V26" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W26" s="109"/>
       <c r="X26" s="109"/>
       <c r="Y26" s="110"/>
       <c r="Z26" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA26" s="109"/>
       <c r="AB26" s="109"/>
       <c r="AC26" s="110"/>
       <c r="AD26" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE26" s="109"/>
       <c r="AF26" s="109"/>
@@ -8273,37 +8273,37 @@
       <c r="F27" s="90"/>
       <c r="G27" s="79"/>
       <c r="J27" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K27" s="109"/>
       <c r="L27" s="109"/>
       <c r="M27" s="110"/>
       <c r="N27" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O27" s="109"/>
       <c r="P27" s="109"/>
       <c r="Q27" s="110"/>
       <c r="R27" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S27" s="122"/>
       <c r="T27" s="122"/>
       <c r="U27" s="123"/>
       <c r="V27" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W27" s="109"/>
       <c r="X27" s="109"/>
       <c r="Y27" s="110"/>
       <c r="Z27" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA27" s="109"/>
       <c r="AB27" s="109"/>
       <c r="AC27" s="110"/>
       <c r="AD27" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE27" s="109"/>
       <c r="AF27" s="109"/>
@@ -8323,37 +8323,37 @@
       <c r="F28" s="90"/>
       <c r="G28" s="79"/>
       <c r="J28" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K28" s="109"/>
       <c r="L28" s="109"/>
       <c r="M28" s="110"/>
       <c r="N28" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O28" s="109"/>
       <c r="P28" s="109"/>
       <c r="Q28" s="110"/>
       <c r="R28" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S28" s="122"/>
       <c r="T28" s="122"/>
       <c r="U28" s="123"/>
       <c r="V28" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W28" s="109"/>
       <c r="X28" s="109"/>
       <c r="Y28" s="110"/>
       <c r="Z28" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA28" s="109"/>
       <c r="AB28" s="109"/>
       <c r="AC28" s="110"/>
       <c r="AD28" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE28" s="109"/>
       <c r="AF28" s="109"/>
@@ -8398,7 +8398,7 @@
       <c r="AE30" s="79"/>
       <c r="AF30" s="79"/>
       <c r="AG30" s="130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AH30" s="130"/>
       <c r="AI30" s="130"/>
@@ -8489,7 +8489,7 @@
     <row r="33" customHeight="1" spans="1:38">
       <c r="A33" s="78"/>
       <c r="B33" s="79" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C33" s="79"/>
       <c r="D33" s="79"/>
@@ -8532,7 +8532,7 @@
       <c r="A34" s="78"/>
       <c r="B34" s="79"/>
       <c r="C34" s="80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D34" s="81"/>
       <c r="E34" s="81"/>
@@ -8614,7 +8614,7 @@
       <c r="A36" s="78"/>
       <c r="B36" s="79"/>
       <c r="C36" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D36" s="79"/>
       <c r="E36" s="79"/>
@@ -8679,7 +8679,7 @@
       <c r="A38" s="78"/>
       <c r="B38" s="79"/>
       <c r="C38" s="78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D38" s="79"/>
       <c r="E38" s="79"/>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="I38" s="79"/>
       <c r="L38" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N38" s="99"/>
       <c r="O38" s="99"/>
@@ -8698,15 +8698,15 @@
       <c r="Q38" s="99"/>
       <c r="R38" s="99"/>
       <c r="U38" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W38" s="99"/>
       <c r="X38" s="99"/>
       <c r="Y38" s="125" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF38" s="126" t="s">
         <v>146</v>
-      </c>
-      <c r="AF38" s="126" t="s">
-        <v>147</v>
       </c>
       <c r="AG38" s="126"/>
       <c r="AJ38" s="90"/>
@@ -8731,44 +8731,44 @@
       <c r="A40" s="78"/>
       <c r="B40" s="79"/>
       <c r="C40" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D40" s="79"/>
       <c r="E40" s="79"/>
       <c r="F40" s="90"/>
       <c r="G40" s="79"/>
       <c r="J40" s="100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K40" s="101"/>
       <c r="L40" s="101"/>
       <c r="M40" s="102"/>
       <c r="N40" s="100" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O40" s="101"/>
       <c r="P40" s="101"/>
       <c r="Q40" s="102"/>
       <c r="R40" s="114" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S40" s="115"/>
       <c r="T40" s="115"/>
       <c r="U40" s="116"/>
       <c r="V40" s="114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="W40" s="115"/>
       <c r="X40" s="115"/>
       <c r="Y40" s="116"/>
       <c r="Z40" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA40" s="115"/>
       <c r="AB40" s="115"/>
       <c r="AC40" s="116"/>
       <c r="AD40" s="114" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AE40" s="115"/>
       <c r="AF40" s="115"/>
@@ -8788,25 +8788,25 @@
       <c r="F41" s="90"/>
       <c r="G41" s="79"/>
       <c r="J41" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K41" s="104"/>
       <c r="L41" s="104"/>
       <c r="M41" s="105"/>
       <c r="N41" s="106" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O41" s="107"/>
       <c r="P41" s="107"/>
       <c r="Q41" s="117"/>
       <c r="R41" s="118" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="S41" s="119"/>
       <c r="T41" s="119"/>
       <c r="U41" s="120"/>
       <c r="V41" s="106" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W41" s="107"/>
       <c r="X41" s="107"/>
@@ -8833,32 +8833,32 @@
       <c r="A42" s="78"/>
       <c r="B42" s="79"/>
       <c r="C42" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D42" s="79"/>
       <c r="E42" s="79"/>
       <c r="F42" s="90"/>
       <c r="G42" s="79"/>
       <c r="J42" s="103" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K42" s="104"/>
       <c r="L42" s="104"/>
       <c r="M42" s="105"/>
       <c r="N42" s="106" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O42" s="107"/>
       <c r="P42" s="107"/>
       <c r="Q42" s="117"/>
       <c r="R42" s="118" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S42" s="119"/>
       <c r="T42" s="119"/>
       <c r="U42" s="120"/>
       <c r="V42" s="106" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="W42" s="107"/>
       <c r="X42" s="107"/>
@@ -8890,25 +8890,25 @@
       <c r="F43" s="90"/>
       <c r="G43" s="79"/>
       <c r="J43" s="103" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K43" s="104"/>
       <c r="L43" s="104"/>
       <c r="M43" s="105"/>
       <c r="N43" s="106" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O43" s="107"/>
       <c r="P43" s="107"/>
       <c r="Q43" s="117"/>
       <c r="R43" s="118" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S43" s="119"/>
       <c r="T43" s="119"/>
       <c r="U43" s="120"/>
       <c r="V43" s="106" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W43" s="107"/>
       <c r="X43" s="107"/>
@@ -8940,25 +8940,25 @@
       <c r="F44" s="90"/>
       <c r="G44" s="79"/>
       <c r="J44" s="103" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K44" s="104"/>
       <c r="L44" s="104"/>
       <c r="M44" s="105"/>
       <c r="N44" s="106" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O44" s="107"/>
       <c r="P44" s="107"/>
       <c r="Q44" s="117"/>
       <c r="R44" s="118" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S44" s="119"/>
       <c r="T44" s="119"/>
       <c r="U44" s="120"/>
       <c r="V44" s="106" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W44" s="107"/>
       <c r="X44" s="107"/>
@@ -8990,25 +8990,25 @@
       <c r="F45" s="90"/>
       <c r="G45" s="79"/>
       <c r="J45" s="103" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K45" s="104"/>
       <c r="L45" s="104"/>
       <c r="M45" s="105"/>
       <c r="N45" s="106" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O45" s="107"/>
       <c r="P45" s="107"/>
       <c r="Q45" s="117"/>
       <c r="R45" s="118" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S45" s="119"/>
       <c r="T45" s="119"/>
       <c r="U45" s="120"/>
       <c r="V45" s="106" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W45" s="107"/>
       <c r="X45" s="107"/>
@@ -9040,25 +9040,25 @@
       <c r="F46" s="90"/>
       <c r="G46" s="79"/>
       <c r="J46" s="103" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K46" s="104"/>
       <c r="L46" s="104"/>
       <c r="M46" s="105"/>
       <c r="N46" s="106" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O46" s="107"/>
       <c r="P46" s="107"/>
       <c r="Q46" s="117"/>
       <c r="R46" s="118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S46" s="119"/>
       <c r="T46" s="119"/>
       <c r="U46" s="120"/>
       <c r="V46" s="106" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W46" s="107"/>
       <c r="X46" s="107"/>
@@ -9090,37 +9090,37 @@
       <c r="F47" s="90"/>
       <c r="G47" s="79"/>
       <c r="J47" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K47" s="109"/>
       <c r="L47" s="109"/>
       <c r="M47" s="110"/>
       <c r="N47" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O47" s="109"/>
       <c r="P47" s="109"/>
       <c r="Q47" s="110"/>
       <c r="R47" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S47" s="122"/>
       <c r="T47" s="122"/>
       <c r="U47" s="123"/>
       <c r="V47" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W47" s="109"/>
       <c r="X47" s="109"/>
       <c r="Y47" s="110"/>
       <c r="Z47" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA47" s="109"/>
       <c r="AB47" s="109"/>
       <c r="AC47" s="110"/>
       <c r="AD47" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE47" s="109"/>
       <c r="AF47" s="109"/>
@@ -9140,37 +9140,37 @@
       <c r="F48" s="90"/>
       <c r="G48" s="79"/>
       <c r="J48" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K48" s="109"/>
       <c r="L48" s="109"/>
       <c r="M48" s="110"/>
       <c r="N48" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O48" s="109"/>
       <c r="P48" s="109"/>
       <c r="Q48" s="110"/>
       <c r="R48" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S48" s="122"/>
       <c r="T48" s="122"/>
       <c r="U48" s="123"/>
       <c r="V48" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W48" s="109"/>
       <c r="X48" s="109"/>
       <c r="Y48" s="110"/>
       <c r="Z48" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA48" s="109"/>
       <c r="AB48" s="109"/>
       <c r="AC48" s="110"/>
       <c r="AD48" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE48" s="109"/>
       <c r="AF48" s="109"/>
@@ -9190,37 +9190,37 @@
       <c r="F49" s="90"/>
       <c r="G49" s="79"/>
       <c r="J49" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K49" s="109"/>
       <c r="L49" s="109"/>
       <c r="M49" s="110"/>
       <c r="N49" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O49" s="109"/>
       <c r="P49" s="109"/>
       <c r="Q49" s="110"/>
       <c r="R49" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S49" s="122"/>
       <c r="T49" s="122"/>
       <c r="U49" s="123"/>
       <c r="V49" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W49" s="109"/>
       <c r="X49" s="109"/>
       <c r="Y49" s="110"/>
       <c r="Z49" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA49" s="109"/>
       <c r="AB49" s="109"/>
       <c r="AC49" s="110"/>
       <c r="AD49" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE49" s="109"/>
       <c r="AF49" s="109"/>
@@ -9240,37 +9240,37 @@
       <c r="F50" s="90"/>
       <c r="G50" s="79"/>
       <c r="J50" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K50" s="109"/>
       <c r="L50" s="109"/>
       <c r="M50" s="110"/>
       <c r="N50" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O50" s="109"/>
       <c r="P50" s="109"/>
       <c r="Q50" s="110"/>
       <c r="R50" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S50" s="122"/>
       <c r="T50" s="122"/>
       <c r="U50" s="123"/>
       <c r="V50" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W50" s="109"/>
       <c r="X50" s="109"/>
       <c r="Y50" s="110"/>
       <c r="Z50" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA50" s="109"/>
       <c r="AB50" s="109"/>
       <c r="AC50" s="110"/>
       <c r="AD50" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE50" s="109"/>
       <c r="AF50" s="109"/>
@@ -9290,37 +9290,37 @@
       <c r="F51" s="90"/>
       <c r="G51" s="79"/>
       <c r="J51" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K51" s="109"/>
       <c r="L51" s="109"/>
       <c r="M51" s="110"/>
       <c r="N51" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O51" s="109"/>
       <c r="P51" s="109"/>
       <c r="Q51" s="110"/>
       <c r="R51" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S51" s="122"/>
       <c r="T51" s="122"/>
       <c r="U51" s="123"/>
       <c r="V51" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W51" s="109"/>
       <c r="X51" s="109"/>
       <c r="Y51" s="110"/>
       <c r="Z51" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA51" s="109"/>
       <c r="AB51" s="109"/>
       <c r="AC51" s="110"/>
       <c r="AD51" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE51" s="109"/>
       <c r="AF51" s="109"/>
@@ -9340,37 +9340,37 @@
       <c r="F52" s="90"/>
       <c r="G52" s="79"/>
       <c r="J52" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K52" s="109"/>
       <c r="L52" s="109"/>
       <c r="M52" s="110"/>
       <c r="N52" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O52" s="109"/>
       <c r="P52" s="109"/>
       <c r="Q52" s="110"/>
       <c r="R52" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S52" s="122"/>
       <c r="T52" s="122"/>
       <c r="U52" s="123"/>
       <c r="V52" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W52" s="109"/>
       <c r="X52" s="109"/>
       <c r="Y52" s="110"/>
       <c r="Z52" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA52" s="109"/>
       <c r="AB52" s="109"/>
       <c r="AC52" s="110"/>
       <c r="AD52" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE52" s="109"/>
       <c r="AF52" s="109"/>
@@ -9390,37 +9390,37 @@
       <c r="F53" s="90"/>
       <c r="G53" s="79"/>
       <c r="J53" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K53" s="109"/>
       <c r="L53" s="109"/>
       <c r="M53" s="110"/>
       <c r="N53" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O53" s="109"/>
       <c r="P53" s="109"/>
       <c r="Q53" s="110"/>
       <c r="R53" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S53" s="122"/>
       <c r="T53" s="122"/>
       <c r="U53" s="123"/>
       <c r="V53" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W53" s="109"/>
       <c r="X53" s="109"/>
       <c r="Y53" s="110"/>
       <c r="Z53" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA53" s="109"/>
       <c r="AB53" s="109"/>
       <c r="AC53" s="110"/>
       <c r="AD53" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE53" s="109"/>
       <c r="AF53" s="109"/>
@@ -9465,7 +9465,7 @@
       <c r="AE55" s="79"/>
       <c r="AF55" s="79"/>
       <c r="AG55" s="130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AH55" s="130"/>
       <c r="AI55" s="130"/>
@@ -9555,7 +9555,7 @@
     </row>
     <row r="58" customHeight="1" spans="1:38">
       <c r="A58" s="77" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B58" s="77"/>
       <c r="C58" s="77"/>
@@ -9598,7 +9598,7 @@
     <row r="59" customHeight="1" spans="1:38">
       <c r="A59" s="78"/>
       <c r="B59" s="79" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C59" s="79"/>
       <c r="D59" s="79"/>
@@ -9641,7 +9641,7 @@
       <c r="A60" s="78"/>
       <c r="B60" s="79"/>
       <c r="C60" s="80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D60" s="81"/>
       <c r="E60" s="81"/>
@@ -9723,7 +9723,7 @@
       <c r="A62" s="78"/>
       <c r="B62" s="79"/>
       <c r="C62" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D62" s="79"/>
       <c r="E62" s="79"/>
@@ -9788,7 +9788,7 @@
       <c r="A64" s="78"/>
       <c r="B64" s="79"/>
       <c r="C64" s="78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D64" s="79"/>
       <c r="E64" s="79"/>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I64" s="79"/>
       <c r="L64" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N64" s="99"/>
       <c r="O64" s="99"/>
@@ -9807,15 +9807,15 @@
       <c r="Q64" s="99"/>
       <c r="R64" s="99"/>
       <c r="U64" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W64" s="99"/>
       <c r="X64" s="99"/>
       <c r="Y64" s="125" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF64" s="126" t="s">
         <v>146</v>
-      </c>
-      <c r="AF64" s="126" t="s">
-        <v>147</v>
       </c>
       <c r="AG64" s="126"/>
       <c r="AJ64" s="90"/>
@@ -9831,7 +9831,7 @@
       <c r="F65" s="90"/>
       <c r="G65" s="79"/>
       <c r="L65" s="131" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AH65" s="79"/>
       <c r="AI65" s="79"/>
@@ -9843,44 +9843,44 @@
       <c r="A66" s="78"/>
       <c r="B66" s="79"/>
       <c r="C66" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D66" s="79"/>
       <c r="E66" s="79"/>
       <c r="F66" s="90"/>
       <c r="G66" s="79"/>
       <c r="J66" s="132" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K66" s="133"/>
       <c r="L66" s="133"/>
       <c r="M66" s="134"/>
       <c r="N66" s="132" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O66" s="133"/>
       <c r="P66" s="133"/>
       <c r="Q66" s="134"/>
       <c r="R66" s="141" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S66" s="142"/>
       <c r="T66" s="142"/>
       <c r="U66" s="143"/>
       <c r="V66" s="141" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="W66" s="142"/>
       <c r="X66" s="142"/>
       <c r="Y66" s="143"/>
       <c r="Z66" s="141" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA66" s="142"/>
       <c r="AB66" s="142"/>
       <c r="AC66" s="143"/>
       <c r="AD66" s="141" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AE66" s="142"/>
       <c r="AF66" s="142"/>
@@ -9900,25 +9900,25 @@
       <c r="F67" s="90"/>
       <c r="G67" s="79"/>
       <c r="J67" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K67" s="104"/>
       <c r="L67" s="104"/>
       <c r="M67" s="105"/>
       <c r="N67" s="106" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O67" s="107"/>
       <c r="P67" s="107"/>
       <c r="Q67" s="117"/>
       <c r="R67" s="118" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="S67" s="119"/>
       <c r="T67" s="119"/>
       <c r="U67" s="120"/>
       <c r="V67" s="106" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W67" s="107"/>
       <c r="X67" s="107"/>
@@ -9945,32 +9945,32 @@
       <c r="A68" s="78"/>
       <c r="B68" s="79"/>
       <c r="C68" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D68" s="79"/>
       <c r="E68" s="79"/>
       <c r="F68" s="90"/>
       <c r="G68" s="79"/>
       <c r="J68" s="103" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K68" s="104"/>
       <c r="L68" s="104"/>
       <c r="M68" s="105"/>
       <c r="N68" s="106" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O68" s="107"/>
       <c r="P68" s="107"/>
       <c r="Q68" s="117"/>
       <c r="R68" s="118" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S68" s="119"/>
       <c r="T68" s="119"/>
       <c r="U68" s="120"/>
       <c r="V68" s="106" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="W68" s="107"/>
       <c r="X68" s="107"/>
@@ -10002,25 +10002,25 @@
       <c r="F69" s="90"/>
       <c r="G69" s="79"/>
       <c r="J69" s="103" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K69" s="104"/>
       <c r="L69" s="104"/>
       <c r="M69" s="105"/>
       <c r="N69" s="106" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O69" s="107"/>
       <c r="P69" s="107"/>
       <c r="Q69" s="117"/>
       <c r="R69" s="118" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S69" s="119"/>
       <c r="T69" s="119"/>
       <c r="U69" s="120"/>
       <c r="V69" s="106" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W69" s="107"/>
       <c r="X69" s="107"/>
@@ -10052,25 +10052,25 @@
       <c r="F70" s="90"/>
       <c r="G70" s="79"/>
       <c r="J70" s="103" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K70" s="104"/>
       <c r="L70" s="104"/>
       <c r="M70" s="105"/>
       <c r="N70" s="106" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O70" s="107"/>
       <c r="P70" s="107"/>
       <c r="Q70" s="117"/>
       <c r="R70" s="118" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S70" s="119"/>
       <c r="T70" s="119"/>
       <c r="U70" s="120"/>
       <c r="V70" s="106" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W70" s="107"/>
       <c r="X70" s="107"/>
@@ -10102,25 +10102,25 @@
       <c r="F71" s="90"/>
       <c r="G71" s="79"/>
       <c r="J71" s="103" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K71" s="104"/>
       <c r="L71" s="104"/>
       <c r="M71" s="105"/>
       <c r="N71" s="106" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O71" s="107"/>
       <c r="P71" s="107"/>
       <c r="Q71" s="117"/>
       <c r="R71" s="118" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S71" s="119"/>
       <c r="T71" s="119"/>
       <c r="U71" s="120"/>
       <c r="V71" s="106" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="W71" s="107"/>
       <c r="X71" s="107"/>
@@ -10152,25 +10152,25 @@
       <c r="F72" s="90"/>
       <c r="G72" s="79"/>
       <c r="J72" s="103" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K72" s="104"/>
       <c r="L72" s="104"/>
       <c r="M72" s="105"/>
       <c r="N72" s="106" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O72" s="107"/>
       <c r="P72" s="107"/>
       <c r="Q72" s="117"/>
       <c r="R72" s="118" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S72" s="119"/>
       <c r="T72" s="119"/>
       <c r="U72" s="120"/>
       <c r="V72" s="106" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W72" s="107"/>
       <c r="X72" s="107"/>
@@ -10202,37 +10202,37 @@
       <c r="F73" s="90"/>
       <c r="G73" s="79"/>
       <c r="J73" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K73" s="109"/>
       <c r="L73" s="109"/>
       <c r="M73" s="110"/>
       <c r="N73" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O73" s="109"/>
       <c r="P73" s="109"/>
       <c r="Q73" s="110"/>
       <c r="R73" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S73" s="122"/>
       <c r="T73" s="122"/>
       <c r="U73" s="123"/>
       <c r="V73" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W73" s="109"/>
       <c r="X73" s="109"/>
       <c r="Y73" s="110"/>
       <c r="Z73" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA73" s="109"/>
       <c r="AB73" s="109"/>
       <c r="AC73" s="110"/>
       <c r="AD73" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE73" s="109"/>
       <c r="AF73" s="109"/>
@@ -10252,37 +10252,37 @@
       <c r="F74" s="90"/>
       <c r="G74" s="79"/>
       <c r="J74" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K74" s="109"/>
       <c r="L74" s="109"/>
       <c r="M74" s="110"/>
       <c r="N74" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O74" s="109"/>
       <c r="P74" s="109"/>
       <c r="Q74" s="110"/>
       <c r="R74" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S74" s="122"/>
       <c r="T74" s="122"/>
       <c r="U74" s="123"/>
       <c r="V74" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W74" s="109"/>
       <c r="X74" s="109"/>
       <c r="Y74" s="110"/>
       <c r="Z74" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA74" s="109"/>
       <c r="AB74" s="109"/>
       <c r="AC74" s="110"/>
       <c r="AD74" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE74" s="109"/>
       <c r="AF74" s="109"/>
@@ -10302,37 +10302,37 @@
       <c r="F75" s="90"/>
       <c r="G75" s="79"/>
       <c r="J75" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K75" s="109"/>
       <c r="L75" s="109"/>
       <c r="M75" s="110"/>
       <c r="N75" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O75" s="109"/>
       <c r="P75" s="109"/>
       <c r="Q75" s="110"/>
       <c r="R75" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S75" s="122"/>
       <c r="T75" s="122"/>
       <c r="U75" s="123"/>
       <c r="V75" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W75" s="109"/>
       <c r="X75" s="109"/>
       <c r="Y75" s="110"/>
       <c r="Z75" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA75" s="109"/>
       <c r="AB75" s="109"/>
       <c r="AC75" s="110"/>
       <c r="AD75" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE75" s="109"/>
       <c r="AF75" s="109"/>
@@ -10352,37 +10352,37 @@
       <c r="F76" s="90"/>
       <c r="G76" s="79"/>
       <c r="J76" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K76" s="109"/>
       <c r="L76" s="109"/>
       <c r="M76" s="110"/>
       <c r="N76" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O76" s="109"/>
       <c r="P76" s="109"/>
       <c r="Q76" s="110"/>
       <c r="R76" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S76" s="122"/>
       <c r="T76" s="122"/>
       <c r="U76" s="123"/>
       <c r="V76" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W76" s="109"/>
       <c r="X76" s="109"/>
       <c r="Y76" s="110"/>
       <c r="Z76" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA76" s="109"/>
       <c r="AB76" s="109"/>
       <c r="AC76" s="110"/>
       <c r="AD76" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE76" s="109"/>
       <c r="AF76" s="109"/>
@@ -10402,37 +10402,37 @@
       <c r="F77" s="90"/>
       <c r="G77" s="79"/>
       <c r="J77" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K77" s="109"/>
       <c r="L77" s="109"/>
       <c r="M77" s="110"/>
       <c r="N77" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O77" s="109"/>
       <c r="P77" s="109"/>
       <c r="Q77" s="110"/>
       <c r="R77" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S77" s="122"/>
       <c r="T77" s="122"/>
       <c r="U77" s="123"/>
       <c r="V77" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W77" s="109"/>
       <c r="X77" s="109"/>
       <c r="Y77" s="110"/>
       <c r="Z77" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA77" s="109"/>
       <c r="AB77" s="109"/>
       <c r="AC77" s="110"/>
       <c r="AD77" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE77" s="109"/>
       <c r="AF77" s="109"/>
@@ -10452,37 +10452,37 @@
       <c r="F78" s="90"/>
       <c r="G78" s="79"/>
       <c r="J78" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K78" s="109"/>
       <c r="L78" s="109"/>
       <c r="M78" s="110"/>
       <c r="N78" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O78" s="109"/>
       <c r="P78" s="109"/>
       <c r="Q78" s="110"/>
       <c r="R78" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S78" s="122"/>
       <c r="T78" s="122"/>
       <c r="U78" s="123"/>
       <c r="V78" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W78" s="109"/>
       <c r="X78" s="109"/>
       <c r="Y78" s="110"/>
       <c r="Z78" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA78" s="109"/>
       <c r="AB78" s="109"/>
       <c r="AC78" s="110"/>
       <c r="AD78" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE78" s="109"/>
       <c r="AF78" s="109"/>
@@ -10502,37 +10502,37 @@
       <c r="F79" s="90"/>
       <c r="G79" s="79"/>
       <c r="J79" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K79" s="109"/>
       <c r="L79" s="109"/>
       <c r="M79" s="110"/>
       <c r="N79" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O79" s="109"/>
       <c r="P79" s="109"/>
       <c r="Q79" s="110"/>
       <c r="R79" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S79" s="122"/>
       <c r="T79" s="122"/>
       <c r="U79" s="123"/>
       <c r="V79" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W79" s="109"/>
       <c r="X79" s="109"/>
       <c r="Y79" s="110"/>
       <c r="Z79" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA79" s="109"/>
       <c r="AB79" s="109"/>
       <c r="AC79" s="110"/>
       <c r="AD79" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE79" s="109"/>
       <c r="AF79" s="109"/>
@@ -10577,7 +10577,7 @@
       <c r="AE81" s="79"/>
       <c r="AF81" s="79"/>
       <c r="AG81" s="130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AH81" s="130"/>
       <c r="AI81" s="130"/>
@@ -10668,7 +10668,7 @@
     <row r="84" customHeight="1" spans="1:38">
       <c r="A84" s="78"/>
       <c r="B84" s="79" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C84" s="79"/>
       <c r="D84" s="79"/>
@@ -10711,7 +10711,7 @@
       <c r="A85" s="78"/>
       <c r="B85" s="79"/>
       <c r="C85" s="80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D85" s="81"/>
       <c r="E85" s="81"/>
@@ -10793,7 +10793,7 @@
       <c r="A87" s="78"/>
       <c r="B87" s="79"/>
       <c r="C87" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D87" s="79"/>
       <c r="E87" s="79"/>
@@ -10858,7 +10858,7 @@
       <c r="A89" s="78"/>
       <c r="B89" s="79"/>
       <c r="C89" s="78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D89" s="79"/>
       <c r="E89" s="79"/>
@@ -10869,7 +10869,7 @@
       </c>
       <c r="I89" s="79"/>
       <c r="L89" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N89" s="99"/>
       <c r="O89" s="99"/>
@@ -10877,15 +10877,15 @@
       <c r="Q89" s="99"/>
       <c r="R89" s="99"/>
       <c r="U89" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W89" s="99"/>
       <c r="X89" s="99"/>
       <c r="Y89" s="125" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF89" s="126" t="s">
         <v>146</v>
-      </c>
-      <c r="AF89" s="126" t="s">
-        <v>147</v>
       </c>
       <c r="AG89" s="126"/>
       <c r="AJ89" s="90"/>
@@ -10910,44 +10910,44 @@
       <c r="A91" s="78"/>
       <c r="B91" s="79"/>
       <c r="C91" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D91" s="79"/>
       <c r="E91" s="79"/>
       <c r="F91" s="90"/>
       <c r="G91" s="79"/>
       <c r="J91" s="100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K91" s="101"/>
       <c r="L91" s="101"/>
       <c r="M91" s="102"/>
       <c r="N91" s="100" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O91" s="101"/>
       <c r="P91" s="101"/>
       <c r="Q91" s="102"/>
       <c r="R91" s="114" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S91" s="115"/>
       <c r="T91" s="115"/>
       <c r="U91" s="116"/>
       <c r="V91" s="114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="W91" s="115"/>
       <c r="X91" s="115"/>
       <c r="Y91" s="116"/>
       <c r="Z91" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA91" s="115"/>
       <c r="AB91" s="115"/>
       <c r="AC91" s="116"/>
       <c r="AD91" s="114" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AE91" s="115"/>
       <c r="AF91" s="115"/>
@@ -10967,25 +10967,25 @@
       <c r="F92" s="90"/>
       <c r="G92" s="79"/>
       <c r="J92" s="135" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K92" s="136"/>
       <c r="L92" s="136"/>
       <c r="M92" s="137"/>
       <c r="N92" s="138" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O92" s="139"/>
       <c r="P92" s="139"/>
       <c r="Q92" s="144"/>
       <c r="R92" s="145" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="S92" s="146"/>
       <c r="T92" s="146"/>
       <c r="U92" s="147"/>
       <c r="V92" s="138" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W92" s="139"/>
       <c r="X92" s="139"/>
@@ -11012,44 +11012,44 @@
       <c r="A93" s="78"/>
       <c r="B93" s="79"/>
       <c r="C93" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D93" s="79"/>
       <c r="E93" s="79"/>
       <c r="F93" s="90"/>
       <c r="G93" s="79"/>
       <c r="J93" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K93" s="109"/>
       <c r="L93" s="109"/>
       <c r="M93" s="110"/>
       <c r="N93" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O93" s="109"/>
       <c r="P93" s="109"/>
       <c r="Q93" s="110"/>
       <c r="R93" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S93" s="122"/>
       <c r="T93" s="122"/>
       <c r="U93" s="123"/>
       <c r="V93" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W93" s="109"/>
       <c r="X93" s="109"/>
       <c r="Y93" s="110"/>
       <c r="Z93" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA93" s="109"/>
       <c r="AB93" s="109"/>
       <c r="AC93" s="110"/>
       <c r="AD93" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE93" s="109"/>
       <c r="AF93" s="109"/>
@@ -11069,37 +11069,37 @@
       <c r="F94" s="90"/>
       <c r="G94" s="79"/>
       <c r="J94" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K94" s="109"/>
       <c r="L94" s="109"/>
       <c r="M94" s="110"/>
       <c r="N94" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O94" s="109"/>
       <c r="P94" s="109"/>
       <c r="Q94" s="110"/>
       <c r="R94" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S94" s="122"/>
       <c r="T94" s="122"/>
       <c r="U94" s="123"/>
       <c r="V94" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W94" s="109"/>
       <c r="X94" s="109"/>
       <c r="Y94" s="110"/>
       <c r="Z94" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA94" s="109"/>
       <c r="AB94" s="109"/>
       <c r="AC94" s="110"/>
       <c r="AD94" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE94" s="109"/>
       <c r="AF94" s="109"/>
@@ -11264,7 +11264,7 @@
       <c r="AE105" s="79"/>
       <c r="AF105" s="79"/>
       <c r="AG105" s="130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AH105" s="130"/>
       <c r="AI105" s="130"/>
@@ -11355,7 +11355,7 @@
     <row r="108" customHeight="1" spans="1:38">
       <c r="A108" s="78"/>
       <c r="B108" s="79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C108" s="79"/>
       <c r="D108" s="79"/>
@@ -11398,7 +11398,7 @@
       <c r="A109" s="78"/>
       <c r="B109" s="79"/>
       <c r="C109" s="80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D109" s="81"/>
       <c r="E109" s="81"/>
@@ -11480,7 +11480,7 @@
       <c r="A111" s="78"/>
       <c r="B111" s="79"/>
       <c r="C111" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D111" s="79"/>
       <c r="E111" s="79"/>
@@ -11545,7 +11545,7 @@
       <c r="A113" s="78"/>
       <c r="B113" s="79"/>
       <c r="C113" s="78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D113" s="79"/>
       <c r="E113" s="79"/>
@@ -11556,25 +11556,25 @@
       </c>
       <c r="I113" s="79"/>
       <c r="L113" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N113" s="99" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O113" s="99"/>
       <c r="P113" s="99"/>
       <c r="Q113" s="99"/>
       <c r="R113" s="99"/>
       <c r="U113" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W113" s="99"/>
       <c r="X113" s="99"/>
       <c r="Y113" s="125" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF113" s="126" t="s">
         <v>146</v>
-      </c>
-      <c r="AF113" s="126" t="s">
-        <v>147</v>
       </c>
       <c r="AG113" s="126"/>
       <c r="AJ113" s="90"/>
@@ -11590,7 +11590,7 @@
       <c r="F114" s="90"/>
       <c r="G114" s="79"/>
       <c r="L114" s="131" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AH114" s="79"/>
       <c r="AI114" s="79"/>
@@ -11602,44 +11602,44 @@
       <c r="A115" s="78"/>
       <c r="B115" s="79"/>
       <c r="C115" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D115" s="79"/>
       <c r="E115" s="79"/>
       <c r="F115" s="90"/>
       <c r="G115" s="79"/>
       <c r="J115" s="132" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K115" s="133"/>
       <c r="L115" s="133"/>
       <c r="M115" s="134"/>
       <c r="N115" s="132" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O115" s="133"/>
       <c r="P115" s="133"/>
       <c r="Q115" s="134"/>
       <c r="R115" s="141" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S115" s="142"/>
       <c r="T115" s="142"/>
       <c r="U115" s="143"/>
       <c r="V115" s="141" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="W115" s="142"/>
       <c r="X115" s="142"/>
       <c r="Y115" s="143"/>
       <c r="Z115" s="141" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA115" s="142"/>
       <c r="AB115" s="142"/>
       <c r="AC115" s="143"/>
       <c r="AD115" s="141" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AE115" s="142"/>
       <c r="AF115" s="142"/>
@@ -11659,25 +11659,25 @@
       <c r="F116" s="90"/>
       <c r="G116" s="79"/>
       <c r="J116" s="135" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K116" s="136"/>
       <c r="L116" s="136"/>
       <c r="M116" s="137"/>
       <c r="N116" s="138" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O116" s="139"/>
       <c r="P116" s="139"/>
       <c r="Q116" s="144"/>
       <c r="R116" s="145" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="S116" s="146"/>
       <c r="T116" s="146"/>
       <c r="U116" s="147"/>
       <c r="V116" s="138" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W116" s="139"/>
       <c r="X116" s="139"/>
@@ -11704,44 +11704,44 @@
       <c r="A117" s="78"/>
       <c r="B117" s="79"/>
       <c r="C117" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D117" s="79"/>
       <c r="E117" s="79"/>
       <c r="F117" s="90"/>
       <c r="G117" s="79"/>
       <c r="J117" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K117" s="109"/>
       <c r="L117" s="109"/>
       <c r="M117" s="110"/>
       <c r="N117" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O117" s="109"/>
       <c r="P117" s="109"/>
       <c r="Q117" s="110"/>
       <c r="R117" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S117" s="122"/>
       <c r="T117" s="122"/>
       <c r="U117" s="123"/>
       <c r="V117" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W117" s="109"/>
       <c r="X117" s="109"/>
       <c r="Y117" s="110"/>
       <c r="Z117" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA117" s="109"/>
       <c r="AB117" s="109"/>
       <c r="AC117" s="110"/>
       <c r="AD117" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE117" s="109"/>
       <c r="AF117" s="109"/>
@@ -11761,37 +11761,37 @@
       <c r="F118" s="90"/>
       <c r="G118" s="79"/>
       <c r="J118" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K118" s="109"/>
       <c r="L118" s="109"/>
       <c r="M118" s="110"/>
       <c r="N118" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O118" s="109"/>
       <c r="P118" s="109"/>
       <c r="Q118" s="110"/>
       <c r="R118" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S118" s="122"/>
       <c r="T118" s="122"/>
       <c r="U118" s="123"/>
       <c r="V118" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W118" s="109"/>
       <c r="X118" s="109"/>
       <c r="Y118" s="110"/>
       <c r="Z118" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA118" s="109"/>
       <c r="AB118" s="109"/>
       <c r="AC118" s="110"/>
       <c r="AD118" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE118" s="109"/>
       <c r="AF118" s="109"/>
@@ -12136,7 +12136,7 @@
       <c r="AE129" s="79"/>
       <c r="AF129" s="79"/>
       <c r="AG129" s="130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AH129" s="130"/>
       <c r="AI129" s="130"/>
@@ -12227,7 +12227,7 @@
     <row r="132" customHeight="1" spans="1:38">
       <c r="A132" s="78"/>
       <c r="B132" s="79" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C132" s="79"/>
       <c r="D132" s="79"/>
@@ -12270,7 +12270,7 @@
       <c r="A133" s="78"/>
       <c r="B133" s="79"/>
       <c r="C133" s="80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D133" s="81"/>
       <c r="E133" s="81"/>
@@ -12352,7 +12352,7 @@
       <c r="A135" s="78"/>
       <c r="B135" s="79"/>
       <c r="C135" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D135" s="79"/>
       <c r="E135" s="79"/>
@@ -12417,7 +12417,7 @@
       <c r="A137" s="78"/>
       <c r="B137" s="79"/>
       <c r="C137" s="78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D137" s="79"/>
       <c r="E137" s="79"/>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="I137" s="79"/>
       <c r="L137" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N137" s="99"/>
       <c r="O137" s="99"/>
@@ -12436,17 +12436,17 @@
       <c r="Q137" s="99"/>
       <c r="R137" s="99"/>
       <c r="U137" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W137" s="99" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X137" s="99"/>
       <c r="Y137" s="125" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF137" s="126" t="s">
         <v>146</v>
-      </c>
-      <c r="AF137" s="126" t="s">
-        <v>147</v>
       </c>
       <c r="AG137" s="126"/>
       <c r="AJ137" s="90"/>
@@ -12472,44 +12472,44 @@
       <c r="A139" s="78"/>
       <c r="B139" s="79"/>
       <c r="C139" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D139" s="79"/>
       <c r="E139" s="79"/>
       <c r="F139" s="90"/>
       <c r="G139" s="79"/>
       <c r="J139" s="100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K139" s="101"/>
       <c r="L139" s="101"/>
       <c r="M139" s="102"/>
       <c r="N139" s="100" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O139" s="101"/>
       <c r="P139" s="101"/>
       <c r="Q139" s="102"/>
       <c r="R139" s="114" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S139" s="115"/>
       <c r="T139" s="115"/>
       <c r="U139" s="116"/>
       <c r="V139" s="114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="W139" s="115"/>
       <c r="X139" s="115"/>
       <c r="Y139" s="116"/>
       <c r="Z139" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA139" s="115"/>
       <c r="AB139" s="115"/>
       <c r="AC139" s="116"/>
       <c r="AD139" s="114" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AE139" s="115"/>
       <c r="AF139" s="115"/>
@@ -12529,25 +12529,25 @@
       <c r="F140" s="90"/>
       <c r="G140" s="79"/>
       <c r="J140" s="103" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K140" s="104"/>
       <c r="L140" s="104"/>
       <c r="M140" s="105"/>
       <c r="N140" s="106" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O140" s="107"/>
       <c r="P140" s="107"/>
       <c r="Q140" s="117"/>
       <c r="R140" s="118" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S140" s="119"/>
       <c r="T140" s="119"/>
       <c r="U140" s="120"/>
       <c r="V140" s="106" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="W140" s="107"/>
       <c r="X140" s="107"/>
@@ -12574,44 +12574,44 @@
       <c r="A141" s="78"/>
       <c r="B141" s="79"/>
       <c r="C141" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D141" s="79"/>
       <c r="E141" s="79"/>
       <c r="F141" s="90"/>
       <c r="G141" s="79"/>
       <c r="J141" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K141" s="109"/>
       <c r="L141" s="109"/>
       <c r="M141" s="110"/>
       <c r="N141" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O141" s="109"/>
       <c r="P141" s="109"/>
       <c r="Q141" s="110"/>
       <c r="R141" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S141" s="122"/>
       <c r="T141" s="122"/>
       <c r="U141" s="123"/>
       <c r="V141" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W141" s="109"/>
       <c r="X141" s="109"/>
       <c r="Y141" s="110"/>
       <c r="Z141" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA141" s="109"/>
       <c r="AB141" s="109"/>
       <c r="AC141" s="110"/>
       <c r="AD141" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE141" s="109"/>
       <c r="AF141" s="109"/>
@@ -12631,37 +12631,37 @@
       <c r="F142" s="90"/>
       <c r="G142" s="79"/>
       <c r="J142" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K142" s="109"/>
       <c r="L142" s="109"/>
       <c r="M142" s="110"/>
       <c r="N142" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O142" s="109"/>
       <c r="P142" s="109"/>
       <c r="Q142" s="110"/>
       <c r="R142" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S142" s="122"/>
       <c r="T142" s="122"/>
       <c r="U142" s="123"/>
       <c r="V142" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W142" s="109"/>
       <c r="X142" s="109"/>
       <c r="Y142" s="110"/>
       <c r="Z142" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA142" s="109"/>
       <c r="AB142" s="109"/>
       <c r="AC142" s="110"/>
       <c r="AD142" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE142" s="109"/>
       <c r="AF142" s="109"/>
@@ -12681,37 +12681,37 @@
       <c r="F143" s="90"/>
       <c r="G143" s="79"/>
       <c r="J143" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K143" s="109"/>
       <c r="L143" s="109"/>
       <c r="M143" s="110"/>
       <c r="N143" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O143" s="109"/>
       <c r="P143" s="109"/>
       <c r="Q143" s="110"/>
       <c r="R143" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S143" s="122"/>
       <c r="T143" s="122"/>
       <c r="U143" s="123"/>
       <c r="V143" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W143" s="109"/>
       <c r="X143" s="109"/>
       <c r="Y143" s="110"/>
       <c r="Z143" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA143" s="109"/>
       <c r="AB143" s="109"/>
       <c r="AC143" s="110"/>
       <c r="AD143" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE143" s="109"/>
       <c r="AF143" s="109"/>
@@ -12862,7 +12862,7 @@
       <c r="AE153" s="79"/>
       <c r="AF153" s="79"/>
       <c r="AG153" s="130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AH153" s="130"/>
       <c r="AI153" s="130"/>
@@ -12953,7 +12953,7 @@
     <row r="156" customHeight="1" spans="1:38">
       <c r="A156" s="78"/>
       <c r="B156" s="79" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C156" s="79"/>
       <c r="D156" s="79"/>
@@ -12996,7 +12996,7 @@
       <c r="A157" s="78"/>
       <c r="B157" s="79"/>
       <c r="C157" s="80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D157" s="81"/>
       <c r="E157" s="81"/>
@@ -13078,7 +13078,7 @@
       <c r="A159" s="78"/>
       <c r="B159" s="79"/>
       <c r="C159" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D159" s="79"/>
       <c r="E159" s="79"/>
@@ -13143,7 +13143,7 @@
       <c r="A161" s="78"/>
       <c r="B161" s="79"/>
       <c r="C161" s="78" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D161" s="79"/>
       <c r="E161" s="79"/>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="I161" s="79"/>
       <c r="L161" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N161" s="99"/>
       <c r="O161" s="99"/>
@@ -13162,17 +13162,17 @@
       <c r="Q161" s="99"/>
       <c r="R161" s="99"/>
       <c r="U161" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="W161" s="99" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X161" s="99"/>
       <c r="Y161" s="125" t="s">
+        <v>145</v>
+      </c>
+      <c r="AF161" s="126" t="s">
         <v>146</v>
-      </c>
-      <c r="AF161" s="126" t="s">
-        <v>147</v>
       </c>
       <c r="AG161" s="126"/>
       <c r="AJ161" s="90"/>
@@ -13188,7 +13188,7 @@
       <c r="F162" s="90"/>
       <c r="G162" s="79"/>
       <c r="L162" s="131" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AH162" s="79"/>
       <c r="AI162" s="79"/>
@@ -13200,44 +13200,44 @@
       <c r="A163" s="78"/>
       <c r="B163" s="79"/>
       <c r="C163" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D163" s="79"/>
       <c r="E163" s="79"/>
       <c r="F163" s="90"/>
       <c r="G163" s="79"/>
       <c r="J163" s="100" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K163" s="101"/>
       <c r="L163" s="101"/>
       <c r="M163" s="102"/>
       <c r="N163" s="100" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O163" s="101"/>
       <c r="P163" s="101"/>
       <c r="Q163" s="102"/>
       <c r="R163" s="114" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S163" s="115"/>
       <c r="T163" s="115"/>
       <c r="U163" s="116"/>
       <c r="V163" s="114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="W163" s="115"/>
       <c r="X163" s="115"/>
       <c r="Y163" s="116"/>
       <c r="Z163" s="114" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA163" s="115"/>
       <c r="AB163" s="115"/>
       <c r="AC163" s="116"/>
       <c r="AD163" s="114" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AE163" s="115"/>
       <c r="AF163" s="115"/>
@@ -13257,25 +13257,25 @@
       <c r="F164" s="90"/>
       <c r="G164" s="79"/>
       <c r="J164" s="103" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K164" s="104"/>
       <c r="L164" s="104"/>
       <c r="M164" s="105"/>
       <c r="N164" s="106" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O164" s="107"/>
       <c r="P164" s="107"/>
       <c r="Q164" s="117"/>
       <c r="R164" s="118" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S164" s="119"/>
       <c r="T164" s="119"/>
       <c r="U164" s="120"/>
       <c r="V164" s="106" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="W164" s="107"/>
       <c r="X164" s="107"/>
@@ -13302,44 +13302,44 @@
       <c r="A165" s="78"/>
       <c r="B165" s="79"/>
       <c r="C165" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D165" s="79"/>
       <c r="E165" s="79"/>
       <c r="F165" s="90"/>
       <c r="G165" s="79"/>
       <c r="J165" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K165" s="109"/>
       <c r="L165" s="109"/>
       <c r="M165" s="110"/>
       <c r="N165" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O165" s="109"/>
       <c r="P165" s="109"/>
       <c r="Q165" s="110"/>
       <c r="R165" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S165" s="122"/>
       <c r="T165" s="122"/>
       <c r="U165" s="123"/>
       <c r="V165" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W165" s="109"/>
       <c r="X165" s="109"/>
       <c r="Y165" s="110"/>
       <c r="Z165" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA165" s="109"/>
       <c r="AB165" s="109"/>
       <c r="AC165" s="110"/>
       <c r="AD165" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE165" s="109"/>
       <c r="AF165" s="109"/>
@@ -13359,37 +13359,37 @@
       <c r="F166" s="90"/>
       <c r="G166" s="79"/>
       <c r="J166" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K166" s="109"/>
       <c r="L166" s="109"/>
       <c r="M166" s="110"/>
       <c r="N166" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O166" s="109"/>
       <c r="P166" s="109"/>
       <c r="Q166" s="110"/>
       <c r="R166" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S166" s="122"/>
       <c r="T166" s="122"/>
       <c r="U166" s="123"/>
       <c r="V166" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W166" s="109"/>
       <c r="X166" s="109"/>
       <c r="Y166" s="110"/>
       <c r="Z166" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA166" s="109"/>
       <c r="AB166" s="109"/>
       <c r="AC166" s="110"/>
       <c r="AD166" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE166" s="109"/>
       <c r="AF166" s="109"/>
@@ -13409,37 +13409,37 @@
       <c r="F167" s="90"/>
       <c r="G167" s="79"/>
       <c r="J167" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K167" s="109"/>
       <c r="L167" s="109"/>
       <c r="M167" s="110"/>
       <c r="N167" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O167" s="109"/>
       <c r="P167" s="109"/>
       <c r="Q167" s="110"/>
       <c r="R167" s="121" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S167" s="122"/>
       <c r="T167" s="122"/>
       <c r="U167" s="123"/>
       <c r="V167" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="W167" s="109"/>
       <c r="X167" s="109"/>
       <c r="Y167" s="110"/>
       <c r="Z167" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AA167" s="109"/>
       <c r="AB167" s="109"/>
       <c r="AC167" s="110"/>
       <c r="AD167" s="108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AE167" s="109"/>
       <c r="AF167" s="109"/>
@@ -13590,7 +13590,7 @@
       <c r="AE177" s="79"/>
       <c r="AF177" s="79"/>
       <c r="AG177" s="130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AH177" s="130"/>
       <c r="AI177" s="130"/>
@@ -13680,7 +13680,7 @@
     </row>
     <row r="180" customHeight="1" spans="1:38">
       <c r="A180" s="77" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B180" s="77"/>
       <c r="C180" s="77"/>
@@ -13723,7 +13723,7 @@
     <row r="181" customHeight="1" spans="1:38">
       <c r="A181" s="78"/>
       <c r="B181" s="79" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C181" s="79"/>
       <c r="D181" s="79"/>
@@ -13765,7 +13765,7 @@
     <row r="182" customHeight="1" spans="1:38">
       <c r="A182" s="78"/>
       <c r="B182" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C182" s="79"/>
       <c r="D182" s="79"/>
@@ -13807,7 +13807,7 @@
     <row r="183" customHeight="1" spans="1:38">
       <c r="A183" s="78"/>
       <c r="B183" s="79" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C183" s="79"/>
       <c r="D183" s="79"/>
@@ -13850,7 +13850,7 @@
       <c r="A184" s="78"/>
       <c r="B184" s="79"/>
       <c r="C184" s="80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D184" s="81"/>
       <c r="E184" s="81"/>
@@ -13932,13 +13932,13 @@
       <c r="A186" s="79"/>
       <c r="B186" s="79"/>
       <c r="C186" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D186" s="79"/>
       <c r="E186" s="79"/>
       <c r="F186" s="90"/>
       <c r="G186" s="79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H186" s="79"/>
       <c r="I186" s="79"/>
@@ -14004,7 +14004,7 @@
       <c r="A188" s="79"/>
       <c r="B188" s="79"/>
       <c r="C188" s="78" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D188" s="79"/>
       <c r="E188" s="79"/>
@@ -14012,7 +14012,7 @@
       <c r="G188" s="79"/>
       <c r="H188" s="91"/>
       <c r="I188" s="79" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M188" s="125"/>
       <c r="N188" s="125"/>
@@ -14042,13 +14042,13 @@
       <c r="F189" s="90"/>
       <c r="G189" s="79"/>
       <c r="I189" s="149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J189" s="150"/>
       <c r="K189" s="150"/>
       <c r="L189" s="151"/>
       <c r="M189" s="152" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N189" s="152"/>
       <c r="O189" s="152"/>
@@ -14079,20 +14079,20 @@
       <c r="A190" s="79"/>
       <c r="B190" s="79"/>
       <c r="C190" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D190" s="79"/>
       <c r="E190" s="79"/>
       <c r="F190" s="90"/>
       <c r="G190" s="79"/>
       <c r="I190" s="149" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J190" s="150"/>
       <c r="K190" s="150"/>
       <c r="L190" s="151"/>
       <c r="M190" s="152" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N190" s="152"/>
       <c r="O190" s="152"/>
@@ -14129,13 +14129,13 @@
       <c r="F191" s="90"/>
       <c r="G191" s="79"/>
       <c r="I191" s="149" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J191" s="150"/>
       <c r="K191" s="150"/>
       <c r="L191" s="151"/>
       <c r="M191" s="152" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N191" s="152"/>
       <c r="O191" s="152"/>
@@ -14167,20 +14167,20 @@
       <c r="A192" s="79"/>
       <c r="B192" s="79"/>
       <c r="C192" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D192" s="79"/>
       <c r="E192" s="79"/>
       <c r="F192" s="90"/>
       <c r="G192" s="79"/>
       <c r="I192" s="149" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J192" s="150"/>
       <c r="K192" s="150"/>
       <c r="L192" s="151"/>
       <c r="M192" s="152" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N192" s="152"/>
       <c r="O192" s="152"/>
@@ -14217,13 +14217,13 @@
       <c r="F193" s="90"/>
       <c r="G193" s="79"/>
       <c r="I193" s="149" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J193" s="150"/>
       <c r="K193" s="150"/>
       <c r="L193" s="151"/>
       <c r="M193" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N193" s="152"/>
       <c r="O193" s="152"/>
@@ -14260,13 +14260,13 @@
       <c r="F194" s="90"/>
       <c r="G194" s="79"/>
       <c r="I194" s="149" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J194" s="150"/>
       <c r="K194" s="150"/>
       <c r="L194" s="151"/>
       <c r="M194" s="106" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N194" s="107"/>
       <c r="O194" s="107"/>
@@ -14303,7 +14303,7 @@
       <c r="F195" s="90"/>
       <c r="G195" s="79"/>
       <c r="I195" s="149" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J195" s="150"/>
       <c r="K195" s="150"/>
@@ -14346,7 +14346,7 @@
       <c r="F196" s="90"/>
       <c r="G196" s="79"/>
       <c r="I196" s="149" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J196" s="150"/>
       <c r="K196" s="150"/>
@@ -14389,7 +14389,7 @@
       <c r="F197" s="90"/>
       <c r="G197" s="79"/>
       <c r="I197" s="157" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J197" s="157"/>
       <c r="K197" s="157"/>
@@ -14460,7 +14460,7 @@
       <c r="F200" s="90"/>
       <c r="G200" s="79"/>
       <c r="I200" s="158" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J200" s="158"/>
       <c r="K200" s="159"/>
@@ -14484,7 +14484,7 @@
       <c r="AC200" s="159"/>
       <c r="AD200" s="159"/>
       <c r="AE200" s="164" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AF200" s="165"/>
       <c r="AI200" s="79"/>
@@ -14629,7 +14629,7 @@
     </row>
     <row r="205" customHeight="1" spans="1:38">
       <c r="A205" s="77" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B205" s="77"/>
       <c r="C205" s="77"/>
@@ -14672,7 +14672,7 @@
     <row r="206" customHeight="1" spans="1:38">
       <c r="A206" s="78"/>
       <c r="B206" s="79" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C206" s="79"/>
       <c r="D206" s="79"/>
@@ -14714,7 +14714,7 @@
     <row r="207" customHeight="1" spans="1:38">
       <c r="A207" s="78"/>
       <c r="B207" s="79" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C207" s="79"/>
       <c r="D207" s="79"/>
@@ -14757,7 +14757,7 @@
       <c r="A208" s="78"/>
       <c r="B208" s="79"/>
       <c r="C208" s="79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D208" s="79"/>
       <c r="E208" s="79"/>
@@ -14799,7 +14799,7 @@
       <c r="A209" s="78"/>
       <c r="B209" s="79"/>
       <c r="C209" s="79" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D209" s="79"/>
       <c r="E209" s="79"/>
@@ -14841,7 +14841,7 @@
       <c r="A210" s="78"/>
       <c r="B210" s="79"/>
       <c r="C210" s="79" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D210" s="79"/>
       <c r="E210" s="79"/>
@@ -14883,7 +14883,7 @@
       <c r="A211" s="78"/>
       <c r="B211" s="79"/>
       <c r="C211" s="79" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D211" s="79"/>
       <c r="E211" s="79"/>
@@ -14925,7 +14925,7 @@
       <c r="A212" s="78"/>
       <c r="B212" s="79"/>
       <c r="C212" s="80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D212" s="81"/>
       <c r="E212" s="81"/>
@@ -15007,13 +15007,13 @@
       <c r="A214" s="79"/>
       <c r="B214" s="79"/>
       <c r="C214" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D214" s="79"/>
       <c r="E214" s="79"/>
       <c r="F214" s="90"/>
       <c r="G214" s="79" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H214" s="79"/>
       <c r="I214" s="79"/>
@@ -15079,7 +15079,7 @@
       <c r="A216" s="79"/>
       <c r="B216" s="79"/>
       <c r="C216" s="78" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D216" s="79"/>
       <c r="E216" s="79"/>
@@ -15087,7 +15087,7 @@
       <c r="G216" s="79"/>
       <c r="H216" s="91"/>
       <c r="I216" s="79" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M216" s="160"/>
       <c r="N216" s="160"/>
@@ -15120,13 +15120,13 @@
       <c r="F217" s="90"/>
       <c r="G217" s="79"/>
       <c r="I217" s="149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J217" s="150"/>
       <c r="K217" s="150"/>
       <c r="L217" s="151"/>
       <c r="M217" s="161" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N217" s="161"/>
       <c r="O217" s="161"/>
@@ -15157,20 +15157,20 @@
       <c r="A218" s="79"/>
       <c r="B218" s="79"/>
       <c r="C218" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D218" s="79"/>
       <c r="E218" s="79"/>
       <c r="F218" s="90"/>
       <c r="G218" s="79"/>
       <c r="I218" s="149" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J218" s="150"/>
       <c r="K218" s="150"/>
       <c r="L218" s="151"/>
       <c r="M218" s="161" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N218" s="161"/>
       <c r="O218" s="161"/>
@@ -15207,13 +15207,13 @@
       <c r="F219" s="90"/>
       <c r="G219" s="79"/>
       <c r="I219" s="149" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J219" s="150"/>
       <c r="K219" s="150"/>
       <c r="L219" s="151"/>
       <c r="M219" s="161" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N219" s="161"/>
       <c r="O219" s="161"/>
@@ -15245,20 +15245,20 @@
       <c r="A220" s="79"/>
       <c r="B220" s="79"/>
       <c r="C220" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D220" s="79"/>
       <c r="E220" s="79"/>
       <c r="F220" s="90"/>
       <c r="G220" s="79"/>
       <c r="I220" s="149" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J220" s="150"/>
       <c r="K220" s="150"/>
       <c r="L220" s="151"/>
       <c r="M220" s="161" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N220" s="161"/>
       <c r="O220" s="161"/>
@@ -15295,13 +15295,13 @@
       <c r="F221" s="90"/>
       <c r="G221" s="79"/>
       <c r="I221" s="149" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J221" s="150"/>
       <c r="K221" s="150"/>
       <c r="L221" s="151"/>
       <c r="M221" s="161" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N221" s="161"/>
       <c r="O221" s="161"/>
@@ -15338,13 +15338,13 @@
       <c r="F222" s="90"/>
       <c r="G222" s="79"/>
       <c r="I222" s="149" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J222" s="150"/>
       <c r="K222" s="150"/>
       <c r="L222" s="151"/>
       <c r="M222" s="106" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N222" s="107"/>
       <c r="O222" s="107"/>
@@ -15381,7 +15381,7 @@
       <c r="F223" s="90"/>
       <c r="G223" s="79"/>
       <c r="I223" s="149" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J223" s="150"/>
       <c r="K223" s="150"/>
@@ -15424,7 +15424,7 @@
       <c r="F224" s="90"/>
       <c r="G224" s="79"/>
       <c r="I224" s="149" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J224" s="150"/>
       <c r="K224" s="150"/>
@@ -15467,7 +15467,7 @@
       <c r="F225" s="90"/>
       <c r="G225" s="79"/>
       <c r="I225" s="157" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J225" s="157"/>
       <c r="K225" s="157"/>
@@ -15538,7 +15538,7 @@
       <c r="F228" s="90"/>
       <c r="G228" s="79"/>
       <c r="I228" s="158" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J228" s="158"/>
       <c r="K228" s="159"/>
@@ -15559,12 +15559,12 @@
       <c r="Z228" s="159"/>
       <c r="AA228" s="159"/>
       <c r="AB228" s="166" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AC228" s="167"/>
       <c r="AD228" s="159"/>
       <c r="AE228" s="164" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AF228" s="165"/>
       <c r="AI228" s="79"/>
@@ -15735,7 +15735,7 @@
     </row>
     <row r="235" customHeight="1" spans="1:38">
       <c r="A235" s="77" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B235" s="77"/>
       <c r="C235" s="77"/>
@@ -15779,7 +15779,7 @@
       <c r="A236" s="78"/>
       <c r="B236" s="79"/>
       <c r="C236" s="79" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D236" s="79"/>
       <c r="E236" s="79"/>
@@ -15821,7 +15821,7 @@
       <c r="A237" s="78"/>
       <c r="B237" s="79"/>
       <c r="C237" s="79" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D237" s="79"/>
       <c r="E237" s="79"/>
@@ -15863,7 +15863,7 @@
       <c r="A238" s="78"/>
       <c r="B238" s="79"/>
       <c r="C238" s="80" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D238" s="81"/>
       <c r="E238" s="81"/>
@@ -15945,13 +15945,13 @@
       <c r="A240" s="79"/>
       <c r="B240" s="79"/>
       <c r="C240" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D240" s="79"/>
       <c r="E240" s="79"/>
       <c r="F240" s="90"/>
       <c r="G240" s="79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H240" s="79"/>
       <c r="I240" s="79"/>
@@ -16017,7 +16017,7 @@
       <c r="A242" s="79"/>
       <c r="B242" s="79"/>
       <c r="C242" s="78" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D242" s="79"/>
       <c r="E242" s="79"/>
@@ -16025,7 +16025,7 @@
       <c r="G242" s="79"/>
       <c r="H242" s="91"/>
       <c r="I242" s="79" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M242" s="125"/>
       <c r="N242" s="125"/>
@@ -16055,13 +16055,13 @@
       <c r="F243" s="90"/>
       <c r="G243" s="79"/>
       <c r="I243" s="149" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J243" s="150"/>
       <c r="K243" s="150"/>
       <c r="L243" s="151"/>
       <c r="M243" s="152" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N243" s="152"/>
       <c r="O243" s="152"/>
@@ -16092,20 +16092,20 @@
       <c r="A244" s="79"/>
       <c r="B244" s="79"/>
       <c r="C244" s="78" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D244" s="79"/>
       <c r="E244" s="79"/>
       <c r="F244" s="90"/>
       <c r="G244" s="79"/>
       <c r="I244" s="149" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J244" s="150"/>
       <c r="K244" s="150"/>
       <c r="L244" s="151"/>
       <c r="M244" s="152" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N244" s="152"/>
       <c r="O244" s="152"/>
@@ -16142,13 +16142,13 @@
       <c r="F245" s="90"/>
       <c r="G245" s="79"/>
       <c r="I245" s="149" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J245" s="150"/>
       <c r="K245" s="150"/>
       <c r="L245" s="151"/>
       <c r="M245" s="152" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N245" s="152"/>
       <c r="O245" s="152"/>
@@ -16180,20 +16180,20 @@
       <c r="A246" s="79"/>
       <c r="B246" s="79"/>
       <c r="C246" s="78" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D246" s="79"/>
       <c r="E246" s="79"/>
       <c r="F246" s="90"/>
       <c r="G246" s="79"/>
       <c r="I246" s="149" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J246" s="150"/>
       <c r="K246" s="150"/>
       <c r="L246" s="151"/>
       <c r="M246" s="152" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N246" s="152"/>
       <c r="O246" s="152"/>
@@ -16230,13 +16230,13 @@
       <c r="F247" s="90"/>
       <c r="G247" s="79"/>
       <c r="I247" s="149" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J247" s="150"/>
       <c r="K247" s="150"/>
       <c r="L247" s="151"/>
       <c r="M247" s="152" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N247" s="152"/>
       <c r="O247" s="152"/>
@@ -16273,13 +16273,13 @@
       <c r="F248" s="90"/>
       <c r="G248" s="79"/>
       <c r="I248" s="149" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J248" s="150"/>
       <c r="K248" s="150"/>
       <c r="L248" s="151"/>
       <c r="M248" s="106" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N248" s="107"/>
       <c r="O248" s="107"/>
@@ -16316,7 +16316,7 @@
       <c r="F249" s="90"/>
       <c r="G249" s="79"/>
       <c r="I249" s="149" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J249" s="150"/>
       <c r="K249" s="150"/>
@@ -16359,7 +16359,7 @@
       <c r="F250" s="90"/>
       <c r="G250" s="79"/>
       <c r="I250" s="149" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J250" s="150"/>
       <c r="K250" s="150"/>
@@ -16402,7 +16402,7 @@
       <c r="F251" s="90"/>
       <c r="G251" s="79"/>
       <c r="I251" s="157" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J251" s="157"/>
       <c r="K251" s="157"/>
@@ -16458,7 +16458,7 @@
       <c r="F253" s="90"/>
       <c r="G253" s="79"/>
       <c r="I253" s="158" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J253" s="158"/>
       <c r="K253" s="159"/>
@@ -16482,7 +16482,7 @@
       <c r="AC253" s="159"/>
       <c r="AD253" s="159"/>
       <c r="AE253" s="164" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AF253" s="165"/>
       <c r="AI253" s="79"/>
@@ -17109,7 +17109,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:38">
       <c r="A1" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -17351,7 +17351,7 @@
     </row>
     <row r="6" customHeight="1" spans="1:38">
       <c r="A6" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -17360,7 +17360,7 @@
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I6" s="34"/>
       <c r="J6" s="34"/>
@@ -17386,7 +17386,7 @@
       <c r="AD6" s="34"/>
       <c r="AE6" s="48"/>
       <c r="AF6" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG6" s="13"/>
       <c r="AH6" s="13"/>
@@ -17437,7 +17437,7 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A8" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -17447,7 +17447,7 @@
       <c r="G8" s="19"/>
       <c r="H8" s="20"/>
       <c r="I8" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AE8" s="51"/>
       <c r="AF8" s="23"/>
@@ -17460,7 +17460,7 @@
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A9" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -17470,7 +17470,7 @@
       <c r="G9" s="19"/>
       <c r="H9" s="20"/>
       <c r="J9" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AE9" s="51"/>
       <c r="AF9" s="23"/>
@@ -17483,7 +17483,7 @@
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A10" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -17493,7 +17493,7 @@
       <c r="G10" s="19"/>
       <c r="H10" s="20"/>
       <c r="K10" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AE10" s="51"/>
       <c r="AF10" s="23"/>
@@ -17514,7 +17514,7 @@
       <c r="G11" s="19"/>
       <c r="H11" s="20"/>
       <c r="K11" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AE11" s="51"/>
       <c r="AF11" s="23"/>
@@ -17553,11 +17553,11 @@
       <c r="G13" s="19"/>
       <c r="H13" s="20"/>
       <c r="J13" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AE13" s="51"/>
       <c r="AF13" s="19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG13" s="19"/>
       <c r="AH13" s="19"/>
@@ -17576,7 +17576,7 @@
       <c r="G14" s="19"/>
       <c r="H14" s="20"/>
       <c r="K14" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AE14" s="51"/>
       <c r="AF14" s="23"/>
@@ -17597,7 +17597,7 @@
       <c r="G15" s="19"/>
       <c r="H15" s="20"/>
       <c r="K15" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AE15" s="51"/>
       <c r="AF15" s="23"/>
@@ -17628,7 +17628,7 @@
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A17" s="19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -17638,7 +17638,7 @@
       <c r="G17" s="21"/>
       <c r="H17" s="20"/>
       <c r="J17" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AE17" s="51"/>
       <c r="AF17" s="23"/>
@@ -17677,7 +17677,7 @@
       <c r="G19" s="19"/>
       <c r="H19" s="20"/>
       <c r="J19" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AE19" s="51"/>
       <c r="AF19" s="23"/>
@@ -17698,7 +17698,7 @@
       <c r="G20" s="19"/>
       <c r="H20" s="20"/>
       <c r="K20" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AE20" s="51"/>
       <c r="AF20" s="23"/>
@@ -17719,7 +17719,7 @@
       <c r="G21" s="19"/>
       <c r="H21" s="20"/>
       <c r="K21" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AE21" s="51"/>
       <c r="AF21" s="23"/>
@@ -17758,11 +17758,11 @@
       <c r="G23" s="23"/>
       <c r="H23" s="20"/>
       <c r="J23" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AE23" s="51"/>
       <c r="AF23" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG23" s="23"/>
       <c r="AH23" s="23"/>
@@ -17791,7 +17791,7 @@
     </row>
     <row r="25" customHeight="1" spans="1:38">
       <c r="A25" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
@@ -17801,7 +17801,7 @@
       <c r="G25" s="19"/>
       <c r="H25" s="24"/>
       <c r="I25" s="25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J25" s="36"/>
       <c r="K25" s="25"/>
@@ -17835,7 +17835,7 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A26" s="18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -17845,7 +17845,7 @@
       <c r="G26" s="19"/>
       <c r="H26" s="20"/>
       <c r="J26" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AE26" s="51"/>
       <c r="AF26" s="23"/>
@@ -17859,7 +17859,7 @@
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A27" s="18"/>
       <c r="B27" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -17868,7 +17868,7 @@
       <c r="G27" s="19"/>
       <c r="H27" s="20"/>
       <c r="K27" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AE27" s="51"/>
       <c r="AF27" s="23"/>
@@ -17882,7 +17882,7 @@
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A28" s="18"/>
       <c r="B28" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -17891,7 +17891,7 @@
       <c r="G28" s="19"/>
       <c r="H28" s="20"/>
       <c r="K28" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AE28" s="51"/>
       <c r="AF28" s="23"/>
@@ -17905,7 +17905,7 @@
     <row r="29" s="1" customFormat="1" customHeight="1" spans="1:38">
       <c r="A29" s="22"/>
       <c r="B29" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
@@ -17934,7 +17934,7 @@
       <c r="H30" s="24"/>
       <c r="I30" s="36"/>
       <c r="J30" s="25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
@@ -17976,7 +17976,7 @@
       <c r="I31" s="25"/>
       <c r="J31" s="25"/>
       <c r="K31" s="25" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L31" s="25"/>
       <c r="M31" s="25"/>
@@ -18018,7 +18018,7 @@
       <c r="I32" s="25"/>
       <c r="J32" s="25"/>
       <c r="K32" s="25" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L32" s="25"/>
       <c r="M32" s="25"/>
@@ -18100,7 +18100,7 @@
       <c r="I34" s="25"/>
       <c r="J34" s="25"/>
       <c r="K34" s="25" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
@@ -18142,14 +18142,14 @@
       <c r="I35" s="25"/>
       <c r="J35" s="25"/>
       <c r="K35" s="29" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L35" s="29"/>
       <c r="M35" s="29"/>
       <c r="N35" s="29"/>
       <c r="O35" s="29"/>
       <c r="P35" s="37" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q35" s="45"/>
       <c r="R35" s="45"/>
@@ -18162,7 +18162,7 @@
       <c r="Y35" s="45"/>
       <c r="Z35" s="53"/>
       <c r="AA35" s="29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB35" s="29"/>
       <c r="AC35" s="29"/>
@@ -18195,7 +18195,7 @@
       <c r="N36" s="39"/>
       <c r="O36" s="39"/>
       <c r="P36" s="40" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q36" s="46"/>
       <c r="R36" s="46"/>
@@ -18208,7 +18208,7 @@
       <c r="Y36" s="46"/>
       <c r="Z36" s="54"/>
       <c r="AA36" s="44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AB36" s="44"/>
       <c r="AC36" s="44"/>
@@ -18234,14 +18234,14 @@
       <c r="I37" s="25"/>
       <c r="J37" s="25"/>
       <c r="K37" s="39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L37" s="39"/>
       <c r="M37" s="39"/>
       <c r="N37" s="39"/>
       <c r="O37" s="39"/>
       <c r="P37" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q37" s="46"/>
       <c r="R37" s="46"/>
@@ -18254,7 +18254,7 @@
       <c r="Y37" s="46"/>
       <c r="Z37" s="54"/>
       <c r="AA37" s="44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AB37" s="44"/>
       <c r="AC37" s="44"/>
@@ -18280,14 +18280,14 @@
       <c r="I38" s="25"/>
       <c r="J38" s="25"/>
       <c r="K38" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L38" s="39"/>
       <c r="M38" s="39"/>
       <c r="N38" s="39"/>
       <c r="O38" s="39"/>
       <c r="P38" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q38" s="46"/>
       <c r="R38" s="46"/>
@@ -18300,7 +18300,7 @@
       <c r="Y38" s="46"/>
       <c r="Z38" s="54"/>
       <c r="AA38" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB38" s="44"/>
       <c r="AC38" s="44"/>
@@ -18326,14 +18326,14 @@
       <c r="I39" s="25"/>
       <c r="J39" s="25"/>
       <c r="K39" s="39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L39" s="39"/>
       <c r="M39" s="39"/>
       <c r="N39" s="39"/>
       <c r="O39" s="39"/>
       <c r="P39" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q39" s="46"/>
       <c r="R39" s="46"/>
@@ -18346,7 +18346,7 @@
       <c r="Y39" s="46"/>
       <c r="Z39" s="54"/>
       <c r="AA39" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB39" s="44"/>
       <c r="AC39" s="44"/>
@@ -18372,14 +18372,14 @@
       <c r="I40" s="25"/>
       <c r="J40" s="25"/>
       <c r="K40" s="39" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L40" s="39"/>
       <c r="M40" s="39"/>
       <c r="N40" s="39"/>
       <c r="O40" s="39"/>
       <c r="P40" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q40" s="46"/>
       <c r="R40" s="46"/>
@@ -18392,7 +18392,7 @@
       <c r="Y40" s="46"/>
       <c r="Z40" s="54"/>
       <c r="AA40" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB40" s="44"/>
       <c r="AC40" s="44"/>
@@ -18418,14 +18418,14 @@
       <c r="I41" s="25"/>
       <c r="J41" s="25"/>
       <c r="K41" s="39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L41" s="39"/>
       <c r="M41" s="39"/>
       <c r="N41" s="39"/>
       <c r="O41" s="39"/>
       <c r="P41" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q41" s="46"/>
       <c r="R41" s="46"/>
@@ -18438,7 +18438,7 @@
       <c r="Y41" s="46"/>
       <c r="Z41" s="54"/>
       <c r="AA41" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB41" s="44"/>
       <c r="AC41" s="44"/>
@@ -18463,15 +18463,15 @@
       <c r="H42" s="24"/>
       <c r="I42" s="25"/>
       <c r="J42" s="25"/>
-      <c r="K42" s="256" t="s">
-        <v>263</v>
+      <c r="K42" s="257" t="s">
+        <v>262</v>
       </c>
       <c r="L42" s="39"/>
       <c r="M42" s="39"/>
       <c r="N42" s="39"/>
       <c r="O42" s="39"/>
       <c r="P42" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q42" s="46"/>
       <c r="R42" s="46"/>
@@ -18484,7 +18484,7 @@
       <c r="Y42" s="46"/>
       <c r="Z42" s="54"/>
       <c r="AA42" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB42" s="44"/>
       <c r="AC42" s="44"/>
@@ -18509,15 +18509,15 @@
       <c r="H43" s="24"/>
       <c r="I43" s="25"/>
       <c r="J43" s="25"/>
-      <c r="K43" s="256" t="s">
-        <v>186</v>
+      <c r="K43" s="257" t="s">
+        <v>185</v>
       </c>
       <c r="L43" s="39"/>
       <c r="M43" s="39"/>
       <c r="N43" s="39"/>
       <c r="O43" s="39"/>
       <c r="P43" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q43" s="46"/>
       <c r="R43" s="46"/>
@@ -18530,7 +18530,7 @@
       <c r="Y43" s="46"/>
       <c r="Z43" s="54"/>
       <c r="AA43" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB43" s="44"/>
       <c r="AC43" s="44"/>
@@ -18555,15 +18555,15 @@
       <c r="H44" s="24"/>
       <c r="I44" s="25"/>
       <c r="J44" s="25"/>
-      <c r="K44" s="256" t="s">
-        <v>264</v>
+      <c r="K44" s="257" t="s">
+        <v>263</v>
       </c>
       <c r="L44" s="39"/>
       <c r="M44" s="39"/>
       <c r="N44" s="39"/>
       <c r="O44" s="39"/>
       <c r="P44" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q44" s="46"/>
       <c r="R44" s="46"/>
@@ -18576,7 +18576,7 @@
       <c r="Y44" s="46"/>
       <c r="Z44" s="54"/>
       <c r="AA44" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB44" s="44"/>
       <c r="AC44" s="44"/>
@@ -18601,15 +18601,15 @@
       <c r="H45" s="24"/>
       <c r="I45" s="25"/>
       <c r="J45" s="25"/>
-      <c r="K45" s="256" t="s">
-        <v>265</v>
+      <c r="K45" s="257" t="s">
+        <v>264</v>
       </c>
       <c r="L45" s="39"/>
       <c r="M45" s="39"/>
       <c r="N45" s="39"/>
       <c r="O45" s="39"/>
       <c r="P45" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q45" s="46"/>
       <c r="R45" s="46"/>
@@ -18622,7 +18622,7 @@
       <c r="Y45" s="46"/>
       <c r="Z45" s="54"/>
       <c r="AA45" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB45" s="44"/>
       <c r="AC45" s="44"/>
@@ -18647,15 +18647,15 @@
       <c r="H46" s="24"/>
       <c r="I46" s="25"/>
       <c r="J46" s="25"/>
-      <c r="K46" s="256" t="s">
-        <v>266</v>
+      <c r="K46" s="257" t="s">
+        <v>265</v>
       </c>
       <c r="L46" s="39"/>
       <c r="M46" s="39"/>
       <c r="N46" s="39"/>
       <c r="O46" s="39"/>
       <c r="P46" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q46" s="46"/>
       <c r="R46" s="46"/>
@@ -18668,7 +18668,7 @@
       <c r="Y46" s="46"/>
       <c r="Z46" s="54"/>
       <c r="AA46" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB46" s="44"/>
       <c r="AC46" s="44"/>
@@ -18693,15 +18693,15 @@
       <c r="H47" s="24"/>
       <c r="I47" s="25"/>
       <c r="J47" s="25"/>
-      <c r="K47" s="256" t="s">
-        <v>267</v>
+      <c r="K47" s="257" t="s">
+        <v>266</v>
       </c>
       <c r="L47" s="39"/>
       <c r="M47" s="39"/>
       <c r="N47" s="39"/>
       <c r="O47" s="39"/>
       <c r="P47" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q47" s="46"/>
       <c r="R47" s="46"/>
@@ -18714,7 +18714,7 @@
       <c r="Y47" s="46"/>
       <c r="Z47" s="54"/>
       <c r="AA47" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB47" s="44"/>
       <c r="AC47" s="44"/>
@@ -18780,7 +18780,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L49" s="25"/>
       <c r="M49" s="25"/>
@@ -18822,14 +18822,14 @@
       <c r="I50" s="25"/>
       <c r="J50" s="25"/>
       <c r="K50" s="29" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L50" s="29"/>
       <c r="M50" s="29"/>
       <c r="N50" s="29"/>
       <c r="O50" s="29"/>
       <c r="P50" s="37" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Q50" s="45"/>
       <c r="R50" s="45"/>
@@ -18842,7 +18842,7 @@
       <c r="Y50" s="45"/>
       <c r="Z50" s="53"/>
       <c r="AA50" s="29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB50" s="29"/>
       <c r="AC50" s="29"/>
@@ -18868,14 +18868,14 @@
       <c r="I51" s="25"/>
       <c r="J51" s="25"/>
       <c r="K51" s="39" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L51" s="39"/>
       <c r="M51" s="39"/>
       <c r="N51" s="39"/>
       <c r="O51" s="39"/>
       <c r="P51" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="46"/>
       <c r="R51" s="46"/>
@@ -18888,7 +18888,7 @@
       <c r="Y51" s="46"/>
       <c r="Z51" s="54"/>
       <c r="AA51" s="44" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB51" s="44"/>
       <c r="AC51" s="44"/>
@@ -18913,8 +18913,8 @@
       <c r="H52" s="24"/>
       <c r="I52" s="25"/>
       <c r="J52" s="25"/>
-      <c r="K52" s="257" t="s">
-        <v>270</v>
+      <c r="K52" s="258" t="s">
+        <v>269</v>
       </c>
       <c r="L52" s="25"/>
       <c r="M52" s="25"/>
@@ -18995,8 +18995,8 @@
       <c r="H54" s="24"/>
       <c r="I54" s="25"/>
       <c r="J54" s="25"/>
-      <c r="K54" s="257" t="s">
-        <v>271</v>
+      <c r="K54" s="258" t="s">
+        <v>270</v>
       </c>
       <c r="L54" s="25"/>
       <c r="M54" s="25"/>
@@ -19039,7 +19039,7 @@
       <c r="J55" s="25"/>
       <c r="K55" s="41"/>
       <c r="L55" s="25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M55" s="25"/>
       <c r="N55" s="25"/>
@@ -19081,7 +19081,7 @@
       <c r="J56" s="25"/>
       <c r="K56" s="41"/>
       <c r="L56" s="25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M56" s="25"/>
       <c r="N56" s="25"/>
@@ -19161,8 +19161,8 @@
       <c r="H58" s="24"/>
       <c r="I58" s="25"/>
       <c r="J58" s="25"/>
-      <c r="K58" s="257" t="s">
-        <v>274</v>
+      <c r="K58" s="258" t="s">
+        <v>273</v>
       </c>
       <c r="L58" s="25"/>
       <c r="M58" s="25"/>
@@ -19185,7 +19185,7 @@
       <c r="AD58" s="25"/>
       <c r="AE58" s="52"/>
       <c r="AF58" s="41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG58" s="27"/>
       <c r="AH58" s="27"/>
@@ -19206,7 +19206,7 @@
       <c r="I59" s="25"/>
       <c r="J59" s="25"/>
       <c r="K59" s="25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L59" s="25"/>
       <c r="M59" s="25"/>
@@ -19238,7 +19238,7 @@
     </row>
     <row r="60" customHeight="1" spans="1:38">
       <c r="A60" s="20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -19249,7 +19249,7 @@
       <c r="H60" s="24"/>
       <c r="I60" s="25"/>
       <c r="J60" s="25" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K60" s="25"/>
       <c r="L60" s="25"/>
@@ -19273,7 +19273,7 @@
       <c r="AD60" s="25"/>
       <c r="AE60" s="52"/>
       <c r="AF60" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG60" s="1"/>
       <c r="AH60" s="1"/>
@@ -19285,7 +19285,7 @@
     <row r="61" customHeight="1" spans="1:38">
       <c r="A61" s="18"/>
       <c r="B61" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
@@ -19296,7 +19296,7 @@
       <c r="I61" s="25"/>
       <c r="J61" s="25"/>
       <c r="K61" s="25" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L61" s="36"/>
       <c r="M61" s="36"/>
@@ -19329,7 +19329,7 @@
     <row r="62" customHeight="1" spans="1:38">
       <c r="A62" s="20"/>
       <c r="B62" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -19340,7 +19340,7 @@
       <c r="I62" s="25"/>
       <c r="J62" s="25"/>
       <c r="K62" s="25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L62" s="25"/>
       <c r="M62" s="25"/>
@@ -19422,7 +19422,7 @@
       <c r="I64" s="25"/>
       <c r="J64" s="25"/>
       <c r="K64" s="25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L64" s="25"/>
       <c r="M64" s="25"/>
@@ -19465,7 +19465,7 @@
       <c r="J65" s="25"/>
       <c r="K65" s="25"/>
       <c r="L65" s="25" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M65" s="25"/>
       <c r="N65" s="25"/>
@@ -19507,7 +19507,7 @@
       <c r="J66" s="25"/>
       <c r="K66" s="25"/>
       <c r="L66" s="25" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M66" s="25"/>
       <c r="N66" s="25"/>
@@ -19549,7 +19549,7 @@
       <c r="J67" s="25"/>
       <c r="K67" s="25"/>
       <c r="L67" s="25" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M67" s="25"/>
       <c r="N67" s="25"/>
@@ -19630,7 +19630,7 @@
       <c r="I69" s="25"/>
       <c r="J69" s="25"/>
       <c r="K69" s="25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L69" s="25"/>
       <c r="M69" s="25"/>
@@ -19673,7 +19673,7 @@
       <c r="J70" s="25"/>
       <c r="K70" s="25"/>
       <c r="L70" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M70" s="25"/>
       <c r="N70" s="25"/>
@@ -19715,7 +19715,7 @@
       <c r="J71" s="25"/>
       <c r="K71" s="25"/>
       <c r="L71" s="25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M71" s="25"/>
       <c r="N71" s="25"/>
@@ -19786,7 +19786,7 @@
     </row>
     <row r="73" customHeight="1" spans="1:38">
       <c r="A73" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -19797,7 +19797,7 @@
       <c r="H73" s="24"/>
       <c r="I73" s="25"/>
       <c r="J73" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K73" s="25"/>
       <c r="L73" s="25"/>
@@ -19879,7 +19879,7 @@
       <c r="H75" s="24"/>
       <c r="I75" s="25"/>
       <c r="J75" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K75" s="25"/>
       <c r="L75" s="25"/>
@@ -19922,7 +19922,7 @@
       <c r="I76" s="25"/>
       <c r="J76" s="25"/>
       <c r="K76" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
@@ -19956,7 +19956,7 @@
       <c r="A77" s="20"/>
       <c r="H77" s="20"/>
       <c r="K77" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AE77" s="51"/>
       <c r="AL77" s="51"/>
@@ -20005,11 +20005,11 @@
       <c r="A79" s="20"/>
       <c r="H79" s="20"/>
       <c r="J79" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AE79" s="51"/>
       <c r="AF79" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AL79" s="51"/>
     </row>
